--- a/2026/EL MIRADOR/Mayo/Mayo - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Mayo/Mayo - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB651A5-179E-4AB5-A6FE-FE7318091AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D7F07E-BAD5-4C78-96DA-2D34F32C80B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1148,9 +1148,6 @@
     <t>Caja Real -Banco - SUM + Ordinaria</t>
   </si>
   <si>
-    <t>Cuota 2/2026 ARBA</t>
-  </si>
-  <si>
     <t>ARBA:</t>
   </si>
   <si>
@@ -1330,6 +1327,9 @@
   </si>
   <si>
     <t>Del total de caja ($1.292.035,37) $$1.031.545,12 corresponde devolver a la desarrolladora, por ende la caja real del consorcio es de $260.490,25</t>
+  </si>
+  <si>
+    <t>Cuota ARBA</t>
   </si>
 </sst>
 </file>
@@ -2343,21 +2343,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2367,20 +2423,110 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2399,15 +2545,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2481,16 +2618,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2516,27 +2662,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2571,131 +2696,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -3177,7 +3177,7 @@
       <c r="A5" s="87"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="92" t="s">
@@ -3220,123 +3220,123 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="231" t="s">
+      <c r="A14" s="303" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="231"/>
-      <c r="C14" s="231"/>
-      <c r="D14" s="231"/>
-      <c r="E14" s="231"/>
-      <c r="F14" s="231"/>
-      <c r="G14" s="231"/>
-      <c r="H14" s="231"/>
-      <c r="I14" s="231"/>
-      <c r="J14" s="231"/>
+      <c r="B14" s="303"/>
+      <c r="C14" s="303"/>
+      <c r="D14" s="303"/>
+      <c r="E14" s="303"/>
+      <c r="F14" s="303"/>
+      <c r="G14" s="303"/>
+      <c r="H14" s="303"/>
+      <c r="I14" s="303"/>
+      <c r="J14" s="303"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="231"/>
-      <c r="B15" s="231"/>
-      <c r="C15" s="231"/>
-      <c r="D15" s="231"/>
-      <c r="E15" s="231"/>
-      <c r="F15" s="231"/>
-      <c r="G15" s="231"/>
-      <c r="H15" s="231"/>
-      <c r="I15" s="231"/>
-      <c r="J15" s="231"/>
+      <c r="A15" s="303"/>
+      <c r="B15" s="303"/>
+      <c r="C15" s="303"/>
+      <c r="D15" s="303"/>
+      <c r="E15" s="303"/>
+      <c r="F15" s="303"/>
+      <c r="G15" s="303"/>
+      <c r="H15" s="303"/>
+      <c r="I15" s="303"/>
+      <c r="J15" s="303"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="231"/>
-      <c r="B16" s="231"/>
-      <c r="C16" s="231"/>
-      <c r="D16" s="231"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="231"/>
-      <c r="G16" s="231"/>
-      <c r="H16" s="231"/>
-      <c r="I16" s="231"/>
-      <c r="J16" s="231"/>
+      <c r="A16" s="303"/>
+      <c r="B16" s="303"/>
+      <c r="C16" s="303"/>
+      <c r="D16" s="303"/>
+      <c r="E16" s="303"/>
+      <c r="F16" s="303"/>
+      <c r="G16" s="303"/>
+      <c r="H16" s="303"/>
+      <c r="I16" s="303"/>
+      <c r="J16" s="303"/>
     </row>
     <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="231"/>
-      <c r="B17" s="231"/>
-      <c r="C17" s="231"/>
-      <c r="D17" s="231"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="231"/>
-      <c r="G17" s="231"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="231"/>
-      <c r="J17" s="231"/>
+      <c r="A17" s="303"/>
+      <c r="B17" s="303"/>
+      <c r="C17" s="303"/>
+      <c r="D17" s="303"/>
+      <c r="E17" s="303"/>
+      <c r="F17" s="303"/>
+      <c r="G17" s="303"/>
+      <c r="H17" s="303"/>
+      <c r="I17" s="303"/>
+      <c r="J17" s="303"/>
     </row>
     <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="231"/>
-      <c r="B18" s="231"/>
-      <c r="C18" s="231"/>
-      <c r="D18" s="231"/>
-      <c r="E18" s="231"/>
-      <c r="F18" s="231"/>
-      <c r="G18" s="231"/>
-      <c r="H18" s="231"/>
-      <c r="I18" s="231"/>
-      <c r="J18" s="231"/>
+      <c r="A18" s="303"/>
+      <c r="B18" s="303"/>
+      <c r="C18" s="303"/>
+      <c r="D18" s="303"/>
+      <c r="E18" s="303"/>
+      <c r="F18" s="303"/>
+      <c r="G18" s="303"/>
+      <c r="H18" s="303"/>
+      <c r="I18" s="303"/>
+      <c r="J18" s="303"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="232" t="s">
-        <v>419</v>
-      </c>
-      <c r="B20" s="232"/>
-      <c r="C20" s="232"/>
-      <c r="D20" s="232"/>
-      <c r="E20" s="232"/>
-      <c r="F20" s="232"/>
-      <c r="G20" s="232"/>
-      <c r="H20" s="232"/>
-      <c r="I20" s="232"/>
-      <c r="J20" s="232"/>
+      <c r="A20" s="304" t="s">
+        <v>418</v>
+      </c>
+      <c r="B20" s="304"/>
+      <c r="C20" s="304"/>
+      <c r="D20" s="304"/>
+      <c r="E20" s="304"/>
+      <c r="F20" s="304"/>
+      <c r="G20" s="304"/>
+      <c r="H20" s="304"/>
+      <c r="I20" s="304"/>
+      <c r="J20" s="304"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="232"/>
-      <c r="B21" s="232"/>
-      <c r="C21" s="232"/>
-      <c r="D21" s="232"/>
-      <c r="E21" s="232"/>
-      <c r="F21" s="232"/>
-      <c r="G21" s="232"/>
-      <c r="H21" s="232"/>
-      <c r="I21" s="232"/>
-      <c r="J21" s="232"/>
+      <c r="A21" s="304"/>
+      <c r="B21" s="304"/>
+      <c r="C21" s="304"/>
+      <c r="D21" s="304"/>
+      <c r="E21" s="304"/>
+      <c r="F21" s="304"/>
+      <c r="G21" s="304"/>
+      <c r="H21" s="304"/>
+      <c r="I21" s="304"/>
+      <c r="J21" s="304"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="232"/>
-      <c r="B22" s="232"/>
-      <c r="C22" s="232"/>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
+      <c r="A22" s="304"/>
+      <c r="B22" s="304"/>
+      <c r="C22" s="304"/>
+      <c r="D22" s="304"/>
+      <c r="E22" s="304"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="304"/>
+      <c r="H22" s="304"/>
+      <c r="I22" s="304"/>
+      <c r="J22" s="304"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="317" t="s">
+      <c r="A24" s="230" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="318"/>
-      <c r="C24" s="319"/>
-      <c r="D24" s="320"/>
-      <c r="E24" s="321" t="s">
+      <c r="B24" s="231"/>
+      <c r="C24" s="232"/>
+      <c r="D24" s="233"/>
+      <c r="E24" s="234" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="321" t="s">
+      <c r="F24" s="234" t="s">
         <v>165</v>
       </c>
       <c r="G24" s="70" t="s">
@@ -3353,14 +3353,14 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="322" t="s">
+      <c r="A25" s="235" t="s">
         <v>341</v>
       </c>
       <c r="B25" s="181"/>
       <c r="C25" s="181"/>
       <c r="D25" s="179"/>
-      <c r="E25" s="323"/>
-      <c r="F25" s="323"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="236"/>
       <c r="G25" s="44"/>
       <c r="H25" s="44"/>
       <c r="I25" s="44"/>
@@ -3368,12 +3368,12 @@
       <c r="L25" s="50"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="324" t="s">
-        <v>395</v>
+      <c r="A26" s="237" t="s">
+        <v>394</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D26" s="179">
         <v>3000000</v>
@@ -3387,11 +3387,11 @@
       <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="325" t="s">
+      <c r="A27" s="238" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="325"/>
-      <c r="C27" s="325"/>
+      <c r="B27" s="238"/>
+      <c r="C27" s="238"/>
       <c r="D27" s="31">
         <f>SUM(D25:D26)</f>
         <v>3000000</v>
@@ -3400,7 +3400,7 @@
         <f>D27*93.2%</f>
         <v>2796000</v>
       </c>
-      <c r="F27" s="326">
+      <c r="F27" s="239">
         <f>$D27*1.08%</f>
         <v>32400</v>
       </c>
@@ -3430,14 +3430,14 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="324" t="s">
+      <c r="A28" s="237" t="s">
         <v>234</v>
       </c>
       <c r="B28" s="181"/>
       <c r="C28" s="181"/>
       <c r="D28" s="179"/>
-      <c r="E28" s="323"/>
-      <c r="F28" s="323"/>
+      <c r="E28" s="236"/>
+      <c r="F28" s="236"/>
       <c r="G28" s="44"/>
       <c r="H28" s="44"/>
       <c r="I28" s="44"/>
@@ -3445,18 +3445,18 @@
       <c r="L28" s="50"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="324" t="s">
-        <v>384</v>
+      <c r="A29" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B29" s="181" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C29" s="181"/>
       <c r="D29" s="179">
         <v>63630</v>
       </c>
-      <c r="E29" s="323"/>
-      <c r="F29" s="323"/>
+      <c r="E29" s="236"/>
+      <c r="F29" s="236"/>
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
       <c r="I29" s="44"/>
@@ -3464,18 +3464,18 @@
       <c r="L29" s="50"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="324" t="s">
-        <v>384</v>
+      <c r="A30" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B30" s="181" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C30" s="181"/>
       <c r="D30" s="179">
         <v>60000</v>
       </c>
-      <c r="E30" s="323"/>
-      <c r="F30" s="323"/>
+      <c r="E30" s="236"/>
+      <c r="F30" s="236"/>
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
       <c r="I30" s="44"/>
@@ -3483,18 +3483,18 @@
       <c r="L30" s="50"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="324" t="s">
-        <v>384</v>
+      <c r="A31" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B31" s="181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C31" s="181"/>
       <c r="D31" s="179">
         <v>99726.06</v>
       </c>
-      <c r="E31" s="323"/>
-      <c r="F31" s="323"/>
+      <c r="E31" s="236"/>
+      <c r="F31" s="236"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
       <c r="I31" s="44"/>
@@ -3502,18 +3502,18 @@
       <c r="L31" s="50"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="324" t="s">
-        <v>384</v>
+      <c r="A32" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B32" s="181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C32" s="181"/>
       <c r="D32" s="179">
         <v>44990.07</v>
       </c>
-      <c r="E32" s="323"/>
-      <c r="F32" s="323"/>
+      <c r="E32" s="236"/>
+      <c r="F32" s="236"/>
       <c r="G32" s="44"/>
       <c r="H32" s="44"/>
       <c r="I32" s="44"/>
@@ -3521,18 +3521,18 @@
       <c r="L32" s="50"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="324" t="s">
-        <v>384</v>
+      <c r="A33" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B33" s="181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C33" s="181"/>
       <c r="D33" s="179">
         <v>70000.03</v>
       </c>
-      <c r="E33" s="323"/>
-      <c r="F33" s="323"/>
+      <c r="E33" s="236"/>
+      <c r="F33" s="236"/>
       <c r="G33" s="44"/>
       <c r="H33" s="44"/>
       <c r="I33" s="44"/>
@@ -3540,18 +3540,18 @@
       <c r="L33" s="50"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="324" t="s">
-        <v>384</v>
+      <c r="A34" s="237" t="s">
+        <v>383</v>
       </c>
       <c r="B34" s="181" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C34" s="181"/>
       <c r="D34" s="179">
         <v>60015.95</v>
       </c>
-      <c r="E34" s="323"/>
-      <c r="F34" s="323"/>
+      <c r="E34" s="236"/>
+      <c r="F34" s="236"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44"/>
       <c r="I34" s="44"/>
@@ -3559,12 +3559,12 @@
       <c r="L34" s="50"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="324"/>
+      <c r="A35" s="237"/>
       <c r="B35" s="181"/>
       <c r="C35" s="181"/>
       <c r="D35" s="179"/>
-      <c r="E35" s="323"/>
-      <c r="F35" s="323"/>
+      <c r="E35" s="236"/>
+      <c r="F35" s="236"/>
       <c r="G35" s="44"/>
       <c r="H35" s="44"/>
       <c r="I35" s="44"/>
@@ -3572,11 +3572,11 @@
       <c r="L35" s="50"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="325" t="s">
+      <c r="A36" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="325"/>
-      <c r="C36" s="325"/>
+      <c r="B36" s="238"/>
+      <c r="C36" s="238"/>
       <c r="D36" s="31">
         <f>SUM(D29:D35)</f>
         <v>398362.11000000004</v>
@@ -3600,14 +3600,14 @@
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="324" t="s">
+      <c r="A37" s="237" t="s">
         <v>230</v>
       </c>
       <c r="B37" s="141"/>
       <c r="C37" s="141"/>
       <c r="D37" s="179"/>
-      <c r="E37" s="327"/>
-      <c r="F37" s="327"/>
+      <c r="E37" s="240"/>
+      <c r="F37" s="240"/>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
@@ -3619,12 +3619,12 @@
         <v>342</v>
       </c>
       <c r="B38" s="141"/>
-      <c r="C38" s="328"/>
+      <c r="C38" s="241"/>
       <c r="D38" s="179">
         <v>0</v>
       </c>
-      <c r="E38" s="327"/>
-      <c r="F38" s="327"/>
+      <c r="E38" s="240"/>
+      <c r="F38" s="240"/>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
@@ -3636,16 +3636,16 @@
         <v>362</v>
       </c>
       <c r="B39" s="141" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C39" s="141" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D39" s="179">
         <v>1742902</v>
       </c>
-      <c r="E39" s="327"/>
-      <c r="F39" s="327"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
@@ -3657,16 +3657,16 @@
         <v>233</v>
       </c>
       <c r="B40" s="141" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C40" s="141" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D40" s="179">
         <v>1742902</v>
       </c>
-      <c r="E40" s="327"/>
-      <c r="F40" s="327"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
       <c r="I40" s="38"/>
@@ -3678,8 +3678,8 @@
       <c r="B41" s="141"/>
       <c r="C41" s="141"/>
       <c r="D41" s="179"/>
-      <c r="E41" s="327"/>
-      <c r="F41" s="327"/>
+      <c r="E41" s="240"/>
+      <c r="F41" s="240"/>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
@@ -3687,11 +3687,11 @@
       <c r="L41" s="50"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="325" t="s">
+      <c r="A42" s="238" t="s">
         <v>232</v>
       </c>
-      <c r="B42" s="325"/>
-      <c r="C42" s="325"/>
+      <c r="B42" s="238"/>
+      <c r="C42" s="238"/>
       <c r="D42" s="180">
         <f>SUM(D38:D41)</f>
         <v>3485804</v>
@@ -3700,7 +3700,7 @@
         <f>D42*93.2%</f>
         <v>3248769.3280000002</v>
       </c>
-      <c r="F42" s="326">
+      <c r="F42" s="239">
         <f>$D42*1.08%</f>
         <v>37646.683199999999</v>
       </c>
@@ -3730,14 +3730,14 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="324" t="s">
+      <c r="A43" s="237" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="181"/>
       <c r="C43" s="181"/>
       <c r="D43" s="33"/>
-      <c r="E43" s="329"/>
-      <c r="F43" s="329"/>
+      <c r="E43" s="242"/>
+      <c r="F43" s="242"/>
       <c r="G43" s="34"/>
       <c r="H43" s="34"/>
       <c r="I43" s="34"/>
@@ -3749,8 +3749,8 @@
       <c r="B44" s="181"/>
       <c r="C44" s="181"/>
       <c r="D44" s="33"/>
-      <c r="E44" s="330"/>
-      <c r="F44" s="330"/>
+      <c r="E44" s="243"/>
+      <c r="F44" s="243"/>
       <c r="G44" s="84"/>
       <c r="H44" s="84"/>
       <c r="I44" s="84"/>
@@ -3762,8 +3762,8 @@
       <c r="B45" s="181"/>
       <c r="C45" s="181"/>
       <c r="D45" s="33"/>
-      <c r="E45" s="330"/>
-      <c r="F45" s="330"/>
+      <c r="E45" s="243"/>
+      <c r="F45" s="243"/>
       <c r="G45" s="84"/>
       <c r="H45" s="84"/>
       <c r="I45" s="84"/>
@@ -3773,10 +3773,10 @@
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="181"/>
       <c r="B46" s="181"/>
-      <c r="C46" s="331"/>
+      <c r="C46" s="244"/>
       <c r="D46" s="33"/>
-      <c r="E46" s="332"/>
-      <c r="F46" s="332"/>
+      <c r="E46" s="245"/>
+      <c r="F46" s="245"/>
       <c r="G46" s="55"/>
       <c r="H46" s="55"/>
       <c r="I46" s="55"/>
@@ -3784,11 +3784,11 @@
       <c r="L46" s="50"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="325" t="s">
+      <c r="A47" s="238" t="s">
         <v>231</v>
       </c>
-      <c r="B47" s="325"/>
-      <c r="C47" s="325"/>
+      <c r="B47" s="238"/>
+      <c r="C47" s="238"/>
       <c r="D47" s="31">
         <f>SUM(D43:D46)</f>
         <v>0</v>
@@ -3797,7 +3797,7 @@
         <f>D47*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F47" s="326">
+      <c r="F47" s="239">
         <f>$D47*1.08%</f>
         <v>0</v>
       </c>
@@ -3827,14 +3827,14 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="324" t="s">
+      <c r="A48" s="237" t="s">
         <v>222</v>
       </c>
       <c r="B48" s="181"/>
       <c r="C48" s="181"/>
       <c r="D48" s="181"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="E48" s="246"/>
+      <c r="F48" s="246"/>
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="35"/>
@@ -3852,11 +3852,11 @@
       <c r="D49" s="33">
         <v>214371</v>
       </c>
-      <c r="E49" s="323">
+      <c r="E49" s="236">
         <f>D49*93.2%</f>
         <v>199793.772</v>
       </c>
-      <c r="F49" s="323">
+      <c r="F49" s="236">
         <f>$D49*1.08%</f>
         <v>2315.2067999999999</v>
       </c>
@@ -3883,12 +3883,12 @@
       <c r="L49" s="50"/>
     </row>
     <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="334"/>
-      <c r="B50" s="335"/>
+      <c r="A50" s="297"/>
+      <c r="B50" s="298"/>
       <c r="C50" s="181"/>
       <c r="D50" s="33"/>
-      <c r="E50" s="323"/>
-      <c r="F50" s="323"/>
+      <c r="E50" s="236"/>
+      <c r="F50" s="236"/>
       <c r="G50" s="44"/>
       <c r="H50" s="44"/>
       <c r="I50" s="44"/>
@@ -3897,11 +3897,11 @@
       <c r="L50" s="50"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="325" t="s">
+      <c r="A51" s="238" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="336"/>
-      <c r="C51" s="336"/>
+      <c r="B51" s="247"/>
+      <c r="C51" s="247"/>
       <c r="D51" s="31">
         <f t="shared" ref="D51:J51" si="0">SUM(D49:D50)</f>
         <v>214371</v>
@@ -3940,14 +3940,14 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="324" t="s">
+      <c r="A52" s="237" t="s">
         <v>3</v>
       </c>
       <c r="B52" s="181"/>
       <c r="C52" s="181"/>
       <c r="D52" s="182"/>
-      <c r="E52" s="333"/>
-      <c r="F52" s="333"/>
+      <c r="E52" s="246"/>
+      <c r="F52" s="246"/>
       <c r="G52" s="35"/>
       <c r="H52" s="35"/>
       <c r="I52" s="35"/>
@@ -3955,21 +3955,21 @@
       <c r="L52" s="50"/>
     </row>
     <row r="53" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="337" t="s">
+      <c r="A53" s="248" t="s">
         <v>227</v>
       </c>
       <c r="B53" s="181"/>
-      <c r="C53" s="331" t="s">
-        <v>404</v>
-      </c>
-      <c r="D53" s="338">
+      <c r="C53" s="244" t="s">
+        <v>403</v>
+      </c>
+      <c r="D53" s="249">
         <v>36079.1</v>
       </c>
-      <c r="E53" s="339">
+      <c r="E53" s="250">
         <f>D53*93.2%</f>
         <v>33625.7212</v>
       </c>
-      <c r="F53" s="323">
+      <c r="F53" s="236">
         <f>$D53*1.08%</f>
         <v>389.65428000000003</v>
       </c>
@@ -4005,17 +4005,17 @@
         <v>228</v>
       </c>
       <c r="B54" s="181"/>
-      <c r="C54" s="331" t="s">
-        <v>391</v>
-      </c>
-      <c r="D54" s="338">
+      <c r="C54" s="244" t="s">
+        <v>390</v>
+      </c>
+      <c r="D54" s="249">
         <v>3898893.1</v>
       </c>
-      <c r="E54" s="339">
+      <c r="E54" s="250">
         <f t="shared" ref="E54" si="1">D54*93.2%</f>
         <v>3633768.3692000001</v>
       </c>
-      <c r="F54" s="323">
+      <c r="F54" s="236">
         <f t="shared" ref="F54" si="2">$D54*1.08%</f>
         <v>42108.045480000001</v>
       </c>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B55" s="181"/>
       <c r="C55" s="181" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D55" s="33">
         <v>151564.79999999999</v>
       </c>
-      <c r="E55" s="339">
+      <c r="E55" s="250">
         <f>D55</f>
         <v>151564.79999999999</v>
       </c>
-      <c r="F55" s="323"/>
+      <c r="F55" s="236"/>
       <c r="G55" s="44"/>
       <c r="H55" s="44"/>
       <c r="I55" s="44"/>
@@ -4085,20 +4085,20 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="181" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B56" s="181"/>
-      <c r="C56" s="331" t="s">
+      <c r="C56" s="244" t="s">
         <v>360</v>
       </c>
       <c r="D56" s="33">
         <v>359504.14</v>
       </c>
-      <c r="E56" s="339">
+      <c r="E56" s="250">
         <f>D56</f>
         <v>359504.14</v>
       </c>
-      <c r="F56" s="323"/>
+      <c r="F56" s="236"/>
       <c r="G56" s="44"/>
       <c r="H56" s="44"/>
       <c r="I56" s="44"/>
@@ -4115,21 +4115,21 @@
       <c r="N56" s="64"/>
     </row>
     <row r="57" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="340" t="s">
+      <c r="A57" s="285" t="s">
         <v>361</v>
       </c>
-      <c r="B57" s="341"/>
+      <c r="B57" s="305"/>
       <c r="C57" s="141" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D57" s="33">
         <v>50000</v>
       </c>
-      <c r="E57" s="339">
+      <c r="E57" s="250">
         <f>D57</f>
         <v>50000</v>
       </c>
-      <c r="F57" s="323"/>
+      <c r="F57" s="236"/>
       <c r="G57" s="44"/>
       <c r="H57" s="44"/>
       <c r="I57" s="44"/>
@@ -4156,17 +4156,17 @@
         <v>259</v>
       </c>
       <c r="B58" s="141"/>
-      <c r="C58" s="331" t="s">
-        <v>392</v>
+      <c r="C58" s="244" t="s">
+        <v>391</v>
       </c>
       <c r="D58" s="33">
         <v>5760.01</v>
       </c>
-      <c r="E58" s="339">
+      <c r="E58" s="250">
         <f>D58*93.2%</f>
         <v>5368.3293200000007</v>
       </c>
-      <c r="F58" s="323">
+      <c r="F58" s="236">
         <f>$D58*1.08%</f>
         <v>62.208108000000003</v>
       </c>
@@ -4208,17 +4208,17 @@
         <v>260</v>
       </c>
       <c r="B59" s="141"/>
-      <c r="C59" s="331" t="s">
-        <v>392</v>
+      <c r="C59" s="244" t="s">
+        <v>391</v>
       </c>
       <c r="D59" s="33">
         <v>907421.13</v>
       </c>
-      <c r="E59" s="339">
+      <c r="E59" s="250">
         <f>D59</f>
         <v>907421.13</v>
       </c>
-      <c r="F59" s="323"/>
+      <c r="F59" s="236"/>
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
       <c r="I59" s="44"/>
@@ -4241,21 +4241,21 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="342" t="s">
+      <c r="A60" s="251" t="s">
         <v>258</v>
       </c>
-      <c r="B60" s="343"/>
+      <c r="B60" s="252"/>
       <c r="C60" s="181" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D60" s="33">
         <v>120000</v>
       </c>
-      <c r="E60" s="339">
+      <c r="E60" s="250">
         <f>D60</f>
         <v>120000</v>
       </c>
-      <c r="F60" s="339"/>
+      <c r="F60" s="250"/>
       <c r="G60" s="49"/>
       <c r="H60" s="49"/>
       <c r="I60" s="49"/>
@@ -4278,11 +4278,11 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="325" t="s">
+      <c r="A61" s="238" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="336"/>
-      <c r="C61" s="336"/>
+      <c r="B61" s="247"/>
+      <c r="C61" s="247"/>
       <c r="D61" s="31">
         <f>SUM(D53:D60)</f>
         <v>5529222.2799999993</v>
@@ -4329,8 +4329,8 @@
       <c r="B62" s="181"/>
       <c r="C62" s="181"/>
       <c r="D62" s="182"/>
-      <c r="E62" s="333"/>
-      <c r="F62" s="333"/>
+      <c r="E62" s="246"/>
+      <c r="F62" s="246"/>
       <c r="G62" s="35"/>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
@@ -4342,8 +4342,8 @@
       <c r="B63" s="181"/>
       <c r="C63" s="181"/>
       <c r="D63" s="182"/>
-      <c r="E63" s="329"/>
-      <c r="F63" s="329"/>
+      <c r="E63" s="242"/>
+      <c r="F63" s="242"/>
       <c r="G63" s="34"/>
       <c r="H63" s="34"/>
       <c r="I63" s="34"/>
@@ -4351,14 +4351,14 @@
       <c r="L63" s="50"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="324" t="s">
+      <c r="A64" s="237" t="s">
         <v>223</v>
       </c>
       <c r="B64" s="181"/>
       <c r="C64" s="181"/>
       <c r="D64" s="182"/>
-      <c r="E64" s="329"/>
-      <c r="F64" s="329"/>
+      <c r="E64" s="242"/>
+      <c r="F64" s="242"/>
       <c r="G64" s="34"/>
       <c r="H64" s="34"/>
       <c r="I64" s="34"/>
@@ -4366,21 +4366,21 @@
       <c r="L64" s="50"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="329" t="s">
+      <c r="A65" s="242" t="s">
         <v>340</v>
       </c>
-      <c r="B65" s="344"/>
+      <c r="B65" s="253"/>
       <c r="C65" s="141" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D65" s="33">
         <v>200000</v>
       </c>
-      <c r="E65" s="339">
+      <c r="E65" s="250">
         <f t="shared" ref="E65:E67" si="12">D65</f>
         <v>200000</v>
       </c>
-      <c r="F65" s="332"/>
+      <c r="F65" s="245"/>
       <c r="G65" s="55"/>
       <c r="H65" s="55"/>
       <c r="I65" s="55"/>
@@ -4395,21 +4395,21 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="334" t="s">
+      <c r="A66" s="297" t="s">
         <v>339</v>
       </c>
-      <c r="B66" s="335"/>
+      <c r="B66" s="298"/>
       <c r="C66" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D66" s="33">
         <v>314672.59999999998</v>
       </c>
-      <c r="E66" s="339">
+      <c r="E66" s="250">
         <f>D66*93.2%</f>
         <v>293274.86320000002</v>
       </c>
-      <c r="F66" s="323">
+      <c r="F66" s="236">
         <f>$D66*1.08%</f>
         <v>3398.4640799999997</v>
       </c>
@@ -4439,21 +4439,21 @@
       </c>
     </row>
     <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="334" t="s">
+      <c r="A67" s="297" t="s">
         <v>339</v>
       </c>
-      <c r="B67" s="335"/>
+      <c r="B67" s="298"/>
       <c r="C67" s="33" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D67" s="33">
         <v>313198</v>
       </c>
-      <c r="E67" s="339">
+      <c r="E67" s="250">
         <f t="shared" si="12"/>
         <v>313198</v>
       </c>
-      <c r="F67" s="323"/>
+      <c r="F67" s="236"/>
       <c r="G67" s="44"/>
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
@@ -4462,21 +4462,21 @@
       <c r="L67" s="54"/>
     </row>
     <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="334" t="s">
-        <v>400</v>
-      </c>
-      <c r="B68" s="335"/>
+      <c r="A68" s="297" t="s">
+        <v>399</v>
+      </c>
+      <c r="B68" s="298"/>
       <c r="C68" s="33" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D68" s="33">
         <v>597500</v>
       </c>
-      <c r="E68" s="339">
+      <c r="E68" s="250">
         <f>D68*93.2%</f>
         <v>556870</v>
       </c>
-      <c r="F68" s="323">
+      <c r="F68" s="236">
         <f>$D68*1.08%</f>
         <v>6453</v>
       </c>
@@ -4503,21 +4503,21 @@
       <c r="L68" s="54"/>
     </row>
     <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="334" t="s">
-        <v>389</v>
-      </c>
-      <c r="B69" s="335"/>
+      <c r="A69" s="297" t="s">
+        <v>388</v>
+      </c>
+      <c r="B69" s="298"/>
       <c r="C69" s="33" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D69" s="33">
         <v>21000</v>
       </c>
-      <c r="E69" s="339">
+      <c r="E69" s="250">
         <f>D69</f>
         <v>21000</v>
       </c>
-      <c r="F69" s="323"/>
+      <c r="F69" s="236"/>
       <c r="G69" s="44"/>
       <c r="H69" s="44"/>
       <c r="I69" s="44"/>
@@ -4532,21 +4532,21 @@
       </c>
     </row>
     <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="345" t="s">
+      <c r="A70" s="254" t="s">
+        <v>401</v>
+      </c>
+      <c r="B70" s="255"/>
+      <c r="C70" s="33" t="s">
         <v>402</v>
-      </c>
-      <c r="B70" s="346"/>
-      <c r="C70" s="33" t="s">
-        <v>403</v>
       </c>
       <c r="D70" s="33">
         <v>200000</v>
       </c>
-      <c r="E70" s="339">
+      <c r="E70" s="250">
         <f>D70</f>
         <v>200000</v>
       </c>
-      <c r="F70" s="323"/>
+      <c r="F70" s="236"/>
       <c r="G70" s="44"/>
       <c r="H70" s="44"/>
       <c r="I70" s="44"/>
@@ -4558,21 +4558,21 @@
       <c r="L70" s="54"/>
     </row>
     <row r="71" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="345" t="s">
+      <c r="A71" s="254" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" s="255"/>
+      <c r="C71" s="33" t="s">
         <v>386</v>
-      </c>
-      <c r="B71" s="346"/>
-      <c r="C71" s="33" t="s">
-        <v>387</v>
       </c>
       <c r="D71" s="33">
         <v>125000</v>
       </c>
-      <c r="E71" s="339">
+      <c r="E71" s="250">
         <f>D71</f>
         <v>125000</v>
       </c>
-      <c r="F71" s="323"/>
+      <c r="F71" s="236"/>
       <c r="G71" s="44"/>
       <c r="H71" s="44"/>
       <c r="I71" s="44"/>
@@ -4584,21 +4584,21 @@
       <c r="L71" s="54"/>
     </row>
     <row r="72" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="345" t="s">
-        <v>390</v>
-      </c>
-      <c r="B72" s="346"/>
+      <c r="A72" s="254" t="s">
+        <v>389</v>
+      </c>
+      <c r="B72" s="255"/>
       <c r="C72" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D72" s="33">
         <v>25000</v>
       </c>
-      <c r="E72" s="339">
+      <c r="E72" s="250">
         <f>D72</f>
         <v>25000</v>
       </c>
-      <c r="F72" s="323"/>
+      <c r="F72" s="236"/>
       <c r="G72" s="44"/>
       <c r="H72" s="44"/>
       <c r="I72" s="44"/>
@@ -4610,21 +4610,21 @@
       <c r="L72" s="54"/>
     </row>
     <row r="73" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="334" t="s">
+      <c r="A73" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="B73" s="335"/>
+      <c r="B73" s="298"/>
       <c r="C73" s="33" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D73" s="33">
         <v>46200</v>
       </c>
-      <c r="E73" s="339">
+      <c r="E73" s="250">
         <f>D73</f>
         <v>46200</v>
       </c>
-      <c r="F73" s="323"/>
+      <c r="F73" s="236"/>
       <c r="G73" s="44"/>
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
@@ -4636,21 +4636,21 @@
       <c r="L73" s="54"/>
     </row>
     <row r="74" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="334" t="s">
-        <v>407</v>
-      </c>
-      <c r="B74" s="335"/>
+      <c r="A74" s="297" t="s">
+        <v>406</v>
+      </c>
+      <c r="B74" s="298"/>
       <c r="C74" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D74" s="33">
         <v>191400</v>
       </c>
-      <c r="E74" s="339">
+      <c r="E74" s="250">
         <f>D74*93.2%</f>
         <v>178384.80000000002</v>
       </c>
-      <c r="F74" s="323">
+      <c r="F74" s="236">
         <f>$D74*1.08%</f>
         <v>2067.12</v>
       </c>
@@ -4674,11 +4674,11 @@
       <c r="M74" s="32"/>
     </row>
     <row r="75" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="325" t="s">
+      <c r="A75" s="238" t="s">
         <v>224</v>
       </c>
-      <c r="B75" s="325"/>
-      <c r="C75" s="325"/>
+      <c r="B75" s="238"/>
+      <c r="C75" s="238"/>
       <c r="D75" s="31">
         <f t="shared" ref="D75:J75" si="15">SUM(D65:D74)</f>
         <v>2033970.6</v>
@@ -4722,8 +4722,8 @@
       <c r="B76" s="181"/>
       <c r="C76" s="181"/>
       <c r="D76" s="182"/>
-      <c r="E76" s="333"/>
-      <c r="F76" s="333"/>
+      <c r="E76" s="246"/>
+      <c r="F76" s="246"/>
       <c r="G76" s="35"/>
       <c r="H76" s="35"/>
       <c r="I76" s="35"/>
@@ -4735,8 +4735,8 @@
       <c r="B77" s="181"/>
       <c r="C77" s="181"/>
       <c r="D77" s="182"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="E77" s="242"/>
+      <c r="F77" s="242"/>
       <c r="G77" s="34"/>
       <c r="H77" s="34"/>
       <c r="I77" s="34"/>
@@ -4744,14 +4744,14 @@
       <c r="L77" s="50"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="324" t="s">
+      <c r="A78" s="237" t="s">
         <v>5</v>
       </c>
       <c r="B78" s="181"/>
       <c r="C78" s="181"/>
       <c r="D78" s="182"/>
-      <c r="E78" s="329"/>
-      <c r="F78" s="329"/>
+      <c r="E78" s="242"/>
+      <c r="F78" s="242"/>
       <c r="G78" s="34"/>
       <c r="H78" s="34"/>
       <c r="I78" s="34"/>
@@ -4759,23 +4759,23 @@
       <c r="L78" s="50"/>
     </row>
     <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="347" t="s">
+      <c r="A79" s="256" t="s">
         <v>6</v>
       </c>
       <c r="B79" s="181" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C79" s="181" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D79" s="33">
         <v>860560</v>
       </c>
-      <c r="E79" s="339">
+      <c r="E79" s="250">
         <f>D79*93.2%</f>
         <v>802041.92</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="236">
         <f>$D79*1.08%</f>
         <v>9294.0480000000007</v>
       </c>
@@ -4800,15 +4800,15 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="324"/>
+      <c r="A80" s="237"/>
       <c r="B80" s="181"/>
       <c r="C80" s="181"/>
       <c r="D80" s="33"/>
-      <c r="E80" s="339">
+      <c r="E80" s="250">
         <f>D80*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="236">
         <f>$D80*1.08%</f>
         <v>0</v>
       </c>
@@ -4836,8 +4836,8 @@
       <c r="B81" s="181"/>
       <c r="C81" s="181"/>
       <c r="D81" s="182"/>
-      <c r="E81" s="348"/>
-      <c r="F81" s="348"/>
+      <c r="E81" s="257"/>
+      <c r="F81" s="257"/>
       <c r="G81" s="36"/>
       <c r="H81" s="36"/>
       <c r="I81" s="36"/>
@@ -4846,11 +4846,11 @@
       <c r="N81" s="32"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="325" t="s">
+      <c r="A82" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="B82" s="325"/>
-      <c r="C82" s="325"/>
+      <c r="B82" s="238"/>
+      <c r="C82" s="238"/>
       <c r="D82" s="31">
         <f>SUM(D79:D81)</f>
         <v>860560</v>
@@ -4899,11 +4899,11 @@
         <f>256650.95-853</f>
         <v>255797.95</v>
       </c>
-      <c r="E83" s="339">
+      <c r="E83" s="250">
         <f>D83*93.2%</f>
         <v>238403.68940000003</v>
       </c>
-      <c r="F83" s="323">
+      <c r="F83" s="236">
         <f>$D83*1.08%</f>
         <v>2762.6178600000003</v>
       </c>
@@ -4930,15 +4930,15 @@
         <v>27</v>
       </c>
       <c r="B84" s="181"/>
-      <c r="C84" s="349"/>
+      <c r="C84" s="258"/>
       <c r="D84" s="33">
         <v>69000</v>
       </c>
-      <c r="E84" s="339">
+      <c r="E84" s="250">
         <f>D84*93.2%</f>
         <v>64308</v>
       </c>
-      <c r="F84" s="323">
+      <c r="F84" s="236">
         <f>$D84*1.08%</f>
         <v>745.2</v>
       </c>
@@ -4961,11 +4961,11 @@
       <c r="L84" s="50"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="325" t="s">
+      <c r="A85" s="238" t="s">
         <v>225</v>
       </c>
-      <c r="B85" s="325"/>
-      <c r="C85" s="325"/>
+      <c r="B85" s="238"/>
+      <c r="C85" s="238"/>
       <c r="D85" s="52">
         <f>SUM(D83:D84)</f>
         <v>324797.95</v>
@@ -5008,8 +5008,8 @@
       <c r="B86" s="73"/>
       <c r="C86" s="73"/>
       <c r="D86" s="73"/>
-      <c r="E86" s="350"/>
-      <c r="F86" s="350"/>
+      <c r="E86" s="259"/>
+      <c r="F86" s="259"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
@@ -5017,17 +5017,17 @@
       <c r="L86" s="50"/>
     </row>
     <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="351" t="s">
+      <c r="A87" s="260" t="s">
         <v>293</v>
       </c>
-      <c r="B87" s="352"/>
-      <c r="C87" s="352"/>
+      <c r="B87" s="261"/>
+      <c r="C87" s="261"/>
       <c r="D87" s="74"/>
-      <c r="E87" s="353">
+      <c r="E87" s="262">
         <f>D87*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F87" s="353">
+      <c r="F87" s="262">
         <f>$D87*1.08%</f>
         <v>0</v>
       </c>
@@ -5057,9 +5057,9 @@
       </c>
     </row>
     <row r="88" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="354"/>
-      <c r="B88" s="355"/>
-      <c r="C88" s="355"/>
+      <c r="A88" s="263"/>
+      <c r="B88" s="264"/>
+      <c r="C88" s="264"/>
       <c r="D88" s="75"/>
       <c r="E88" s="75"/>
       <c r="F88" s="75"/>
@@ -5071,11 +5071,11 @@
       <c r="L88" s="50"/>
     </row>
     <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="356" t="s">
+      <c r="A89" s="265" t="s">
         <v>28</v>
       </c>
-      <c r="B89" s="357"/>
-      <c r="C89" s="358"/>
+      <c r="B89" s="266"/>
+      <c r="C89" s="267"/>
       <c r="D89" s="66">
         <f t="shared" ref="D89:J89" si="18">SUM(D87+D42+D36+D85+D82+D75+D61+D51+D27++D47)</f>
         <v>15847087.939999999</v>
@@ -5122,70 +5122,70 @@
       <c r="B90" s="65"/>
       <c r="C90" s="65"/>
       <c r="D90" s="65"/>
-      <c r="E90" s="359"/>
-      <c r="F90" s="359"/>
+      <c r="E90" s="268"/>
+      <c r="F90" s="268"/>
       <c r="G90" s="32"/>
       <c r="H90" s="32"/>
       <c r="I90" s="32"/>
     </row>
     <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="360" t="s">
+      <c r="A91" s="269" t="s">
         <v>36</v>
       </c>
-      <c r="B91" s="361"/>
-      <c r="C91" s="361"/>
+      <c r="B91" s="270"/>
+      <c r="C91" s="270"/>
       <c r="D91" s="65"/>
-      <c r="E91" s="359"/>
-      <c r="F91" s="359"/>
+      <c r="E91" s="268"/>
+      <c r="F91" s="268"/>
       <c r="G91" s="32"/>
       <c r="H91" s="32"/>
       <c r="I91" s="32"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="362"/>
+      <c r="A92" s="271"/>
       <c r="B92" s="65"/>
       <c r="C92" s="210"/>
       <c r="D92" s="65"/>
-      <c r="E92" s="359"/>
-      <c r="F92" s="359"/>
+      <c r="E92" s="268"/>
+      <c r="F92" s="268"/>
       <c r="G92" s="32"/>
       <c r="H92" s="32"/>
       <c r="I92" s="32"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="362"/>
+      <c r="A93" s="271"/>
       <c r="B93" s="65"/>
       <c r="C93" s="210"/>
       <c r="D93" s="65"/>
-      <c r="E93" s="359"/>
-      <c r="F93" s="359"/>
+      <c r="E93" s="268"/>
+      <c r="F93" s="268"/>
       <c r="G93" s="32"/>
       <c r="H93" s="32"/>
       <c r="I93" s="32"/>
     </row>
     <row r="94" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="362"/>
+      <c r="A94" s="271"/>
       <c r="B94" s="65"/>
       <c r="C94" s="210"/>
       <c r="D94" s="65"/>
-      <c r="E94" s="359"/>
-      <c r="F94" s="359"/>
+      <c r="E94" s="268"/>
+      <c r="F94" s="268"/>
       <c r="G94" s="32"/>
       <c r="H94" s="32"/>
       <c r="I94" s="32"/>
     </row>
     <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="363" t="s">
+      <c r="A95" s="272" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="364"/>
-      <c r="C95" s="365">
+      <c r="B95" s="273"/>
+      <c r="C95" s="274">
         <f>SUM(C92:C94)</f>
         <v>0</v>
       </c>
       <c r="D95" s="65"/>
-      <c r="E95" s="359"/>
-      <c r="F95" s="359"/>
+      <c r="E95" s="268"/>
+      <c r="F95" s="268"/>
       <c r="G95" s="32"/>
       <c r="H95" s="32"/>
       <c r="I95" s="32"/>
@@ -5195,8 +5195,8 @@
       <c r="B96" s="65"/>
       <c r="C96" s="65"/>
       <c r="D96" s="65"/>
-      <c r="E96" s="359"/>
-      <c r="F96" s="359"/>
+      <c r="E96" s="268"/>
+      <c r="F96" s="268"/>
       <c r="G96" s="32"/>
       <c r="H96" s="32"/>
       <c r="I96" s="32"/>
@@ -5206,19 +5206,19 @@
       <c r="B97" s="65"/>
       <c r="C97" s="65"/>
       <c r="D97" s="65"/>
-      <c r="E97" s="366"/>
-      <c r="F97" s="366"/>
+      <c r="E97" s="275"/>
+      <c r="F97" s="275"/>
       <c r="G97" s="46"/>
       <c r="H97" s="46"/>
       <c r="I97" s="46"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="367" t="s">
+      <c r="A98" s="281" t="s">
         <v>32</v>
       </c>
-      <c r="B98" s="368"/>
-      <c r="C98" s="368"/>
-      <c r="D98" s="368"/>
+      <c r="B98" s="282"/>
+      <c r="C98" s="282"/>
+      <c r="D98" s="282"/>
       <c r="E98" s="60" t="s">
         <v>10</v>
       </c>
@@ -5239,23 +5239,23 @@
       </c>
     </row>
     <row r="99" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="340"/>
-      <c r="B99" s="369"/>
-      <c r="C99" s="370"/>
+      <c r="A99" s="285"/>
+      <c r="B99" s="286"/>
+      <c r="C99" s="276"/>
       <c r="D99" s="33"/>
-      <c r="E99" s="339">
+      <c r="E99" s="250">
         <f>D99</f>
         <v>0</v>
       </c>
-      <c r="F99" s="339"/>
+      <c r="F99" s="250"/>
       <c r="G99" s="49"/>
       <c r="H99" s="49"/>
       <c r="I99" s="49"/>
       <c r="J99" s="44"/>
     </row>
     <row r="100" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="233"/>
-      <c r="B100" s="237"/>
+      <c r="A100" s="283"/>
+      <c r="B100" s="284"/>
       <c r="C100" s="62"/>
       <c r="D100" s="33"/>
       <c r="E100" s="49"/>
@@ -5266,11 +5266,11 @@
       <c r="J100" s="44"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="234" t="s">
+      <c r="A101" s="278" t="s">
         <v>16</v>
       </c>
-      <c r="B101" s="235"/>
-      <c r="C101" s="236"/>
+      <c r="B101" s="279"/>
+      <c r="C101" s="280"/>
       <c r="D101" s="59">
         <f>SUM(D99:D100)</f>
         <v>0</v>
@@ -5320,30 +5320,30 @@
         <f>D89-D87</f>
         <v>15847087.939999999</v>
       </c>
-      <c r="D105" s="238" t="s">
+      <c r="D105" s="287" t="s">
         <v>284</v>
       </c>
-      <c r="E105" s="238"/>
-      <c r="F105" s="238"/>
-      <c r="G105" s="238"/>
-      <c r="H105" s="238"/>
-      <c r="I105" s="238"/>
+      <c r="E105" s="287"/>
+      <c r="F105" s="287"/>
+      <c r="G105" s="287"/>
+      <c r="H105" s="287"/>
+      <c r="I105" s="287"/>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D106" s="238"/>
-      <c r="E106" s="238"/>
-      <c r="F106" s="238"/>
-      <c r="G106" s="238"/>
-      <c r="H106" s="238"/>
-      <c r="I106" s="238"/>
+      <c r="D106" s="287"/>
+      <c r="E106" s="287"/>
+      <c r="F106" s="287"/>
+      <c r="G106" s="287"/>
+      <c r="H106" s="287"/>
+      <c r="I106" s="287"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D107" s="238"/>
-      <c r="E107" s="238"/>
-      <c r="F107" s="238"/>
-      <c r="G107" s="238"/>
-      <c r="H107" s="238"/>
-      <c r="I107" s="238"/>
+      <c r="D107" s="287"/>
+      <c r="E107" s="287"/>
+      <c r="F107" s="287"/>
+      <c r="G107" s="287"/>
+      <c r="H107" s="287"/>
+      <c r="I107" s="287"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="B108" s="9"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="238"/>
-      <c r="E108" s="238"/>
-      <c r="F108" s="238"/>
-      <c r="G108" s="238"/>
-      <c r="H108" s="238"/>
-      <c r="I108" s="238"/>
+      <c r="D108" s="287"/>
+      <c r="E108" s="287"/>
+      <c r="F108" s="287"/>
+      <c r="G108" s="287"/>
+      <c r="H108" s="287"/>
+      <c r="I108" s="287"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
@@ -5366,12 +5366,12 @@
         <v>4948144.8095401041</v>
       </c>
       <c r="C109" s="12"/>
-      <c r="D109" s="238"/>
-      <c r="E109" s="238"/>
-      <c r="F109" s="238"/>
-      <c r="G109" s="238"/>
-      <c r="H109" s="238"/>
-      <c r="I109" s="238"/>
+      <c r="D109" s="287"/>
+      <c r="E109" s="287"/>
+      <c r="F109" s="287"/>
+      <c r="G109" s="287"/>
+      <c r="H109" s="287"/>
+      <c r="I109" s="287"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
@@ -5384,12 +5384,12 @@
       <c r="C110" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D110" s="238"/>
-      <c r="E110" s="238"/>
-      <c r="F110" s="238"/>
-      <c r="G110" s="238"/>
-      <c r="H110" s="238"/>
-      <c r="I110" s="238"/>
+      <c r="D110" s="287"/>
+      <c r="E110" s="287"/>
+      <c r="F110" s="287"/>
+      <c r="G110" s="287"/>
+      <c r="H110" s="287"/>
+      <c r="I110" s="287"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
@@ -5400,12 +5400,12 @@
         <v>1031545.1199999999</v>
       </c>
       <c r="C111" s="12"/>
-      <c r="D111" s="238"/>
-      <c r="E111" s="238"/>
-      <c r="F111" s="238"/>
-      <c r="G111" s="238"/>
-      <c r="H111" s="238"/>
-      <c r="I111" s="238"/>
+      <c r="D111" s="287"/>
+      <c r="E111" s="287"/>
+      <c r="F111" s="287"/>
+      <c r="G111" s="287"/>
+      <c r="H111" s="287"/>
+      <c r="I111" s="287"/>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
@@ -5416,12 +5416,12 @@
         <v>-15847087.939999999</v>
       </c>
       <c r="C112" s="10"/>
-      <c r="D112" s="238"/>
-      <c r="E112" s="238"/>
-      <c r="F112" s="238"/>
-      <c r="G112" s="238"/>
-      <c r="H112" s="238"/>
-      <c r="I112" s="238"/>
+      <c r="D112" s="287"/>
+      <c r="E112" s="287"/>
+      <c r="F112" s="287"/>
+      <c r="G112" s="287"/>
+      <c r="H112" s="287"/>
+      <c r="I112" s="287"/>
       <c r="K112" s="33"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -5433,46 +5433,46 @@
         <v>0</v>
       </c>
       <c r="C113" s="10"/>
-      <c r="D113" s="238"/>
-      <c r="E113" s="238"/>
-      <c r="F113" s="238"/>
-      <c r="G113" s="238"/>
-      <c r="H113" s="238"/>
-      <c r="I113" s="238"/>
+      <c r="D113" s="287"/>
+      <c r="E113" s="287"/>
+      <c r="F113" s="287"/>
+      <c r="G113" s="287"/>
+      <c r="H113" s="287"/>
+      <c r="I113" s="287"/>
       <c r="K113" s="39"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B114" s="63">
         <f>-PRORRATEO!H57</f>
         <v>-640914.39</v>
       </c>
       <c r="C114" s="10"/>
-      <c r="D114" s="238"/>
-      <c r="E114" s="238"/>
-      <c r="F114" s="238"/>
-      <c r="G114" s="238"/>
-      <c r="H114" s="238"/>
-      <c r="I114" s="238"/>
+      <c r="D114" s="287"/>
+      <c r="E114" s="287"/>
+      <c r="F114" s="287"/>
+      <c r="G114" s="287"/>
+      <c r="H114" s="287"/>
+      <c r="I114" s="287"/>
       <c r="K114" s="39"/>
     </row>
     <row r="115" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="194" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B115" s="63">
         <f>-B131</f>
         <v>534732.1100000001</v>
       </c>
       <c r="C115" s="10"/>
-      <c r="D115" s="238"/>
-      <c r="E115" s="238"/>
-      <c r="F115" s="238"/>
-      <c r="G115" s="238"/>
-      <c r="H115" s="238"/>
-      <c r="I115" s="238"/>
+      <c r="D115" s="287"/>
+      <c r="E115" s="287"/>
+      <c r="F115" s="287"/>
+      <c r="G115" s="287"/>
+      <c r="H115" s="287"/>
+      <c r="I115" s="287"/>
       <c r="K115" s="39"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -5484,12 +5484,12 @@
         <v>0</v>
       </c>
       <c r="C116" s="10"/>
-      <c r="D116" s="238"/>
-      <c r="E116" s="238"/>
-      <c r="F116" s="238"/>
-      <c r="G116" s="238"/>
-      <c r="H116" s="238"/>
-      <c r="I116" s="238"/>
+      <c r="D116" s="287"/>
+      <c r="E116" s="287"/>
+      <c r="F116" s="287"/>
+      <c r="G116" s="287"/>
+      <c r="H116" s="287"/>
+      <c r="I116" s="287"/>
       <c r="K116" s="39"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -5501,27 +5501,27 @@
         <v>-60000</v>
       </c>
       <c r="C117" s="14"/>
-      <c r="D117" s="238"/>
-      <c r="E117" s="238"/>
-      <c r="F117" s="238"/>
-      <c r="G117" s="238"/>
-      <c r="H117" s="238"/>
-      <c r="I117" s="238"/>
+      <c r="D117" s="287"/>
+      <c r="E117" s="287"/>
+      <c r="F117" s="287"/>
+      <c r="G117" s="287"/>
+      <c r="H117" s="287"/>
+      <c r="I117" s="287"/>
     </row>
     <row r="118" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="194" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B118" s="63">
         <v>-39639</v>
       </c>
       <c r="C118" s="14"/>
-      <c r="D118" s="238"/>
-      <c r="E118" s="238"/>
-      <c r="F118" s="238"/>
-      <c r="G118" s="238"/>
-      <c r="H118" s="238"/>
-      <c r="I118" s="238"/>
+      <c r="D118" s="287"/>
+      <c r="E118" s="287"/>
+      <c r="F118" s="287"/>
+      <c r="G118" s="287"/>
+      <c r="H118" s="287"/>
+      <c r="I118" s="287"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
@@ -5532,42 +5532,42 @@
         <v>0</v>
       </c>
       <c r="C119" s="14"/>
-      <c r="D119" s="238"/>
-      <c r="E119" s="238"/>
-      <c r="F119" s="238"/>
-      <c r="G119" s="238"/>
-      <c r="H119" s="238"/>
-      <c r="I119" s="238"/>
+      <c r="D119" s="287"/>
+      <c r="E119" s="287"/>
+      <c r="F119" s="287"/>
+      <c r="G119" s="287"/>
+      <c r="H119" s="287"/>
+      <c r="I119" s="287"/>
     </row>
     <row r="120" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="228" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B120" s="63">
         <v>-81371</v>
       </c>
       <c r="C120" s="14"/>
-      <c r="D120" s="238"/>
-      <c r="E120" s="238"/>
-      <c r="F120" s="238"/>
-      <c r="G120" s="238"/>
-      <c r="H120" s="238"/>
-      <c r="I120" s="238"/>
+      <c r="D120" s="287"/>
+      <c r="E120" s="287"/>
+      <c r="F120" s="287"/>
+      <c r="G120" s="287"/>
+      <c r="H120" s="287"/>
+      <c r="I120" s="287"/>
     </row>
     <row r="121" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="194" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B121" s="63">
         <v>-10013539</v>
       </c>
       <c r="C121" s="14"/>
-      <c r="D121" s="238"/>
-      <c r="E121" s="238"/>
-      <c r="F121" s="238"/>
-      <c r="G121" s="238"/>
-      <c r="H121" s="238"/>
-      <c r="I121" s="238"/>
+      <c r="D121" s="287"/>
+      <c r="E121" s="287"/>
+      <c r="F121" s="287"/>
+      <c r="G121" s="287"/>
+      <c r="H121" s="287"/>
+      <c r="I121" s="287"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
@@ -5578,22 +5578,22 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C122" s="51"/>
-      <c r="D122" s="238"/>
-      <c r="E122" s="238"/>
-      <c r="F122" s="238"/>
-      <c r="G122" s="238"/>
-      <c r="H122" s="238"/>
-      <c r="I122" s="238"/>
+      <c r="D122" s="287"/>
+      <c r="E122" s="287"/>
+      <c r="F122" s="287"/>
+      <c r="G122" s="287"/>
+      <c r="H122" s="287"/>
+      <c r="I122" s="287"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="14"/>
       <c r="C123" s="10"/>
-      <c r="D123" s="238"/>
-      <c r="E123" s="238"/>
-      <c r="F123" s="238"/>
-      <c r="G123" s="238"/>
-      <c r="H123" s="238"/>
-      <c r="I123" s="238"/>
+      <c r="D123" s="287"/>
+      <c r="E123" s="287"/>
+      <c r="F123" s="287"/>
+      <c r="G123" s="287"/>
+      <c r="H123" s="287"/>
+      <c r="I123" s="287"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="10"/>
-      <c r="D124" s="238"/>
-      <c r="E124" s="238"/>
-      <c r="F124" s="238"/>
-      <c r="G124" s="238"/>
-      <c r="H124" s="238"/>
-      <c r="I124" s="238"/>
+      <c r="D124" s="287"/>
+      <c r="E124" s="287"/>
+      <c r="F124" s="287"/>
+      <c r="G124" s="287"/>
+      <c r="H124" s="287"/>
+      <c r="I124" s="287"/>
     </row>
     <row r="125" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="207"/>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B130" s="23">
         <f>-B114</f>
@@ -5658,8 +5658,8 @@
       <c r="D130" s="17"/>
     </row>
     <row r="131" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="305" t="s">
-        <v>423</v>
+      <c r="A131" s="229" t="s">
+        <v>422</v>
       </c>
       <c r="B131" s="63">
         <f>-(D30+D31+D32+D33+D34+D70)</f>
@@ -5711,15 +5711,15 @@
         <v>438840</v>
       </c>
       <c r="C137" s="16"/>
-      <c r="D137" s="308" t="s">
-        <v>425</v>
-      </c>
-      <c r="E137" s="309"/>
-      <c r="F137" s="309"/>
-      <c r="G137" s="309"/>
-      <c r="H137" s="309"/>
-      <c r="I137" s="309"/>
-      <c r="J137" s="310"/>
+      <c r="D137" s="288" t="s">
+        <v>424</v>
+      </c>
+      <c r="E137" s="289"/>
+      <c r="F137" s="289"/>
+      <c r="G137" s="289"/>
+      <c r="H137" s="289"/>
+      <c r="I137" s="289"/>
+      <c r="J137" s="290"/>
     </row>
     <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
@@ -5729,25 +5729,25 @@
         <v>60000</v>
       </c>
       <c r="C138" s="16"/>
-      <c r="D138" s="311"/>
-      <c r="E138" s="312"/>
-      <c r="F138" s="312"/>
-      <c r="G138" s="312"/>
-      <c r="H138" s="312"/>
-      <c r="I138" s="312"/>
-      <c r="J138" s="313"/>
+      <c r="D138" s="291"/>
+      <c r="E138" s="292"/>
+      <c r="F138" s="292"/>
+      <c r="G138" s="292"/>
+      <c r="H138" s="292"/>
+      <c r="I138" s="292"/>
+      <c r="J138" s="293"/>
     </row>
     <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="11"/>
       <c r="B139" s="63"/>
       <c r="C139" s="16"/>
-      <c r="D139" s="311"/>
-      <c r="E139" s="312"/>
-      <c r="F139" s="312"/>
-      <c r="G139" s="312"/>
-      <c r="H139" s="312"/>
-      <c r="I139" s="312"/>
-      <c r="J139" s="313"/>
+      <c r="D139" s="291"/>
+      <c r="E139" s="292"/>
+      <c r="F139" s="292"/>
+      <c r="G139" s="292"/>
+      <c r="H139" s="292"/>
+      <c r="I139" s="292"/>
+      <c r="J139" s="293"/>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="25" t="s">
@@ -5758,59 +5758,54 @@
         <v>498840</v>
       </c>
       <c r="C140" s="16"/>
-      <c r="D140" s="311"/>
-      <c r="E140" s="312"/>
-      <c r="F140" s="312"/>
-      <c r="G140" s="312"/>
-      <c r="H140" s="312"/>
-      <c r="I140" s="312"/>
-      <c r="J140" s="313"/>
+      <c r="D140" s="291"/>
+      <c r="E140" s="292"/>
+      <c r="F140" s="292"/>
+      <c r="G140" s="292"/>
+      <c r="H140" s="292"/>
+      <c r="I140" s="292"/>
+      <c r="J140" s="293"/>
     </row>
     <row r="141" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C141" s="17"/>
-      <c r="D141" s="311"/>
-      <c r="E141" s="312"/>
-      <c r="F141" s="312"/>
-      <c r="G141" s="312"/>
-      <c r="H141" s="312"/>
-      <c r="I141" s="312"/>
-      <c r="J141" s="313"/>
+      <c r="D141" s="291"/>
+      <c r="E141" s="292"/>
+      <c r="F141" s="292"/>
+      <c r="G141" s="292"/>
+      <c r="H141" s="292"/>
+      <c r="I141" s="292"/>
+      <c r="J141" s="293"/>
     </row>
     <row r="142" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="229" t="s">
+      <c r="A142" s="299" t="s">
         <v>367</v>
       </c>
-      <c r="B142" s="230">
+      <c r="B142" s="301">
         <f>B140+B122+B132</f>
         <v>1292035.369540107</v>
       </c>
       <c r="C142" s="10"/>
-      <c r="D142" s="311"/>
-      <c r="E142" s="312"/>
-      <c r="F142" s="312"/>
-      <c r="G142" s="312"/>
-      <c r="H142" s="312"/>
-      <c r="I142" s="312"/>
-      <c r="J142" s="313"/>
+      <c r="D142" s="291"/>
+      <c r="E142" s="292"/>
+      <c r="F142" s="292"/>
+      <c r="G142" s="292"/>
+      <c r="H142" s="292"/>
+      <c r="I142" s="292"/>
+      <c r="J142" s="293"/>
     </row>
     <row r="143" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="306"/>
-      <c r="B143" s="307"/>
-      <c r="D143" s="314"/>
-      <c r="E143" s="315"/>
-      <c r="F143" s="315"/>
-      <c r="G143" s="315"/>
-      <c r="H143" s="315"/>
-      <c r="I143" s="315"/>
-      <c r="J143" s="316"/>
+      <c r="A143" s="300"/>
+      <c r="B143" s="302"/>
+      <c r="D143" s="294"/>
+      <c r="E143" s="295"/>
+      <c r="F143" s="295"/>
+      <c r="G143" s="295"/>
+      <c r="H143" s="295"/>
+      <c r="I143" s="295"/>
+      <c r="J143" s="296"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="D105:I124"/>
     <mergeCell ref="D137:J143"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A142:A143"/>
@@ -5824,6 +5819,11 @@
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="D105:I124"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5858,13 +5858,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="269" t="s">
+      <c r="A1" s="340" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="270"/>
-      <c r="C1" s="270"/>
-      <c r="D1" s="270"/>
-      <c r="E1" s="270"/>
+      <c r="B1" s="341"/>
+      <c r="C1" s="341"/>
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
       <c r="F1" s="125" t="s">
         <v>276</v>
       </c>
@@ -5876,20 +5876,20 @@
       <c r="L1" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="244">
+      <c r="M1" s="318">
         <f>RESUMEN!D89-N3</f>
-        <v>10160573.239999998</v>
-      </c>
-      <c r="N1" s="245"/>
+        <v>15847087.939999999</v>
+      </c>
+      <c r="N1" s="319"/>
       <c r="O1" s="126"/>
       <c r="P1" s="45"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="271"/>
-      <c r="B2" s="272"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
+      <c r="A2" s="342"/>
+      <c r="B2" s="343"/>
+      <c r="C2" s="343"/>
+      <c r="D2" s="343"/>
+      <c r="E2" s="343"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5909,11 +5909,11 @@
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="271"/>
-      <c r="B3" s="272"/>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
+      <c r="A3" s="342"/>
+      <c r="B3" s="343"/>
+      <c r="C3" s="343"/>
+      <c r="D3" s="343"/>
+      <c r="E3" s="343"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5923,21 +5923,21 @@
       <c r="J3" s="128"/>
       <c r="K3" s="128"/>
       <c r="L3" s="155" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="183">
-        <v>5686514.7000000002</v>
+        <v>0</v>
       </c>
       <c r="O3" s="129"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="273"/>
-      <c r="B4" s="274"/>
-      <c r="C4" s="274"/>
-      <c r="D4" s="274"/>
-      <c r="E4" s="274"/>
+      <c r="A4" s="344"/>
+      <c r="B4" s="345"/>
+      <c r="C4" s="345"/>
+      <c r="D4" s="345"/>
+      <c r="E4" s="345"/>
       <c r="F4" s="130"/>
       <c r="G4" s="130"/>
       <c r="H4" s="130"/>
@@ -5953,95 +5953,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="254" t="s">
+      <c r="C5" s="325" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
-      <c r="M5" s="255"/>
-      <c r="N5" s="255"/>
-      <c r="O5" s="256"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="326"/>
+      <c r="F5" s="326"/>
+      <c r="G5" s="326"/>
+      <c r="H5" s="326"/>
+      <c r="I5" s="326"/>
+      <c r="J5" s="326"/>
+      <c r="K5" s="326"/>
+      <c r="L5" s="326"/>
+      <c r="M5" s="326"/>
+      <c r="N5" s="326"/>
+      <c r="O5" s="327"/>
       <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="257"/>
-      <c r="D6" s="258"/>
-      <c r="E6" s="258"/>
-      <c r="F6" s="258"/>
-      <c r="G6" s="258"/>
-      <c r="H6" s="258"/>
-      <c r="I6" s="258"/>
-      <c r="J6" s="258"/>
-      <c r="K6" s="258"/>
-      <c r="L6" s="258"/>
-      <c r="M6" s="258"/>
-      <c r="N6" s="258"/>
-      <c r="O6" s="259"/>
+      <c r="C6" s="328"/>
+      <c r="D6" s="329"/>
+      <c r="E6" s="329"/>
+      <c r="F6" s="329"/>
+      <c r="G6" s="329"/>
+      <c r="H6" s="329"/>
+      <c r="I6" s="329"/>
+      <c r="J6" s="329"/>
+      <c r="K6" s="329"/>
+      <c r="L6" s="329"/>
+      <c r="M6" s="329"/>
+      <c r="N6" s="329"/>
+      <c r="O6" s="330"/>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="257"/>
-      <c r="D7" s="258"/>
-      <c r="E7" s="258"/>
-      <c r="F7" s="258"/>
-      <c r="G7" s="258"/>
-      <c r="H7" s="258"/>
-      <c r="I7" s="258"/>
-      <c r="J7" s="258"/>
-      <c r="K7" s="258"/>
-      <c r="L7" s="258"/>
-      <c r="M7" s="258"/>
-      <c r="N7" s="258"/>
-      <c r="O7" s="259"/>
+      <c r="C7" s="328"/>
+      <c r="D7" s="329"/>
+      <c r="E7" s="329"/>
+      <c r="F7" s="329"/>
+      <c r="G7" s="329"/>
+      <c r="H7" s="329"/>
+      <c r="I7" s="329"/>
+      <c r="J7" s="329"/>
+      <c r="K7" s="329"/>
+      <c r="L7" s="329"/>
+      <c r="M7" s="329"/>
+      <c r="N7" s="329"/>
+      <c r="O7" s="330"/>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="260"/>
-      <c r="D8" s="261"/>
-      <c r="E8" s="261"/>
-      <c r="F8" s="261"/>
-      <c r="G8" s="261"/>
-      <c r="H8" s="261"/>
-      <c r="I8" s="261"/>
-      <c r="J8" s="261"/>
-      <c r="K8" s="261"/>
-      <c r="L8" s="261"/>
-      <c r="M8" s="261"/>
-      <c r="N8" s="261"/>
-      <c r="O8" s="262"/>
+      <c r="C8" s="331"/>
+      <c r="D8" s="332"/>
+      <c r="E8" s="332"/>
+      <c r="F8" s="332"/>
+      <c r="G8" s="332"/>
+      <c r="H8" s="332"/>
+      <c r="I8" s="332"/>
+      <c r="J8" s="332"/>
+      <c r="K8" s="332"/>
+      <c r="L8" s="332"/>
+      <c r="M8" s="332"/>
+      <c r="N8" s="332"/>
+      <c r="O8" s="333"/>
       <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="263" t="s">
+      <c r="C9" s="334" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="264"/>
-      <c r="E9" s="264"/>
-      <c r="F9" s="264"/>
-      <c r="G9" s="264"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="264"/>
-      <c r="J9" s="264"/>
-      <c r="K9" s="264"/>
-      <c r="L9" s="264"/>
-      <c r="M9" s="264"/>
-      <c r="N9" s="264"/>
-      <c r="O9" s="265"/>
+      <c r="D9" s="335"/>
+      <c r="E9" s="335"/>
+      <c r="F9" s="335"/>
+      <c r="G9" s="335"/>
+      <c r="H9" s="335"/>
+      <c r="I9" s="335"/>
+      <c r="J9" s="335"/>
+      <c r="K9" s="335"/>
+      <c r="L9" s="335"/>
+      <c r="M9" s="335"/>
+      <c r="N9" s="335"/>
+      <c r="O9" s="336"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -6053,19 +6053,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="266"/>
-      <c r="D10" s="267"/>
-      <c r="E10" s="267"/>
-      <c r="F10" s="267"/>
-      <c r="G10" s="267"/>
-      <c r="H10" s="267"/>
-      <c r="I10" s="267"/>
-      <c r="J10" s="267"/>
-      <c r="K10" s="267"/>
-      <c r="L10" s="267"/>
-      <c r="M10" s="267"/>
-      <c r="N10" s="267"/>
-      <c r="O10" s="268"/>
+      <c r="C10" s="337"/>
+      <c r="D10" s="338"/>
+      <c r="E10" s="338"/>
+      <c r="F10" s="338"/>
+      <c r="G10" s="338"/>
+      <c r="H10" s="338"/>
+      <c r="I10" s="338"/>
+      <c r="J10" s="338"/>
+      <c r="K10" s="338"/>
+      <c r="L10" s="338"/>
+      <c r="M10" s="338"/>
+      <c r="N10" s="338"/>
+      <c r="O10" s="339"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -6075,49 +6075,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="240" t="s">
+      <c r="A11" s="309" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="275" t="s">
+      <c r="B11" s="311" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="240" t="s">
+      <c r="C11" s="309" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="277" t="s">
+      <c r="D11" s="313" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="277" t="s">
+      <c r="E11" s="313" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="240" t="s">
+      <c r="F11" s="309" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="240" t="s">
+      <c r="G11" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="240" t="s">
+      <c r="H11" s="309" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="246" t="s">
+      <c r="I11" s="320" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="248" t="s">
+      <c r="J11" s="306" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="248" t="s">
-        <v>368</v>
-      </c>
-      <c r="L11" s="248" t="s">
+      <c r="K11" s="306" t="s">
+        <v>425</v>
+      </c>
+      <c r="L11" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="251" t="s">
+      <c r="M11" s="322" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="248" t="s">
+      <c r="N11" s="306" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="248" t="s">
+      <c r="O11" s="306" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -6129,21 +6129,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="241"/>
-      <c r="B12" s="276"/>
-      <c r="C12" s="241"/>
-      <c r="D12" s="278"/>
-      <c r="E12" s="278"/>
-      <c r="F12" s="241"/>
-      <c r="G12" s="241"/>
-      <c r="H12" s="241"/>
-      <c r="I12" s="247"/>
-      <c r="J12" s="249"/>
-      <c r="K12" s="249"/>
-      <c r="L12" s="249"/>
-      <c r="M12" s="252"/>
-      <c r="N12" s="249"/>
-      <c r="O12" s="249"/>
+      <c r="A12" s="310"/>
+      <c r="B12" s="312"/>
+      <c r="C12" s="310"/>
+      <c r="D12" s="314"/>
+      <c r="E12" s="314"/>
+      <c r="F12" s="310"/>
+      <c r="G12" s="310"/>
+      <c r="H12" s="310"/>
+      <c r="I12" s="321"/>
+      <c r="J12" s="307"/>
+      <c r="K12" s="307"/>
+      <c r="L12" s="307"/>
+      <c r="M12" s="323"/>
+      <c r="N12" s="307"/>
+      <c r="O12" s="307"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -6153,19 +6153,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="241"/>
-      <c r="B13" s="276"/>
-      <c r="C13" s="241"/>
-      <c r="D13" s="278"/>
-      <c r="E13" s="278"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="247"/>
-      <c r="J13" s="249"/>
-      <c r="K13" s="250"/>
-      <c r="L13" s="250"/>
-      <c r="M13" s="252"/>
+      <c r="A13" s="310"/>
+      <c r="B13" s="312"/>
+      <c r="C13" s="310"/>
+      <c r="D13" s="314"/>
+      <c r="E13" s="314"/>
+      <c r="F13" s="310"/>
+      <c r="G13" s="310"/>
+      <c r="H13" s="310"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="307"/>
+      <c r="K13" s="308"/>
+      <c r="L13" s="308"/>
+      <c r="M13" s="323"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 18/06</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K14" s="151">
         <f>N$3*F14</f>
-        <v>61414.358760000003</v>
+        <v>0</v>
       </c>
       <c r="L14" s="112">
         <v>206250.11834400002</v>
@@ -6224,17 +6224,17 @@
       </c>
       <c r="N14" s="113">
         <f>L14+J14+I14+M14+K14</f>
-        <v>329078.9542080001</v>
+        <v>267664.59544800007</v>
       </c>
       <c r="O14" s="114">
         <f>N14*6% + N14</f>
-        <v>348823.6914604801</v>
+        <v>283724.47117488005</v>
       </c>
       <c r="P14" s="85" t="s">
         <v>350</v>
       </c>
-      <c r="R14" s="239"/>
-      <c r="S14" s="239"/>
+      <c r="R14" s="315"/>
+      <c r="S14" s="315"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="K15" s="151">
         <f t="shared" ref="K15:K18" si="1">N$3*F15</f>
-        <v>73924.691099999996</v>
+        <v>0</v>
       </c>
       <c r="L15" s="112">
         <v>244444.58470400001</v>
@@ -6275,17 +6275,17 @@
       </c>
       <c r="N15" s="113">
         <f t="shared" ref="N15:N18" si="2">L15+J15+I15+M15+K15</f>
-        <v>283615.68027200003</v>
+        <v>209690.989172</v>
       </c>
       <c r="O15" s="114">
         <f t="shared" ref="O15:O18" si="3">N15*6% + N15</f>
-        <v>300632.62108832004</v>
+        <v>222272.44852231999</v>
       </c>
       <c r="P15" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="R15" s="239"/>
-      <c r="S15" s="239"/>
+      <c r="R15" s="315"/>
+      <c r="S15" s="315"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="K16" s="151">
         <f t="shared" si="1"/>
-        <v>68806.827869999994</v>
+        <v>0</v>
       </c>
       <c r="L16" s="112">
         <v>231076.52147800004</v>
@@ -6330,11 +6330,11 @@
       </c>
       <c r="N16" s="113">
         <f t="shared" si="2"/>
-        <v>299882.69869600004</v>
+        <v>231075.87082600006</v>
       </c>
       <c r="O16" s="114">
         <f t="shared" si="3"/>
-        <v>317875.66061776003</v>
+        <v>244940.42307556007</v>
       </c>
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="K17" s="151">
         <f t="shared" si="1"/>
-        <v>84729.069029999999</v>
+        <v>0</v>
       </c>
       <c r="L17" s="112">
         <v>284548.77438200003</v>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="N17" s="113">
         <f t="shared" si="2"/>
-        <v>369278.13870438008</v>
+        <v>284549.06967438007</v>
       </c>
       <c r="O17" s="114">
         <f t="shared" si="3"/>
-        <v>391434.82702664286</v>
+        <v>301622.01385484287</v>
       </c>
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="K18" s="120">
         <f t="shared" si="1"/>
-        <v>98945.355779999998</v>
+        <v>0</v>
       </c>
       <c r="L18" s="120">
         <v>332291.85733199993</v>
@@ -6429,11 +6429,11 @@
       </c>
       <c r="N18" s="113">
         <f t="shared" si="2"/>
-        <v>723798.72274599981</v>
+        <v>624853.36696599983</v>
       </c>
       <c r="O18" s="122">
         <f t="shared" si="3"/>
-        <v>767226.64611075982</v>
+        <v>662344.56898395985</v>
       </c>
       <c r="P18" s="85"/>
       <c r="S18" s="32"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K19" s="151">
         <f>N$3*F19</f>
-        <v>106906.47636</v>
+        <v>0</v>
       </c>
       <c r="L19" s="151">
         <f>N$2*F19</f>
@@ -6481,11 +6481,11 @@
       </c>
       <c r="N19" s="152">
         <f>ROUND((L19+J19+I19+K19+M19),0) + P19</f>
-        <v>388906.01</v>
+        <v>282000.01</v>
       </c>
       <c r="O19" s="152">
         <f>ROUND((N19*6% + N19 ),0) + P19</f>
-        <v>412240.01</v>
+        <v>298920.01</v>
       </c>
       <c r="P19" s="102">
         <v>0.01</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="K20" s="151">
         <f t="shared" ref="K20:K83" si="6">N$3*F20</f>
-        <v>47766.723480000001</v>
+        <v>0</v>
       </c>
       <c r="L20" s="112">
         <f t="shared" ref="L20:L50" si="7">N$2*F20</f>
@@ -6535,11 +6535,11 @@
       </c>
       <c r="N20" s="152">
         <f t="shared" ref="N20:N83" si="8">ROUND((L20+J20+I20+K20+M20),0) + P20</f>
-        <v>173767.02</v>
+        <v>126000.02</v>
       </c>
       <c r="O20" s="114">
         <f t="shared" ref="O20:O83" si="9">ROUND((N20*6% + N20 ),0) + P20</f>
-        <v>184193.02</v>
+        <v>133560.01999999999</v>
       </c>
       <c r="P20" s="102">
         <f>P19+0.01</f>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K21" s="151">
         <f t="shared" si="6"/>
-        <v>114298.94547000001</v>
+        <v>0</v>
       </c>
       <c r="L21" s="112">
         <f t="shared" si="7"/>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="N21" s="152">
         <f t="shared" si="8"/>
-        <v>415799.03</v>
+        <v>301500.03000000003</v>
       </c>
       <c r="O21" s="114">
         <f t="shared" si="9"/>
-        <v>440747.03</v>
+        <v>319590.03000000003</v>
       </c>
       <c r="P21" s="102">
         <f t="shared" ref="P21:P84" si="10">P20+0.01</f>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="K22" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L22" s="112">
         <f t="shared" si="7"/>
@@ -6646,11 +6646,11 @@
       </c>
       <c r="N22" s="152">
         <f t="shared" si="8"/>
-        <v>141000.04</v>
+        <v>87547.04</v>
       </c>
       <c r="O22" s="114">
         <f t="shared" si="9"/>
-        <v>149460.04</v>
+        <v>92800.04</v>
       </c>
       <c r="P22" s="102">
         <f t="shared" si="10"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="K23" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L23" s="112">
         <f t="shared" si="7"/>
@@ -6705,11 +6705,11 @@
       </c>
       <c r="N23" s="152">
         <f t="shared" si="8"/>
-        <v>179973.05</v>
+        <v>130500.05</v>
       </c>
       <c r="O23" s="114">
         <f t="shared" si="9"/>
-        <v>190771.05</v>
+        <v>138330.04999999999</v>
       </c>
       <c r="P23" s="102">
         <f t="shared" si="10"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="K24" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L24" s="112">
         <f t="shared" si="7"/>
@@ -6761,11 +6761,11 @@
       </c>
       <c r="N24" s="152">
         <f t="shared" si="8"/>
-        <v>128905.06</v>
+        <v>74883.06</v>
       </c>
       <c r="O24" s="114">
         <f t="shared" si="9"/>
-        <v>136639.06</v>
+        <v>79376.06</v>
       </c>
       <c r="P24" s="102">
         <f t="shared" si="10"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K25" s="151">
         <f t="shared" si="6"/>
-        <v>93827.49255000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="112">
         <f t="shared" si="7"/>
@@ -6817,11 +6817,11 @@
       </c>
       <c r="N25" s="152">
         <f t="shared" si="8"/>
-        <v>267500.07</v>
+        <v>173673.07</v>
       </c>
       <c r="O25" s="114">
         <f t="shared" si="9"/>
-        <v>283550.07</v>
+        <v>184093.07</v>
       </c>
       <c r="P25" s="102">
         <f t="shared" si="10"/>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="K26" s="151">
         <f t="shared" si="6"/>
-        <v>41511.557310000004</v>
+        <v>0</v>
       </c>
       <c r="L26" s="112">
         <f t="shared" si="7"/>
@@ -6871,11 +6871,11 @@
       </c>
       <c r="N26" s="152">
         <f t="shared" si="8"/>
-        <v>151012.07999999999</v>
+        <v>109500.08</v>
       </c>
       <c r="O26" s="114">
         <f t="shared" si="9"/>
-        <v>160073.07999999999</v>
+        <v>116070.08</v>
       </c>
       <c r="P26" s="102">
         <f t="shared" si="10"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="K27" s="151">
         <f t="shared" si="6"/>
-        <v>101219.96166</v>
+        <v>0</v>
       </c>
       <c r="L27" s="112">
         <f t="shared" si="7"/>
@@ -6927,11 +6927,11 @@
       </c>
       <c r="N27" s="152">
         <f t="shared" si="8"/>
-        <v>539815.09</v>
+        <v>438595.09</v>
       </c>
       <c r="O27" s="114">
         <f t="shared" si="9"/>
-        <v>572204.09</v>
+        <v>464911.09</v>
       </c>
       <c r="P27" s="102">
         <f t="shared" si="10"/>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="K28" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L28" s="112">
         <f t="shared" si="7"/>
@@ -6981,11 +6981,11 @@
       </c>
       <c r="N28" s="152">
         <f t="shared" si="8"/>
-        <v>194453.1</v>
+        <v>141000.1</v>
       </c>
       <c r="O28" s="114">
         <f t="shared" si="9"/>
-        <v>206120.1</v>
+        <v>149460.1</v>
       </c>
       <c r="P28" s="102">
         <f t="shared" si="10"/>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="K29" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L29" s="112">
         <f t="shared" si="7"/>
@@ -7035,11 +7035,11 @@
       </c>
       <c r="N29" s="152">
         <f t="shared" si="8"/>
-        <v>179973.11</v>
+        <v>130500.11</v>
       </c>
       <c r="O29" s="114">
         <f t="shared" si="9"/>
-        <v>190771.11</v>
+        <v>138330.10999999999</v>
       </c>
       <c r="P29" s="102">
         <f t="shared" si="10"/>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="K30" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L30" s="112">
         <f t="shared" si="7"/>
@@ -7086,11 +7086,11 @@
       </c>
       <c r="N30" s="152">
         <f t="shared" si="8"/>
-        <v>1468390.12</v>
+        <v>1414368.12</v>
       </c>
       <c r="O30" s="114">
         <f t="shared" si="9"/>
-        <v>1556494.12</v>
+        <v>1499230.12</v>
       </c>
       <c r="P30" s="102">
         <f t="shared" si="10"/>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="K31" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L31" s="112">
         <f t="shared" si="7"/>
@@ -7140,11 +7140,11 @@
       </c>
       <c r="N31" s="152">
         <f t="shared" si="8"/>
-        <v>339259.13</v>
+        <v>246000.13</v>
       </c>
       <c r="O31" s="114">
         <f t="shared" si="9"/>
-        <v>359615.13</v>
+        <v>260760.13</v>
       </c>
       <c r="P31" s="102">
         <f t="shared" si="10"/>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="K32" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L32" s="112">
         <f t="shared" si="7"/>
@@ -7196,11 +7196,11 @@
       </c>
       <c r="N32" s="152">
         <f t="shared" si="8"/>
-        <v>148943.14000000001</v>
+        <v>108000.14</v>
       </c>
       <c r="O32" s="114">
         <f t="shared" si="9"/>
-        <v>157880.14000000001</v>
+        <v>114480.14</v>
       </c>
       <c r="P32" s="102">
         <f t="shared" si="10"/>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="K33" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L33" s="112">
         <f t="shared" si="7"/>
@@ -7250,11 +7250,11 @@
       </c>
       <c r="N33" s="152">
         <f t="shared" si="8"/>
-        <v>294247.15000000002</v>
+        <v>195870.15</v>
       </c>
       <c r="O33" s="114">
         <f t="shared" si="9"/>
-        <v>311902.15000000002</v>
+        <v>207622.15</v>
       </c>
       <c r="P33" s="102">
         <f t="shared" si="10"/>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="K34" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L34" s="112">
         <f t="shared" si="7"/>
@@ -7304,11 +7304,11 @@
       </c>
       <c r="N34" s="152">
         <f t="shared" si="8"/>
-        <v>194453.16</v>
+        <v>141000.16</v>
       </c>
       <c r="O34" s="114">
         <f t="shared" si="9"/>
-        <v>206120.16</v>
+        <v>149460.16</v>
       </c>
       <c r="P34" s="102">
         <f t="shared" si="10"/>
@@ -7327,7 +7327,7 @@
         <v>56</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E35" s="104" t="s">
         <v>272</v>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="K35" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L35" s="112">
         <f t="shared" si="7"/>
@@ -7363,11 +7363,11 @@
       </c>
       <c r="N35" s="152">
         <f t="shared" si="8"/>
-        <v>229446.17</v>
+        <v>179973.17</v>
       </c>
       <c r="O35" s="114">
         <f t="shared" si="9"/>
-        <v>243213.17</v>
+        <v>190772.17</v>
       </c>
       <c r="P35" s="102">
         <f t="shared" si="10"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="K36" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L36" s="112">
         <f t="shared" si="7"/>
@@ -7414,11 +7414,11 @@
       </c>
       <c r="N36" s="152">
         <f t="shared" si="8"/>
-        <v>950639.18</v>
+        <v>896617.18</v>
       </c>
       <c r="O36" s="114">
         <f t="shared" si="9"/>
-        <v>1007678.18</v>
+        <v>950414.18</v>
       </c>
       <c r="P36" s="102">
         <f t="shared" si="10"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="K37" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L37" s="112">
         <f t="shared" si="7"/>
@@ -7470,11 +7470,11 @@
       </c>
       <c r="N37" s="152">
         <f t="shared" si="8"/>
-        <v>339259.19</v>
+        <v>246000.19</v>
       </c>
       <c r="O37" s="114">
         <f t="shared" si="9"/>
-        <v>359615.19</v>
+        <v>260760.19</v>
       </c>
       <c r="P37" s="102">
         <f t="shared" si="10"/>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="K38" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L38" s="112">
         <f t="shared" si="7"/>
@@ -7527,11 +7527,11 @@
       </c>
       <c r="N38" s="152">
         <f t="shared" si="8"/>
-        <v>148943.20000000001</v>
+        <v>108000.2</v>
       </c>
       <c r="O38" s="114">
         <f t="shared" si="9"/>
-        <v>157880.20000000001</v>
+        <v>114480.2</v>
       </c>
       <c r="P38" s="102">
         <f t="shared" si="10"/>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="K39" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L39" s="112">
         <f t="shared" si="7"/>
@@ -7581,11 +7581,11 @@
       </c>
       <c r="N39" s="152">
         <f t="shared" si="8"/>
-        <v>377877.21</v>
+        <v>279500.21000000002</v>
       </c>
       <c r="O39" s="114">
         <f t="shared" si="9"/>
-        <v>400550.21</v>
+        <v>296270.21000000002</v>
       </c>
       <c r="P39" s="138">
         <f t="shared" si="10"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="K40" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L40" s="112">
         <f t="shared" si="7"/>
@@ -7730,11 +7730,11 @@
       </c>
       <c r="N40" s="152">
         <f t="shared" si="8"/>
-        <v>1014267.22</v>
+        <v>960814.22</v>
       </c>
       <c r="O40" s="114">
         <f t="shared" si="9"/>
-        <v>1075123.22</v>
+        <v>1018463.22</v>
       </c>
       <c r="P40" s="138">
         <f t="shared" si="10"/>
@@ -7850,7 +7850,7 @@
         <v>62</v>
       </c>
       <c r="D41" s="78" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E41" s="104"/>
       <c r="F41" s="105">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="K41" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L41" s="112">
         <f t="shared" si="7"/>
@@ -7884,11 +7884,11 @@
       </c>
       <c r="N41" s="152">
         <f t="shared" si="8"/>
-        <v>179973.23</v>
+        <v>130500.23</v>
       </c>
       <c r="O41" s="114">
         <f t="shared" si="9"/>
-        <v>190772.23</v>
+        <v>138330.23000000001</v>
       </c>
       <c r="P41" s="138">
         <f t="shared" si="10"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="K42" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L42" s="112">
         <f t="shared" si="7"/>
@@ -8037,11 +8037,11 @@
       </c>
       <c r="N42" s="152">
         <f t="shared" si="8"/>
-        <v>695859.24</v>
+        <v>641837.24</v>
       </c>
       <c r="O42" s="114">
         <f t="shared" si="9"/>
-        <v>737611.24</v>
+        <v>680347.24</v>
       </c>
       <c r="P42" s="138">
         <f t="shared" si="10"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="K43" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L43" s="112">
         <f t="shared" si="7"/>
@@ -8189,11 +8189,11 @@
       </c>
       <c r="N43" s="152">
         <f t="shared" si="8"/>
-        <v>339259.25</v>
+        <v>246000.25</v>
       </c>
       <c r="O43" s="114">
         <f t="shared" si="9"/>
-        <v>359615.25</v>
+        <v>260760.25</v>
       </c>
       <c r="P43" s="102">
         <f t="shared" si="10"/>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="K44" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L44" s="112">
         <f t="shared" si="7"/>
@@ -8245,11 +8245,11 @@
       </c>
       <c r="N44" s="152">
         <f t="shared" si="8"/>
-        <v>148943.26</v>
+        <v>108000.26</v>
       </c>
       <c r="O44" s="114">
         <f t="shared" si="9"/>
-        <v>157880.26</v>
+        <v>114480.26</v>
       </c>
       <c r="P44" s="102">
         <f t="shared" si="10"/>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="K45" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L45" s="112">
         <f t="shared" si="7"/>
@@ -8299,11 +8299,11 @@
       </c>
       <c r="N45" s="152">
         <f t="shared" si="8"/>
-        <v>357877.27</v>
+        <v>259500.27</v>
       </c>
       <c r="O45" s="114">
         <f t="shared" si="9"/>
-        <v>379350.27</v>
+        <v>275070.27</v>
       </c>
       <c r="P45" s="102">
         <f t="shared" si="10"/>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="K46" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L46" s="112">
         <f t="shared" si="7"/>
@@ -8359,11 +8359,11 @@
       </c>
       <c r="N46" s="152">
         <f t="shared" si="8"/>
-        <v>194454.28</v>
+        <v>141000.28</v>
       </c>
       <c r="O46" s="114">
         <f t="shared" si="9"/>
-        <v>206122.28</v>
+        <v>149460.28</v>
       </c>
       <c r="P46" s="102">
         <f t="shared" si="10"/>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="K47" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L47" s="112">
         <f t="shared" si="7"/>
@@ -8415,11 +8415,11 @@
       </c>
       <c r="N47" s="152">
         <f t="shared" si="8"/>
-        <v>174189.29</v>
+        <v>124717.29</v>
       </c>
       <c r="O47" s="114">
         <f t="shared" si="9"/>
-        <v>184641.29</v>
+        <v>132200.29</v>
       </c>
       <c r="P47" s="102">
         <f t="shared" si="10"/>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="K48" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L48" s="112">
         <f t="shared" si="7"/>
@@ -8469,11 +8469,11 @@
       </c>
       <c r="N48" s="152">
         <f t="shared" si="8"/>
-        <v>196522.3</v>
+        <v>142500.29999999999</v>
       </c>
       <c r="O48" s="114">
         <f t="shared" si="9"/>
-        <v>208314.3</v>
+        <v>151050.29999999999</v>
       </c>
       <c r="P48" s="102">
         <f t="shared" si="10"/>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="K49" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L49" s="112">
         <f t="shared" si="7"/>
@@ -8523,11 +8523,11 @@
       </c>
       <c r="N49" s="152">
         <f t="shared" si="8"/>
-        <v>339259.31</v>
+        <v>246000.31</v>
       </c>
       <c r="O49" s="114">
         <f t="shared" si="9"/>
-        <v>359615.31</v>
+        <v>260760.31</v>
       </c>
       <c r="P49" s="102">
         <f t="shared" si="10"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="K50" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L50" s="112">
         <f t="shared" si="7"/>
@@ -8577,11 +8577,11 @@
       </c>
       <c r="N50" s="152">
         <f t="shared" si="8"/>
-        <v>148943.32</v>
+        <v>108000.32000000001</v>
       </c>
       <c r="O50" s="114">
         <f t="shared" si="9"/>
-        <v>157880.32000000001</v>
+        <v>114480.32000000001</v>
       </c>
       <c r="P50" s="102">
         <f t="shared" si="10"/>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="K51" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L51" s="112">
         <f t="shared" ref="L51:L82" si="16">N$2*F51</f>
@@ -8632,11 +8632,11 @@
       </c>
       <c r="N51" s="152">
         <f t="shared" si="8"/>
-        <v>357877.33</v>
+        <v>259500.33</v>
       </c>
       <c r="O51" s="114">
         <f t="shared" si="9"/>
-        <v>379350.33</v>
+        <v>275070.33</v>
       </c>
       <c r="P51" s="102">
         <f t="shared" si="10"/>
@@ -8656,7 +8656,7 @@
         <v>267</v>
       </c>
       <c r="E52" s="104" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F52" s="105">
         <v>9.4000000000000004E-3</v>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K52" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L52" s="112">
         <f t="shared" si="16"/>
@@ -8689,18 +8689,18 @@
       </c>
       <c r="N52" s="152">
         <f t="shared" si="8"/>
-        <v>247907.34</v>
+        <v>194453.34</v>
       </c>
       <c r="O52" s="114">
         <f t="shared" si="9"/>
-        <v>262782.34000000003</v>
+        <v>206121.34</v>
       </c>
       <c r="P52" s="102">
         <f t="shared" si="10"/>
         <v>0.34000000000000014</v>
       </c>
       <c r="Q52" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="K53" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L53" s="112">
         <f t="shared" si="16"/>
@@ -8746,11 +8746,11 @@
       </c>
       <c r="N53" s="152">
         <f t="shared" si="8"/>
-        <v>179973.35</v>
+        <v>130500.35</v>
       </c>
       <c r="O53" s="114">
         <f t="shared" si="9"/>
-        <v>190772.35</v>
+        <v>138330.35</v>
       </c>
       <c r="P53" s="102">
         <f t="shared" si="10"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="K54" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L54" s="112">
         <f t="shared" si="16"/>
@@ -8797,11 +8797,11 @@
       </c>
       <c r="N54" s="152">
         <f t="shared" si="8"/>
-        <v>501097.36</v>
+        <v>447075.36</v>
       </c>
       <c r="O54" s="114">
         <f t="shared" si="9"/>
-        <v>531163.36</v>
+        <v>473900.36</v>
       </c>
       <c r="P54" s="102">
         <f t="shared" si="10"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="K55" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L55" s="112">
         <f t="shared" si="16"/>
@@ -8851,11 +8851,11 @@
       </c>
       <c r="N55" s="152">
         <f t="shared" si="8"/>
-        <v>339259.37</v>
+        <v>246000.37</v>
       </c>
       <c r="O55" s="114">
         <f t="shared" si="9"/>
-        <v>359615.37</v>
+        <v>260760.37</v>
       </c>
       <c r="P55" s="102">
         <f t="shared" si="10"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="K56" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L56" s="112">
         <f t="shared" si="16"/>
@@ -8908,11 +8908,11 @@
       </c>
       <c r="N56" s="152">
         <f t="shared" si="8"/>
-        <v>148943.38</v>
+        <v>108000.38</v>
       </c>
       <c r="O56" s="114">
         <f t="shared" si="9"/>
-        <v>157880.38</v>
+        <v>114480.38</v>
       </c>
       <c r="P56" s="102">
         <f t="shared" si="10"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="K57" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L57" s="112">
         <f t="shared" si="16"/>
@@ -8961,11 +8961,11 @@
       </c>
       <c r="N57" s="152">
         <f t="shared" si="8"/>
-        <v>357877.39</v>
+        <v>259500.39</v>
       </c>
       <c r="O57" s="114">
         <f t="shared" si="9"/>
-        <v>379350.39</v>
+        <v>275070.39</v>
       </c>
       <c r="P57" s="102">
         <f t="shared" si="10"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="K58" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L58" s="112">
         <f t="shared" si="16"/>
@@ -9014,11 +9014,11 @@
       </c>
       <c r="N58" s="152">
         <f t="shared" si="8"/>
-        <v>400575.4</v>
+        <v>347121.4</v>
       </c>
       <c r="O58" s="114">
         <f t="shared" si="9"/>
-        <v>424610.4</v>
+        <v>367949.4</v>
       </c>
       <c r="P58" s="102">
         <f t="shared" si="10"/>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="K59" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L59" s="112">
         <f t="shared" si="16"/>
@@ -9068,11 +9068,11 @@
       </c>
       <c r="N59" s="152">
         <f t="shared" si="8"/>
-        <v>179973.41</v>
+        <v>130500.41</v>
       </c>
       <c r="O59" s="114">
         <f t="shared" si="9"/>
-        <v>190772.41</v>
+        <v>138330.41</v>
       </c>
       <c r="P59" s="102">
         <f t="shared" si="10"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="K60" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L60" s="112">
         <f t="shared" si="16"/>
@@ -9125,11 +9125,11 @@
       </c>
       <c r="N60" s="152">
         <f t="shared" si="8"/>
-        <v>196522.42</v>
+        <v>142500.42000000001</v>
       </c>
       <c r="O60" s="114">
         <f t="shared" si="9"/>
-        <v>208314.42</v>
+        <v>151050.42000000001</v>
       </c>
       <c r="P60" s="102">
         <f t="shared" si="10"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="K61" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L61" s="112">
         <f t="shared" si="16"/>
@@ -9182,11 +9182,11 @@
       </c>
       <c r="N61" s="152">
         <f t="shared" si="8"/>
-        <v>359259.43</v>
+        <v>266000.43</v>
       </c>
       <c r="O61" s="114">
         <f t="shared" si="9"/>
-        <v>380815.43</v>
+        <v>281960.43</v>
       </c>
       <c r="P61" s="102">
         <f t="shared" si="10"/>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="K62" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L62" s="112">
         <f t="shared" si="16"/>
@@ -9236,11 +9236,11 @@
       </c>
       <c r="N62" s="152">
         <f t="shared" si="8"/>
-        <v>148943.44</v>
+        <v>108000.44</v>
       </c>
       <c r="O62" s="114">
         <f t="shared" si="9"/>
-        <v>157880.44</v>
+        <v>114480.44</v>
       </c>
       <c r="P62" s="102">
         <f t="shared" si="10"/>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="K63" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L63" s="112">
         <f t="shared" si="16"/>
@@ -9289,11 +9289,11 @@
       </c>
       <c r="N63" s="152">
         <f t="shared" si="8"/>
-        <v>379350.45</v>
+        <v>280973.45</v>
       </c>
       <c r="O63" s="114">
         <f t="shared" si="9"/>
-        <v>402111.45</v>
+        <v>297832.45</v>
       </c>
       <c r="P63" s="102">
         <f t="shared" si="10"/>
@@ -9312,7 +9312,7 @@
         <v>197</v>
       </c>
       <c r="E64" s="104" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F64" s="105">
         <v>9.4000000000000004E-3</v>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="K64" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L64" s="112">
         <f t="shared" si="16"/>
@@ -9344,11 +9344,11 @@
       </c>
       <c r="N64" s="152">
         <f t="shared" si="8"/>
-        <v>216325.46</v>
+        <v>162871.46</v>
       </c>
       <c r="O64" s="114">
         <f t="shared" si="9"/>
-        <v>229305.46</v>
+        <v>172644.46</v>
       </c>
       <c r="P64" s="138">
         <f t="shared" si="10"/>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="K65" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L65" s="112">
         <f t="shared" si="16"/>
@@ -9398,11 +9398,11 @@
       </c>
       <c r="N65" s="152">
         <f t="shared" si="8"/>
-        <v>179973.47</v>
+        <v>130500.47</v>
       </c>
       <c r="O65" s="114">
         <f t="shared" si="9"/>
-        <v>190772.47</v>
+        <v>138330.47</v>
       </c>
       <c r="P65" s="138">
         <f t="shared" si="10"/>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="K66" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L66" s="112">
         <f t="shared" si="16"/>
@@ -9452,11 +9452,11 @@
       </c>
       <c r="N66" s="152">
         <f t="shared" si="8"/>
-        <v>250544.48</v>
+        <v>196522.48</v>
       </c>
       <c r="O66" s="114">
         <f t="shared" si="9"/>
-        <v>265577.48</v>
+        <v>208314.48</v>
       </c>
       <c r="P66" s="138">
         <f t="shared" si="10"/>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="K67" s="151">
         <f t="shared" si="6"/>
-        <v>93258.841080000013</v>
+        <v>0</v>
       </c>
       <c r="L67" s="112">
         <f t="shared" si="16"/>
@@ -9507,11 +9507,11 @@
       </c>
       <c r="N67" s="152">
         <f t="shared" si="8"/>
-        <v>339259.49</v>
+        <v>246000.49</v>
       </c>
       <c r="O67" s="114">
         <f t="shared" si="9"/>
-        <v>359615.49</v>
+        <v>260761.49</v>
       </c>
       <c r="P67" s="102">
         <f t="shared" si="10"/>
@@ -9528,7 +9528,7 @@
         <v>89</v>
       </c>
       <c r="D68" s="78" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E68" s="104"/>
       <c r="F68" s="105">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="K68" s="151">
         <f t="shared" si="6"/>
-        <v>40942.905839999999</v>
+        <v>0</v>
       </c>
       <c r="L68" s="112">
         <f t="shared" si="16"/>
@@ -9562,11 +9562,11 @@
       </c>
       <c r="N68" s="152">
         <f t="shared" si="8"/>
-        <v>67572.5</v>
+        <v>26629.5</v>
       </c>
       <c r="O68" s="114">
         <f t="shared" si="9"/>
-        <v>71627.5</v>
+        <v>28227.5</v>
       </c>
       <c r="P68" s="102">
         <f t="shared" si="10"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="K69" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L69" s="112">
         <f t="shared" si="16"/>
@@ -9616,11 +9616,11 @@
       </c>
       <c r="N69" s="152">
         <f t="shared" si="8"/>
-        <v>377877.51</v>
+        <v>279500.51</v>
       </c>
       <c r="O69" s="114">
         <f t="shared" si="9"/>
-        <v>400550.51</v>
+        <v>296271.51</v>
       </c>
       <c r="P69" s="102">
         <f t="shared" si="10"/>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="K70" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L70" s="112">
         <f t="shared" si="16"/>
@@ -9670,11 +9670,11 @@
       </c>
       <c r="N70" s="152">
         <f t="shared" si="8"/>
-        <v>176017.52</v>
+        <v>122564.52</v>
       </c>
       <c r="O70" s="114">
         <f t="shared" si="9"/>
-        <v>186579.52</v>
+        <v>129918.52</v>
       </c>
       <c r="P70" s="102">
         <f t="shared" si="10"/>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="K71" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L71" s="112">
         <f t="shared" si="16"/>
@@ -9724,11 +9724,11 @@
       </c>
       <c r="N71" s="152">
         <f t="shared" si="8"/>
-        <v>179973.53</v>
+        <v>130500.53</v>
       </c>
       <c r="O71" s="114">
         <f t="shared" si="9"/>
-        <v>190772.53</v>
+        <v>138331.53</v>
       </c>
       <c r="P71" s="102">
         <f t="shared" si="10"/>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="K72" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L72" s="112">
         <f t="shared" si="16"/>
@@ -9778,11 +9778,11 @@
       </c>
       <c r="N72" s="152">
         <f t="shared" si="8"/>
-        <v>498288.54</v>
+        <v>444267.54</v>
       </c>
       <c r="O72" s="114">
         <f t="shared" si="9"/>
-        <v>528186.54</v>
+        <v>470924.54</v>
       </c>
       <c r="P72" s="102">
         <f t="shared" si="10"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="K73" s="151">
         <f t="shared" si="6"/>
-        <v>133633.09544999999</v>
+        <v>0</v>
       </c>
       <c r="L73" s="112">
         <f t="shared" si="16"/>
@@ -9832,11 +9832,11 @@
       </c>
       <c r="N73" s="152">
         <f t="shared" si="8"/>
-        <v>486133.55</v>
+        <v>352500.55</v>
       </c>
       <c r="O73" s="114">
         <f t="shared" si="9"/>
-        <v>515302.55</v>
+        <v>373651.55</v>
       </c>
       <c r="P73" s="102">
         <f t="shared" si="10"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="K74" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L74" s="112">
         <f t="shared" si="16"/>
@@ -9886,11 +9886,11 @@
       </c>
       <c r="N74" s="152">
         <f t="shared" si="8"/>
-        <v>379350.56</v>
+        <v>280973.56</v>
       </c>
       <c r="O74" s="114">
         <f t="shared" si="9"/>
-        <v>402112.56</v>
+        <v>297832.56</v>
       </c>
       <c r="P74" s="102">
         <f t="shared" si="10"/>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="K75" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L75" s="112">
         <f t="shared" si="16"/>
@@ -9940,11 +9940,11 @@
       </c>
       <c r="N75" s="152">
         <f t="shared" si="8"/>
-        <v>194453.57</v>
+        <v>141000.57</v>
       </c>
       <c r="O75" s="114">
         <f t="shared" si="9"/>
-        <v>206121.57</v>
+        <v>149461.57</v>
       </c>
       <c r="P75" s="102">
         <f t="shared" si="10"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="K76" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L76" s="112">
         <f t="shared" si="16"/>
@@ -9993,11 +9993,11 @@
       </c>
       <c r="N76" s="152">
         <f t="shared" si="8"/>
-        <v>639972.57999999996</v>
+        <v>590500.57999999996</v>
       </c>
       <c r="O76" s="114">
         <f t="shared" si="9"/>
-        <v>678371.58</v>
+        <v>625931.57999999996</v>
       </c>
       <c r="P76" s="102">
         <f t="shared" si="10"/>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="K77" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L77" s="112">
         <f t="shared" si="16"/>
@@ -10046,11 +10046,11 @@
       </c>
       <c r="N77" s="152">
         <f t="shared" si="8"/>
-        <v>177890.59</v>
+        <v>123868.59</v>
       </c>
       <c r="O77" s="114">
         <f t="shared" si="9"/>
-        <v>188564.59</v>
+        <v>131301.59</v>
       </c>
       <c r="P77" s="102">
         <f t="shared" si="10"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="K78" s="151">
         <f t="shared" si="6"/>
-        <v>133633.09544999999</v>
+        <v>0</v>
       </c>
       <c r="L78" s="112">
         <f t="shared" si="16"/>
@@ -10100,11 +10100,11 @@
       </c>
       <c r="N78" s="152">
         <f t="shared" si="8"/>
-        <v>482612.6</v>
+        <v>348979.6</v>
       </c>
       <c r="O78" s="114">
         <f t="shared" si="9"/>
-        <v>511569.6</v>
+        <v>369918.6</v>
       </c>
       <c r="P78" s="102">
         <f t="shared" si="10"/>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="K79" s="151">
         <f t="shared" si="6"/>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L79" s="112">
         <f t="shared" si="16"/>
@@ -10154,11 +10154,11 @@
       </c>
       <c r="N79" s="152">
         <f t="shared" si="8"/>
-        <v>357877.61</v>
+        <v>259500.61</v>
       </c>
       <c r="O79" s="114">
         <f t="shared" si="9"/>
-        <v>379350.61</v>
+        <v>275071.61</v>
       </c>
       <c r="P79" s="102">
         <f t="shared" si="10"/>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="K80" s="151">
         <f t="shared" si="6"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L80" s="112">
         <f t="shared" si="16"/>
@@ -10205,11 +10205,11 @@
       </c>
       <c r="N80" s="152">
         <f t="shared" si="8"/>
-        <v>1108303.6200000001</v>
+        <v>1054850.6200000001</v>
       </c>
       <c r="O80" s="114">
         <f t="shared" si="9"/>
-        <v>1174802.6200000001</v>
+        <v>1118142.6200000001</v>
       </c>
       <c r="P80" s="102">
         <f t="shared" si="10"/>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="K81" s="151">
         <f t="shared" si="6"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L81" s="112">
         <f t="shared" si="16"/>
@@ -10261,11 +10261,11 @@
       </c>
       <c r="N81" s="152">
         <f t="shared" si="8"/>
-        <v>179973.63</v>
+        <v>130500.63</v>
       </c>
       <c r="O81" s="114">
         <f t="shared" si="9"/>
-        <v>190772.63</v>
+        <v>138331.63</v>
       </c>
       <c r="P81" s="102">
         <f t="shared" si="10"/>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="K82" s="151">
         <f t="shared" si="6"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L82" s="112">
         <f t="shared" si="16"/>
@@ -10315,11 +10315,11 @@
       </c>
       <c r="N82" s="152">
         <f t="shared" si="8"/>
-        <v>196522.64</v>
+        <v>142500.64000000001</v>
       </c>
       <c r="O82" s="114">
         <f t="shared" si="9"/>
-        <v>208314.64</v>
+        <v>151051.64000000001</v>
       </c>
       <c r="P82" s="102">
         <f t="shared" si="10"/>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="K83" s="151">
         <f t="shared" si="6"/>
-        <v>133633.09544999999</v>
+        <v>0</v>
       </c>
       <c r="L83" s="112">
         <f t="shared" ref="L83:L114" si="24">N$2*F83</f>
@@ -10372,11 +10372,11 @@
       </c>
       <c r="N83" s="152">
         <f t="shared" si="8"/>
-        <v>486133.65</v>
+        <v>352500.65</v>
       </c>
       <c r="O83" s="114">
         <f t="shared" si="9"/>
-        <v>515302.65</v>
+        <v>373651.65</v>
       </c>
       <c r="P83" s="102">
         <f t="shared" si="10"/>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="K84" s="151">
         <f t="shared" ref="K84:K131" si="25">N$3*F84</f>
-        <v>98376.704310000001</v>
+        <v>0</v>
       </c>
       <c r="L84" s="112">
         <f t="shared" si="24"/>
@@ -10426,11 +10426,11 @@
       </c>
       <c r="N84" s="152">
         <f t="shared" ref="N84:N131" si="26">ROUND((L84+J84+I84+K84+M84),0) + P84</f>
-        <v>357877.66</v>
+        <v>259500.66</v>
       </c>
       <c r="O84" s="114">
         <f t="shared" ref="O84:O131" si="27">ROUND((N84*6% + N84 ),0) + P84</f>
-        <v>379350.66</v>
+        <v>275071.65999999997</v>
       </c>
       <c r="P84" s="102">
         <f t="shared" si="10"/>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="K85" s="151">
         <f t="shared" si="25"/>
-        <v>53453.23818</v>
+        <v>0</v>
       </c>
       <c r="L85" s="112">
         <f t="shared" si="24"/>
@@ -10480,11 +10480,11 @@
       </c>
       <c r="N85" s="152">
         <f t="shared" si="26"/>
-        <v>194453.67</v>
+        <v>141000.67000000001</v>
       </c>
       <c r="O85" s="114">
         <f t="shared" si="27"/>
-        <v>206121.67</v>
+        <v>149461.67000000001</v>
       </c>
       <c r="P85" s="102">
         <f t="shared" ref="P85:P131" si="28">P84+0.01</f>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="K86" s="151">
         <f t="shared" si="25"/>
-        <v>49472.677889999999</v>
+        <v>0</v>
       </c>
       <c r="L86" s="112">
         <f t="shared" si="24"/>
@@ -10534,11 +10534,11 @@
       </c>
       <c r="N86" s="152">
         <f t="shared" si="26"/>
-        <v>179973.68</v>
+        <v>130500.68</v>
       </c>
       <c r="O86" s="114">
         <f t="shared" si="27"/>
-        <v>190772.68</v>
+        <v>138331.68</v>
       </c>
       <c r="P86" s="102">
         <f t="shared" si="28"/>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="K87" s="151">
         <f t="shared" si="25"/>
-        <v>54021.889649999997</v>
+        <v>0</v>
       </c>
       <c r="L87" s="112">
         <f t="shared" si="24"/>
@@ -10588,11 +10588,11 @@
       </c>
       <c r="N87" s="152">
         <f t="shared" si="26"/>
-        <v>196522.69</v>
+        <v>142500.69</v>
       </c>
       <c r="O87" s="114">
         <f t="shared" si="27"/>
-        <v>208314.69</v>
+        <v>151051.69</v>
       </c>
       <c r="P87" s="102">
         <f t="shared" si="28"/>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="K88" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L88" s="112">
         <f t="shared" si="24"/>
@@ -10640,11 +10640,11 @@
       </c>
       <c r="N88" s="152">
         <f t="shared" si="26"/>
-        <v>47579.7</v>
+        <v>34500.699999999997</v>
       </c>
       <c r="O88" s="114">
         <f t="shared" si="27"/>
-        <v>50434.7</v>
+        <v>36571.699999999997</v>
       </c>
       <c r="P88" s="102">
         <f t="shared" si="28"/>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="K89" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L89" s="112">
         <f t="shared" si="24"/>
@@ -10692,11 +10692,11 @@
       </c>
       <c r="N89" s="152">
         <f t="shared" si="26"/>
-        <v>47579.71</v>
+        <v>34500.71</v>
       </c>
       <c r="O89" s="114">
         <f t="shared" si="27"/>
-        <v>50434.71</v>
+        <v>36571.71</v>
       </c>
       <c r="P89" s="102">
         <f t="shared" si="28"/>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="K90" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L90" s="112">
         <f t="shared" si="24"/>
@@ -10744,11 +10744,11 @@
       </c>
       <c r="N90" s="152">
         <f t="shared" si="26"/>
-        <v>47579.72</v>
+        <v>34500.720000000001</v>
       </c>
       <c r="O90" s="114">
         <f t="shared" si="27"/>
-        <v>50435.72</v>
+        <v>36571.72</v>
       </c>
       <c r="P90" s="102">
         <f t="shared" si="28"/>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="K91" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L91" s="112">
         <f t="shared" si="24"/>
@@ -10796,11 +10796,11 @@
       </c>
       <c r="N91" s="152">
         <f t="shared" si="26"/>
-        <v>47579.73</v>
+        <v>34500.730000000003</v>
       </c>
       <c r="O91" s="114">
         <f t="shared" si="27"/>
-        <v>50435.73</v>
+        <v>36571.730000000003</v>
       </c>
       <c r="P91" s="102">
         <f t="shared" si="28"/>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="K92" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L92" s="145">
         <f t="shared" si="24"/>
@@ -10848,11 +10848,11 @@
       </c>
       <c r="N92" s="152">
         <f t="shared" si="26"/>
-        <v>47579.74</v>
+        <v>34500.74</v>
       </c>
       <c r="O92" s="146">
         <f t="shared" si="27"/>
-        <v>50435.74</v>
+        <v>36571.74</v>
       </c>
       <c r="P92" s="102">
         <f t="shared" si="28"/>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="K93" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L93" s="112">
         <f t="shared" si="24"/>
@@ -10900,11 +10900,11 @@
       </c>
       <c r="N93" s="152">
         <f t="shared" si="26"/>
-        <v>120639.75</v>
+        <v>107560.75</v>
       </c>
       <c r="O93" s="114">
         <f t="shared" si="27"/>
-        <v>127878.75</v>
+        <v>114014.75</v>
       </c>
       <c r="P93" s="102">
         <f t="shared" si="28"/>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="K94" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L94" s="112">
         <f t="shared" si="24"/>
@@ -10952,11 +10952,11 @@
       </c>
       <c r="N94" s="152">
         <f t="shared" si="26"/>
-        <v>47579.76</v>
+        <v>34500.76</v>
       </c>
       <c r="O94" s="114">
         <f t="shared" si="27"/>
-        <v>50435.76</v>
+        <v>36571.760000000002</v>
       </c>
       <c r="P94" s="102">
         <f t="shared" si="28"/>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K95" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L95" s="112">
         <f t="shared" si="24"/>
@@ -11004,11 +11004,11 @@
       </c>
       <c r="N95" s="152">
         <f t="shared" si="26"/>
-        <v>47579.77</v>
+        <v>34500.769999999997</v>
       </c>
       <c r="O95" s="114">
         <f t="shared" si="27"/>
-        <v>50435.77</v>
+        <v>36571.769999999997</v>
       </c>
       <c r="P95" s="102">
         <f t="shared" si="28"/>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="K96" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L96" s="112">
         <f t="shared" si="24"/>
@@ -11056,11 +11056,11 @@
       </c>
       <c r="N96" s="152">
         <f t="shared" si="26"/>
-        <v>47579.78</v>
+        <v>34500.78</v>
       </c>
       <c r="O96" s="114">
         <f t="shared" si="27"/>
-        <v>50435.78</v>
+        <v>36571.78</v>
       </c>
       <c r="P96" s="102">
         <f t="shared" si="28"/>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="K97" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L97" s="112">
         <f t="shared" si="24"/>
@@ -11105,11 +11105,11 @@
       </c>
       <c r="N97" s="152">
         <f t="shared" si="26"/>
-        <v>371942.79</v>
+        <v>358863.79</v>
       </c>
       <c r="O97" s="114">
         <f t="shared" si="27"/>
-        <v>394259.79</v>
+        <v>380396.79</v>
       </c>
       <c r="P97" s="102">
         <f t="shared" si="28"/>
@@ -11146,7 +11146,7 @@
       </c>
       <c r="K98" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L98" s="112">
         <f t="shared" si="24"/>
@@ -11157,11 +11157,11 @@
       </c>
       <c r="N98" s="152">
         <f t="shared" si="26"/>
-        <v>47579.8</v>
+        <v>34500.800000000003</v>
       </c>
       <c r="O98" s="114">
         <f t="shared" si="27"/>
-        <v>50435.8</v>
+        <v>36571.800000000003</v>
       </c>
       <c r="P98" s="102">
         <f t="shared" si="28"/>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="K99" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L99" s="18">
         <f t="shared" si="24"/>
@@ -11209,11 +11209,11 @@
       </c>
       <c r="N99" s="152">
         <f t="shared" si="26"/>
-        <v>47579.81</v>
+        <v>34500.81</v>
       </c>
       <c r="O99" s="5">
         <f t="shared" si="27"/>
-        <v>50435.81</v>
+        <v>36571.81</v>
       </c>
       <c r="P99" s="102">
         <f t="shared" si="28"/>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="K100" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L100" s="18">
         <f t="shared" si="24"/>
@@ -11261,11 +11261,11 @@
       </c>
       <c r="N100" s="152">
         <f t="shared" si="26"/>
-        <v>47579.82</v>
+        <v>34500.82</v>
       </c>
       <c r="O100" s="5">
         <f t="shared" si="27"/>
-        <v>50435.82</v>
+        <v>36571.82</v>
       </c>
       <c r="P100" s="102">
         <f t="shared" si="28"/>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="K101" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L101" s="112">
         <f t="shared" si="24"/>
@@ -11310,11 +11310,11 @@
       </c>
       <c r="N101" s="152">
         <f t="shared" si="26"/>
-        <v>122760.83</v>
+        <v>109681.83</v>
       </c>
       <c r="O101" s="114">
         <f t="shared" si="27"/>
-        <v>130126.83</v>
+        <v>116263.83</v>
       </c>
       <c r="P101" s="102">
         <f t="shared" si="28"/>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="K102" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L102" s="112">
         <f t="shared" si="24"/>
@@ -11362,11 +11362,11 @@
       </c>
       <c r="N102" s="152">
         <f t="shared" si="26"/>
-        <v>47579.839999999997</v>
+        <v>34500.839999999997</v>
       </c>
       <c r="O102" s="114">
         <f t="shared" si="27"/>
-        <v>50435.839999999997</v>
+        <v>36571.839999999997</v>
       </c>
       <c r="P102" s="102">
         <f t="shared" si="28"/>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="K103" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L103" s="112">
         <f t="shared" si="24"/>
@@ -11414,11 +11414,11 @@
       </c>
       <c r="N103" s="152">
         <f t="shared" si="26"/>
-        <v>47579.85</v>
+        <v>34500.85</v>
       </c>
       <c r="O103" s="114">
         <f t="shared" si="27"/>
-        <v>50435.85</v>
+        <v>36571.85</v>
       </c>
       <c r="P103" s="102">
         <f t="shared" si="28"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="K104" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L104" s="18">
         <f t="shared" si="24"/>
@@ -11463,11 +11463,11 @@
       </c>
       <c r="N104" s="152">
         <f t="shared" si="26"/>
-        <v>95159.86</v>
+        <v>82080.86</v>
       </c>
       <c r="O104" s="5">
         <f t="shared" si="27"/>
-        <v>100869.86</v>
+        <v>87006.86</v>
       </c>
       <c r="P104" s="102">
         <f t="shared" si="28"/>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="K105" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L105" s="18">
         <f t="shared" si="24"/>
@@ -11515,11 +11515,11 @@
       </c>
       <c r="N105" s="152">
         <f t="shared" si="26"/>
-        <v>47579.87</v>
+        <v>34500.870000000003</v>
       </c>
       <c r="O105" s="5">
         <f t="shared" si="27"/>
-        <v>50435.87</v>
+        <v>36571.870000000003</v>
       </c>
       <c r="P105" s="102">
         <f t="shared" si="28"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="K106" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L106" s="18">
         <f t="shared" si="24"/>
@@ -11566,11 +11566,11 @@
       </c>
       <c r="N106" s="152">
         <f t="shared" si="26"/>
-        <v>43067.88</v>
+        <v>29988.880000000001</v>
       </c>
       <c r="O106" s="5">
         <f t="shared" si="27"/>
-        <v>45652.88</v>
+        <v>31788.880000000001</v>
       </c>
       <c r="P106" s="102">
         <f t="shared" si="28"/>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="K107" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L107" s="18">
         <f t="shared" si="24"/>
@@ -11618,11 +11618,11 @@
       </c>
       <c r="N107" s="152">
         <f t="shared" si="26"/>
-        <v>60658.89</v>
+        <v>47579.89</v>
       </c>
       <c r="O107" s="5">
         <f t="shared" si="27"/>
-        <v>64298.89</v>
+        <v>50435.89</v>
       </c>
       <c r="P107" s="102">
         <f t="shared" si="28"/>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="K108" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L108" s="18">
         <f t="shared" si="24"/>
@@ -11670,11 +11670,11 @@
       </c>
       <c r="N108" s="152">
         <f t="shared" si="26"/>
-        <v>47579.9</v>
+        <v>34500.9</v>
       </c>
       <c r="O108" s="5">
         <f t="shared" si="27"/>
-        <v>50435.9</v>
+        <v>36571.9</v>
       </c>
       <c r="P108" s="102">
         <f t="shared" si="28"/>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="K109" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L109" s="18">
         <f t="shared" si="24"/>
@@ -11722,11 +11722,11 @@
       </c>
       <c r="N109" s="152">
         <f t="shared" si="26"/>
-        <v>47579.91</v>
+        <v>34500.910000000003</v>
       </c>
       <c r="O109" s="5">
         <f t="shared" si="27"/>
-        <v>50435.91</v>
+        <v>36571.910000000003</v>
       </c>
       <c r="P109" s="102">
         <f t="shared" si="28"/>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="K110" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L110" s="112">
         <f t="shared" si="24"/>
@@ -11773,11 +11773,11 @@
       </c>
       <c r="N110" s="152">
         <f t="shared" si="26"/>
-        <v>158089.92000000001</v>
+        <v>145010.92000000001</v>
       </c>
       <c r="O110" s="114">
         <f t="shared" si="27"/>
-        <v>167575.92000000001</v>
+        <v>153712.92000000001</v>
       </c>
       <c r="P110" s="102">
         <f t="shared" si="28"/>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="K111" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L111" s="112">
         <f t="shared" si="24"/>
@@ -11825,11 +11825,11 @@
       </c>
       <c r="N111" s="152">
         <f t="shared" si="26"/>
-        <v>47579.93</v>
+        <v>34500.93</v>
       </c>
       <c r="O111" s="114">
         <f t="shared" si="27"/>
-        <v>50435.93</v>
+        <v>36571.93</v>
       </c>
       <c r="P111" s="102">
         <f t="shared" si="28"/>
@@ -11866,7 +11866,7 @@
       </c>
       <c r="K112" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L112" s="112">
         <f t="shared" si="24"/>
@@ -11877,11 +11877,11 @@
       </c>
       <c r="N112" s="152">
         <f t="shared" si="26"/>
-        <v>47579.94</v>
+        <v>34500.94</v>
       </c>
       <c r="O112" s="114">
         <f t="shared" si="27"/>
-        <v>50435.94</v>
+        <v>36571.94</v>
       </c>
       <c r="P112" s="102">
         <f t="shared" si="28"/>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="K113" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L113" s="112">
         <f t="shared" si="24"/>
@@ -11929,11 +11929,11 @@
       </c>
       <c r="N113" s="152">
         <f t="shared" si="26"/>
-        <v>47579.95</v>
+        <v>34500.949999999997</v>
       </c>
       <c r="O113" s="114">
         <f t="shared" si="27"/>
-        <v>50435.95</v>
+        <v>36571.949999999997</v>
       </c>
       <c r="P113" s="102">
         <f t="shared" si="28"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="K114" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L114" s="112">
         <f t="shared" si="24"/>
@@ -11981,11 +11981,11 @@
       </c>
       <c r="N114" s="152">
         <f t="shared" si="26"/>
-        <v>47579.96</v>
+        <v>34500.959999999999</v>
       </c>
       <c r="O114" s="114">
         <f t="shared" si="27"/>
-        <v>50435.96</v>
+        <v>36571.96</v>
       </c>
       <c r="P114" s="102">
         <f t="shared" si="28"/>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="K115" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L115" s="112">
         <f t="shared" ref="L115:L131" si="36">N$2*F115</f>
@@ -12033,11 +12033,11 @@
       </c>
       <c r="N115" s="152">
         <f t="shared" si="26"/>
-        <v>47579.97</v>
+        <v>34500.97</v>
       </c>
       <c r="O115" s="114">
         <f t="shared" si="27"/>
-        <v>50435.97</v>
+        <v>36571.97</v>
       </c>
       <c r="P115" s="102">
         <f t="shared" si="28"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="K116" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L116" s="112">
         <f t="shared" si="36"/>
@@ -12087,11 +12087,11 @@
       </c>
       <c r="N116" s="152">
         <f t="shared" si="26"/>
-        <v>32384.98</v>
+        <v>19305.98</v>
       </c>
       <c r="O116" s="114">
         <f t="shared" si="27"/>
-        <v>34328.980000000003</v>
+        <v>20464.98</v>
       </c>
       <c r="P116" s="102">
         <f t="shared" si="28"/>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="K117" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L117" s="112">
         <f t="shared" si="36"/>
@@ -12141,11 +12141,11 @@
       </c>
       <c r="N117" s="152">
         <f t="shared" si="26"/>
-        <v>11650.99</v>
+        <v>-1428.01</v>
       </c>
       <c r="O117" s="114">
         <f t="shared" si="27"/>
-        <v>12350.99</v>
+        <v>-1513.01</v>
       </c>
       <c r="P117" s="102">
         <f t="shared" si="28"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="K118" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L118" s="112">
         <f t="shared" si="36"/>
@@ -12195,11 +12195,11 @@
       </c>
       <c r="N118" s="152">
         <f t="shared" si="26"/>
-        <v>47580</v>
+        <v>34501</v>
       </c>
       <c r="O118" s="114">
         <f t="shared" si="27"/>
-        <v>50436</v>
+        <v>36572</v>
       </c>
       <c r="P118" s="102">
         <f t="shared" si="28"/>
@@ -12239,7 +12239,7 @@
       </c>
       <c r="K119" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L119" s="112">
         <f t="shared" si="36"/>
@@ -12250,11 +12250,11 @@
       </c>
       <c r="N119" s="152">
         <f t="shared" si="26"/>
-        <v>47580.01</v>
+        <v>34501.01</v>
       </c>
       <c r="O119" s="114">
         <f t="shared" si="27"/>
-        <v>50436.01</v>
+        <v>36572.01</v>
       </c>
       <c r="P119" s="102">
         <f t="shared" si="28"/>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="K120" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L120" s="112">
         <f t="shared" si="36"/>
@@ -12302,11 +12302,11 @@
       </c>
       <c r="N120" s="152">
         <f t="shared" si="26"/>
-        <v>47580.02</v>
+        <v>34501.019999999997</v>
       </c>
       <c r="O120" s="114">
         <f t="shared" si="27"/>
-        <v>50436.02</v>
+        <v>36572.019999999997</v>
       </c>
       <c r="P120" s="102">
         <f t="shared" si="28"/>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="K121" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L121" s="112">
         <f t="shared" si="36"/>
@@ -12356,11 +12356,11 @@
       </c>
       <c r="N121" s="152">
         <f t="shared" si="26"/>
-        <v>69753.03</v>
+        <v>56674.03</v>
       </c>
       <c r="O121" s="114">
         <f t="shared" si="27"/>
-        <v>73939.03</v>
+        <v>60075.03</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="28"/>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="K122" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L122" s="112">
         <f t="shared" si="36"/>
@@ -12408,11 +12408,11 @@
       </c>
       <c r="N122" s="152">
         <f t="shared" si="26"/>
-        <v>47580.04</v>
+        <v>34501.040000000001</v>
       </c>
       <c r="O122" s="114">
         <f t="shared" si="27"/>
-        <v>50436.04</v>
+        <v>36572.04</v>
       </c>
       <c r="P122" s="102">
         <f t="shared" si="28"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="K123" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L123" s="112">
         <f t="shared" si="36"/>
@@ -12459,11 +12459,11 @@
       </c>
       <c r="N123" s="152">
         <f t="shared" si="26"/>
-        <v>47092.05</v>
+        <v>34013.050000000003</v>
       </c>
       <c r="O123" s="114">
         <f t="shared" si="27"/>
-        <v>49919.05</v>
+        <v>36055.050000000003</v>
       </c>
       <c r="P123" s="102">
         <f t="shared" si="28"/>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="K124" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L124" s="112">
         <f t="shared" si="36"/>
@@ -12511,11 +12511,11 @@
       </c>
       <c r="N124" s="152">
         <f t="shared" si="26"/>
-        <v>68096.06</v>
+        <v>55017.06</v>
       </c>
       <c r="O124" s="114">
         <f t="shared" si="27"/>
-        <v>72183.06</v>
+        <v>58319.06</v>
       </c>
       <c r="P124" s="102">
         <f t="shared" si="28"/>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="K125" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L125" s="112">
         <f t="shared" si="36"/>
@@ -12568,11 +12568,11 @@
       </c>
       <c r="N125" s="152">
         <f t="shared" si="26"/>
-        <v>70589.070000000007</v>
+        <v>57510.07</v>
       </c>
       <c r="O125" s="114">
         <f t="shared" si="27"/>
-        <v>74825.070000000007</v>
+        <v>60962.07</v>
       </c>
       <c r="P125" s="102">
         <f t="shared" si="28"/>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="K126" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L126" s="112">
         <f t="shared" si="36"/>
@@ -12620,11 +12620,11 @@
       </c>
       <c r="N126" s="152">
         <f t="shared" si="26"/>
-        <v>105683.08</v>
+        <v>92604.08</v>
       </c>
       <c r="O126" s="114">
         <f t="shared" si="27"/>
-        <v>112025.08</v>
+        <v>98161.08</v>
       </c>
       <c r="P126" s="102">
         <f t="shared" si="28"/>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="K127" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L127" s="112">
         <f t="shared" si="36"/>
@@ -12672,11 +12672,11 @@
       </c>
       <c r="N127" s="152">
         <f t="shared" si="26"/>
-        <v>47580.09</v>
+        <v>34501.089999999997</v>
       </c>
       <c r="O127" s="114">
         <f t="shared" si="27"/>
-        <v>50436.09</v>
+        <v>36572.089999999997</v>
       </c>
       <c r="P127" s="102">
         <f t="shared" si="28"/>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="K128" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L128" s="18">
         <f t="shared" si="36"/>
@@ -12723,11 +12723,11 @@
       </c>
       <c r="N128" s="152">
         <f t="shared" si="26"/>
-        <v>50436.1</v>
+        <v>37357.1</v>
       </c>
       <c r="O128" s="5">
         <f t="shared" si="27"/>
-        <v>53463.1</v>
+        <v>39600.1</v>
       </c>
       <c r="P128" s="102">
         <f t="shared" si="28"/>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="K129" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L129" s="18">
         <f t="shared" si="36"/>
@@ -12775,11 +12775,11 @@
       </c>
       <c r="N129" s="152">
         <f t="shared" si="26"/>
-        <v>47580.11</v>
+        <v>34501.11</v>
       </c>
       <c r="O129" s="5">
         <f t="shared" si="27"/>
-        <v>50436.11</v>
+        <v>36572.11</v>
       </c>
       <c r="P129" s="102">
         <f t="shared" si="28"/>
@@ -12817,7 +12817,7 @@
       </c>
       <c r="K130" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L130" s="18">
         <f t="shared" si="36"/>
@@ -12828,11 +12828,11 @@
       </c>
       <c r="N130" s="152">
         <f t="shared" si="26"/>
-        <v>50436.12</v>
+        <v>37357.120000000003</v>
       </c>
       <c r="O130" s="5">
         <f t="shared" si="27"/>
-        <v>53463.12</v>
+        <v>39600.120000000003</v>
       </c>
       <c r="P130" s="102">
         <f t="shared" si="28"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="K131" s="151">
         <f t="shared" si="25"/>
-        <v>13078.98381</v>
+        <v>0</v>
       </c>
       <c r="L131" s="18">
         <f t="shared" si="36"/>
@@ -12882,11 +12882,11 @@
       </c>
       <c r="N131" s="152">
         <f t="shared" si="26"/>
-        <v>47580.13</v>
+        <v>34501.129999999997</v>
       </c>
       <c r="O131" s="5">
         <f t="shared" si="27"/>
-        <v>50436.13</v>
+        <v>36572.129999999997</v>
       </c>
       <c r="P131" s="102">
         <f t="shared" si="28"/>
@@ -12946,49 +12946,49 @@
       </c>
       <c r="N133" s="21">
         <f>SUM(N14:N132)</f>
-        <v>27559886.60462638</v>
+        <v>21883599.302086379</v>
       </c>
       <c r="O133" s="20">
         <f>SUM(O14:O132)</f>
-        <v>29213551.856303964</v>
+        <v>23196679.335611559</v>
       </c>
       <c r="Q133" s="45"/>
     </row>
     <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L134" s="47">
         <f>L133-M1</f>
-        <v>5088038.6162400022</v>
+        <v>-598476.0837599989</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="243"/>
-      <c r="D135" s="243"/>
-      <c r="E135" s="243"/>
-      <c r="F135" s="243"/>
-      <c r="G135" s="243"/>
-      <c r="H135" s="243"/>
-      <c r="I135" s="243"/>
-      <c r="J135" s="243"/>
-      <c r="K135" s="243"/>
-      <c r="L135" s="243"/>
-      <c r="M135" s="243"/>
-      <c r="N135" s="243"/>
-      <c r="O135" s="243"/>
+      <c r="C135" s="317"/>
+      <c r="D135" s="317"/>
+      <c r="E135" s="317"/>
+      <c r="F135" s="317"/>
+      <c r="G135" s="317"/>
+      <c r="H135" s="317"/>
+      <c r="I135" s="317"/>
+      <c r="J135" s="317"/>
+      <c r="K135" s="317"/>
+      <c r="L135" s="317"/>
+      <c r="M135" s="317"/>
+      <c r="N135" s="317"/>
+      <c r="O135" s="317"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="243"/>
-      <c r="D136" s="243"/>
-      <c r="E136" s="243"/>
-      <c r="F136" s="243"/>
-      <c r="G136" s="243"/>
-      <c r="H136" s="243"/>
-      <c r="I136" s="243"/>
-      <c r="J136" s="243"/>
-      <c r="K136" s="243"/>
-      <c r="L136" s="243"/>
-      <c r="M136" s="243"/>
-      <c r="N136" s="243"/>
-      <c r="O136" s="243"/>
+      <c r="C136" s="317"/>
+      <c r="D136" s="317"/>
+      <c r="E136" s="317"/>
+      <c r="F136" s="317"/>
+      <c r="G136" s="317"/>
+      <c r="H136" s="317"/>
+      <c r="I136" s="317"/>
+      <c r="J136" s="317"/>
+      <c r="K136" s="317"/>
+      <c r="L136" s="317"/>
+      <c r="M136" s="317"/>
+      <c r="N136" s="317"/>
+      <c r="O136" s="317"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
@@ -13006,126 +13006,126 @@
       <c r="O137" s="57"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="253" t="s">
+      <c r="C138" s="324" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="253"/>
-      <c r="E138" s="253"/>
-      <c r="F138" s="253"/>
-      <c r="G138" s="253"/>
-      <c r="H138" s="253"/>
-      <c r="I138" s="253"/>
-      <c r="J138" s="253"/>
-      <c r="K138" s="253"/>
-      <c r="L138" s="253"/>
-      <c r="M138" s="253"/>
-      <c r="N138" s="253"/>
-      <c r="O138" s="253"/>
+      <c r="D138" s="324"/>
+      <c r="E138" s="324"/>
+      <c r="F138" s="324"/>
+      <c r="G138" s="324"/>
+      <c r="H138" s="324"/>
+      <c r="I138" s="324"/>
+      <c r="J138" s="324"/>
+      <c r="K138" s="324"/>
+      <c r="L138" s="324"/>
+      <c r="M138" s="324"/>
+      <c r="N138" s="324"/>
+      <c r="O138" s="324"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="253"/>
-      <c r="D139" s="253"/>
-      <c r="E139" s="253"/>
-      <c r="F139" s="253"/>
-      <c r="G139" s="253"/>
-      <c r="H139" s="253"/>
-      <c r="I139" s="253"/>
-      <c r="J139" s="253"/>
-      <c r="K139" s="253"/>
-      <c r="L139" s="253"/>
-      <c r="M139" s="253"/>
-      <c r="N139" s="253"/>
-      <c r="O139" s="253"/>
+      <c r="C139" s="324"/>
+      <c r="D139" s="324"/>
+      <c r="E139" s="324"/>
+      <c r="F139" s="324"/>
+      <c r="G139" s="324"/>
+      <c r="H139" s="324"/>
+      <c r="I139" s="324"/>
+      <c r="J139" s="324"/>
+      <c r="K139" s="324"/>
+      <c r="L139" s="324"/>
+      <c r="M139" s="324"/>
+      <c r="N139" s="324"/>
+      <c r="O139" s="324"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="253"/>
-      <c r="D140" s="253"/>
-      <c r="E140" s="253"/>
-      <c r="F140" s="253"/>
-      <c r="G140" s="253"/>
-      <c r="H140" s="253"/>
-      <c r="I140" s="253"/>
-      <c r="J140" s="253"/>
-      <c r="K140" s="253"/>
-      <c r="L140" s="253"/>
-      <c r="M140" s="253"/>
-      <c r="N140" s="253"/>
-      <c r="O140" s="253"/>
+      <c r="C140" s="324"/>
+      <c r="D140" s="324"/>
+      <c r="E140" s="324"/>
+      <c r="F140" s="324"/>
+      <c r="G140" s="324"/>
+      <c r="H140" s="324"/>
+      <c r="I140" s="324"/>
+      <c r="J140" s="324"/>
+      <c r="K140" s="324"/>
+      <c r="L140" s="324"/>
+      <c r="M140" s="324"/>
+      <c r="N140" s="324"/>
+      <c r="O140" s="324"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="253"/>
-      <c r="D141" s="253"/>
-      <c r="E141" s="253"/>
-      <c r="F141" s="253"/>
-      <c r="G141" s="253"/>
-      <c r="H141" s="253"/>
-      <c r="I141" s="253"/>
-      <c r="J141" s="253"/>
-      <c r="K141" s="253"/>
-      <c r="L141" s="253"/>
-      <c r="M141" s="253"/>
-      <c r="N141" s="253"/>
-      <c r="O141" s="253"/>
+      <c r="C141" s="324"/>
+      <c r="D141" s="324"/>
+      <c r="E141" s="324"/>
+      <c r="F141" s="324"/>
+      <c r="G141" s="324"/>
+      <c r="H141" s="324"/>
+      <c r="I141" s="324"/>
+      <c r="J141" s="324"/>
+      <c r="K141" s="324"/>
+      <c r="L141" s="324"/>
+      <c r="M141" s="324"/>
+      <c r="N141" s="324"/>
+      <c r="O141" s="324"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="253"/>
-      <c r="D142" s="253"/>
-      <c r="E142" s="253"/>
-      <c r="F142" s="253"/>
-      <c r="G142" s="253"/>
-      <c r="H142" s="253"/>
-      <c r="I142" s="253"/>
-      <c r="J142" s="253"/>
-      <c r="K142" s="253"/>
-      <c r="L142" s="253"/>
-      <c r="M142" s="253"/>
-      <c r="N142" s="253"/>
-      <c r="O142" s="253"/>
+      <c r="C142" s="324"/>
+      <c r="D142" s="324"/>
+      <c r="E142" s="324"/>
+      <c r="F142" s="324"/>
+      <c r="G142" s="324"/>
+      <c r="H142" s="324"/>
+      <c r="I142" s="324"/>
+      <c r="J142" s="324"/>
+      <c r="K142" s="324"/>
+      <c r="L142" s="324"/>
+      <c r="M142" s="324"/>
+      <c r="N142" s="324"/>
+      <c r="O142" s="324"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="253"/>
-      <c r="D143" s="253"/>
-      <c r="E143" s="253"/>
-      <c r="F143" s="253"/>
-      <c r="G143" s="253"/>
-      <c r="H143" s="253"/>
-      <c r="I143" s="253"/>
-      <c r="J143" s="253"/>
-      <c r="K143" s="253"/>
-      <c r="L143" s="253"/>
-      <c r="M143" s="253"/>
-      <c r="N143" s="253"/>
-      <c r="O143" s="253"/>
+      <c r="C143" s="324"/>
+      <c r="D143" s="324"/>
+      <c r="E143" s="324"/>
+      <c r="F143" s="324"/>
+      <c r="G143" s="324"/>
+      <c r="H143" s="324"/>
+      <c r="I143" s="324"/>
+      <c r="J143" s="324"/>
+      <c r="K143" s="324"/>
+      <c r="L143" s="324"/>
+      <c r="M143" s="324"/>
+      <c r="N143" s="324"/>
+      <c r="O143" s="324"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="253"/>
-      <c r="D144" s="253"/>
-      <c r="E144" s="253"/>
-      <c r="F144" s="253"/>
-      <c r="G144" s="253"/>
-      <c r="H144" s="253"/>
-      <c r="I144" s="253"/>
-      <c r="J144" s="253"/>
-      <c r="K144" s="253"/>
-      <c r="L144" s="253"/>
-      <c r="M144" s="253"/>
-      <c r="N144" s="253"/>
-      <c r="O144" s="253"/>
+      <c r="C144" s="324"/>
+      <c r="D144" s="324"/>
+      <c r="E144" s="324"/>
+      <c r="F144" s="324"/>
+      <c r="G144" s="324"/>
+      <c r="H144" s="324"/>
+      <c r="I144" s="324"/>
+      <c r="J144" s="324"/>
+      <c r="K144" s="324"/>
+      <c r="L144" s="324"/>
+      <c r="M144" s="324"/>
+      <c r="N144" s="324"/>
+      <c r="O144" s="324"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="253"/>
-      <c r="D145" s="253"/>
-      <c r="E145" s="253"/>
-      <c r="F145" s="253"/>
-      <c r="G145" s="253"/>
-      <c r="H145" s="253"/>
-      <c r="I145" s="253"/>
-      <c r="J145" s="253"/>
-      <c r="K145" s="253"/>
-      <c r="L145" s="253"/>
-      <c r="M145" s="253"/>
-      <c r="N145" s="253"/>
-      <c r="O145" s="253"/>
+      <c r="C145" s="324"/>
+      <c r="D145" s="324"/>
+      <c r="E145" s="324"/>
+      <c r="F145" s="324"/>
+      <c r="G145" s="324"/>
+      <c r="H145" s="324"/>
+      <c r="I145" s="324"/>
+      <c r="J145" s="324"/>
+      <c r="K145" s="324"/>
+      <c r="L145" s="324"/>
+      <c r="M145" s="324"/>
+      <c r="N145" s="324"/>
+      <c r="O145" s="324"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
@@ -13158,125 +13158,118 @@
       <c r="O147" s="57"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="242" t="s">
+      <c r="C148" s="316" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="242"/>
-      <c r="E148" s="242"/>
-      <c r="F148" s="242"/>
-      <c r="G148" s="242"/>
-      <c r="H148" s="242"/>
-      <c r="I148" s="242"/>
-      <c r="J148" s="242"/>
-      <c r="K148" s="242"/>
-      <c r="L148" s="242"/>
-      <c r="M148" s="242"/>
-      <c r="N148" s="242"/>
-      <c r="O148" s="242"/>
+      <c r="D148" s="316"/>
+      <c r="E148" s="316"/>
+      <c r="F148" s="316"/>
+      <c r="G148" s="316"/>
+      <c r="H148" s="316"/>
+      <c r="I148" s="316"/>
+      <c r="J148" s="316"/>
+      <c r="K148" s="316"/>
+      <c r="L148" s="316"/>
+      <c r="M148" s="316"/>
+      <c r="N148" s="316"/>
+      <c r="O148" s="316"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="242"/>
-      <c r="D149" s="242"/>
-      <c r="E149" s="242"/>
-      <c r="F149" s="242"/>
-      <c r="G149" s="242"/>
-      <c r="H149" s="242"/>
-      <c r="I149" s="242"/>
-      <c r="J149" s="242"/>
-      <c r="K149" s="242"/>
-      <c r="L149" s="242"/>
-      <c r="M149" s="242"/>
-      <c r="N149" s="242"/>
-      <c r="O149" s="242"/>
+      <c r="C149" s="316"/>
+      <c r="D149" s="316"/>
+      <c r="E149" s="316"/>
+      <c r="F149" s="316"/>
+      <c r="G149" s="316"/>
+      <c r="H149" s="316"/>
+      <c r="I149" s="316"/>
+      <c r="J149" s="316"/>
+      <c r="K149" s="316"/>
+      <c r="L149" s="316"/>
+      <c r="M149" s="316"/>
+      <c r="N149" s="316"/>
+      <c r="O149" s="316"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="242"/>
-      <c r="D150" s="242"/>
-      <c r="E150" s="242"/>
-      <c r="F150" s="242"/>
-      <c r="G150" s="242"/>
-      <c r="H150" s="242"/>
-      <c r="I150" s="242"/>
-      <c r="J150" s="242"/>
-      <c r="K150" s="242"/>
-      <c r="L150" s="242"/>
-      <c r="M150" s="242"/>
-      <c r="N150" s="242"/>
-      <c r="O150" s="242"/>
+      <c r="C150" s="316"/>
+      <c r="D150" s="316"/>
+      <c r="E150" s="316"/>
+      <c r="F150" s="316"/>
+      <c r="G150" s="316"/>
+      <c r="H150" s="316"/>
+      <c r="I150" s="316"/>
+      <c r="J150" s="316"/>
+      <c r="K150" s="316"/>
+      <c r="L150" s="316"/>
+      <c r="M150" s="316"/>
+      <c r="N150" s="316"/>
+      <c r="O150" s="316"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
-        <v>-5088038.6162400022</v>
+        <v>598476.0837599989</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="242"/>
-      <c r="D151" s="242"/>
-      <c r="E151" s="242"/>
-      <c r="F151" s="242"/>
-      <c r="G151" s="242"/>
-      <c r="H151" s="242"/>
-      <c r="I151" s="242"/>
-      <c r="J151" s="242"/>
-      <c r="K151" s="242"/>
-      <c r="L151" s="242"/>
-      <c r="M151" s="242"/>
-      <c r="N151" s="242"/>
-      <c r="O151" s="242"/>
+      <c r="C151" s="316"/>
+      <c r="D151" s="316"/>
+      <c r="E151" s="316"/>
+      <c r="F151" s="316"/>
+      <c r="G151" s="316"/>
+      <c r="H151" s="316"/>
+      <c r="I151" s="316"/>
+      <c r="J151" s="316"/>
+      <c r="K151" s="316"/>
+      <c r="L151" s="316"/>
+      <c r="M151" s="316"/>
+      <c r="N151" s="316"/>
+      <c r="O151" s="316"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="242"/>
-      <c r="D152" s="242"/>
-      <c r="E152" s="242"/>
-      <c r="F152" s="242"/>
-      <c r="G152" s="242"/>
-      <c r="H152" s="242"/>
-      <c r="I152" s="242"/>
-      <c r="J152" s="242"/>
-      <c r="K152" s="242"/>
-      <c r="L152" s="242"/>
-      <c r="M152" s="242"/>
-      <c r="N152" s="242"/>
-      <c r="O152" s="242"/>
+      <c r="C152" s="316"/>
+      <c r="D152" s="316"/>
+      <c r="E152" s="316"/>
+      <c r="F152" s="316"/>
+      <c r="G152" s="316"/>
+      <c r="H152" s="316"/>
+      <c r="I152" s="316"/>
+      <c r="J152" s="316"/>
+      <c r="K152" s="316"/>
+      <c r="L152" s="316"/>
+      <c r="M152" s="316"/>
+      <c r="N152" s="316"/>
+      <c r="O152" s="316"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="242"/>
-      <c r="D153" s="242"/>
-      <c r="E153" s="242"/>
-      <c r="F153" s="242"/>
-      <c r="G153" s="242"/>
-      <c r="H153" s="242"/>
-      <c r="I153" s="242"/>
-      <c r="J153" s="242"/>
-      <c r="K153" s="242"/>
-      <c r="L153" s="242"/>
-      <c r="M153" s="242"/>
-      <c r="N153" s="242"/>
-      <c r="O153" s="242"/>
+      <c r="C153" s="316"/>
+      <c r="D153" s="316"/>
+      <c r="E153" s="316"/>
+      <c r="F153" s="316"/>
+      <c r="G153" s="316"/>
+      <c r="H153" s="316"/>
+      <c r="I153" s="316"/>
+      <c r="J153" s="316"/>
+      <c r="K153" s="316"/>
+      <c r="L153" s="316"/>
+      <c r="M153" s="316"/>
+      <c r="N153" s="316"/>
+      <c r="O153" s="316"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="242"/>
-      <c r="D154" s="242"/>
-      <c r="E154" s="242"/>
-      <c r="F154" s="242"/>
-      <c r="G154" s="242"/>
-      <c r="H154" s="242"/>
-      <c r="I154" s="242"/>
-      <c r="J154" s="242"/>
-      <c r="K154" s="242"/>
-      <c r="L154" s="242"/>
-      <c r="M154" s="242"/>
-      <c r="N154" s="242"/>
-      <c r="O154" s="242"/>
+      <c r="C154" s="316"/>
+      <c r="D154" s="316"/>
+      <c r="E154" s="316"/>
+      <c r="F154" s="316"/>
+      <c r="G154" s="316"/>
+      <c r="H154" s="316"/>
+      <c r="I154" s="316"/>
+      <c r="J154" s="316"/>
+      <c r="K154" s="316"/>
+      <c r="L154" s="316"/>
+      <c r="M154" s="316"/>
+      <c r="N154" s="316"/>
+      <c r="O154" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13293,6 +13286,13 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13326,61 +13326,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="290" t="s">
+      <c r="A1" s="349" t="s">
         <v>305</v>
       </c>
-      <c r="B1" s="290"/>
-      <c r="C1" s="290"/>
-      <c r="D1" s="290"/>
-      <c r="E1" s="290"/>
-      <c r="F1" s="290"/>
-      <c r="G1" s="290"/>
-      <c r="H1" s="290"/>
-      <c r="I1" s="290"/>
-      <c r="J1" s="290"/>
-      <c r="K1" s="290"/>
-      <c r="L1" s="290"/>
-      <c r="M1" s="290"/>
-      <c r="N1" s="290"/>
-      <c r="O1" s="291"/>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
+      <c r="I1" s="349"/>
+      <c r="J1" s="349"/>
+      <c r="K1" s="349"/>
+      <c r="L1" s="349"/>
+      <c r="M1" s="349"/>
+      <c r="N1" s="349"/>
+      <c r="O1" s="350"/>
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="292"/>
-      <c r="B2" s="292"/>
-      <c r="C2" s="292"/>
-      <c r="D2" s="292"/>
-      <c r="E2" s="292"/>
-      <c r="F2" s="292"/>
-      <c r="G2" s="292"/>
-      <c r="H2" s="292"/>
-      <c r="I2" s="292"/>
-      <c r="J2" s="292"/>
-      <c r="K2" s="292"/>
-      <c r="L2" s="292"/>
-      <c r="M2" s="292"/>
-      <c r="N2" s="292"/>
-      <c r="O2" s="293"/>
+      <c r="A2" s="351"/>
+      <c r="B2" s="351"/>
+      <c r="C2" s="351"/>
+      <c r="D2" s="351"/>
+      <c r="E2" s="351"/>
+      <c r="F2" s="351"/>
+      <c r="G2" s="351"/>
+      <c r="H2" s="351"/>
+      <c r="I2" s="351"/>
+      <c r="J2" s="351"/>
+      <c r="K2" s="351"/>
+      <c r="L2" s="351"/>
+      <c r="M2" s="351"/>
+      <c r="N2" s="351"/>
+      <c r="O2" s="352"/>
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:27" s="190" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="287" t="s">
-        <v>370</v>
-      </c>
-      <c r="B3" s="288"/>
-      <c r="C3" s="288"/>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288"/>
-      <c r="G3" s="288"/>
-      <c r="H3" s="288"/>
-      <c r="I3" s="288"/>
-      <c r="J3" s="288"/>
-      <c r="K3" s="288"/>
-      <c r="L3" s="288"/>
-      <c r="M3" s="288"/>
-      <c r="N3" s="288"/>
-      <c r="O3" s="289"/>
+      <c r="A3" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="B3" s="347"/>
+      <c r="C3" s="347"/>
+      <c r="D3" s="347"/>
+      <c r="E3" s="347"/>
+      <c r="F3" s="347"/>
+      <c r="G3" s="347"/>
+      <c r="H3" s="347"/>
+      <c r="I3" s="347"/>
+      <c r="J3" s="347"/>
+      <c r="K3" s="347"/>
+      <c r="L3" s="347"/>
+      <c r="M3" s="347"/>
+      <c r="N3" s="347"/>
+      <c r="O3" s="348"/>
       <c r="P3" s="191"/>
       <c r="Q3" s="191"/>
       <c r="R3" s="191"/>
@@ -13395,85 +13395,85 @@
       <c r="AA3" s="191"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="240" t="s">
+      <c r="A4" s="309" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="240" t="s">
+      <c r="B4" s="309" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="240" t="s">
+      <c r="C4" s="309" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="240" t="s">
+      <c r="D4" s="309" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="248" t="s">
+      <c r="E4" s="306" t="s">
         <v>331</v>
       </c>
-      <c r="F4" s="248" t="s">
+      <c r="F4" s="306" t="s">
         <v>332</v>
       </c>
-      <c r="G4" s="248" t="s">
+      <c r="G4" s="306" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="248" t="s">
+      <c r="H4" s="306" t="s">
         <v>337</v>
       </c>
-      <c r="I4" s="248" t="s">
+      <c r="I4" s="306" t="s">
         <v>347</v>
       </c>
-      <c r="J4" s="279" t="s">
+      <c r="J4" s="353" t="s">
         <v>333</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="284" t="s">
+      <c r="L4" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="M4" s="248" t="s">
+      <c r="M4" s="306" t="s">
         <v>345</v>
       </c>
-      <c r="N4" s="248" t="s">
+      <c r="N4" s="306" t="s">
         <v>334</v>
       </c>
-      <c r="O4" s="248" t="s">
+      <c r="O4" s="306" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="241"/>
-      <c r="B5" s="241"/>
-      <c r="C5" s="241"/>
-      <c r="D5" s="241"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="280"/>
+      <c r="A5" s="310"/>
+      <c r="B5" s="310"/>
+      <c r="C5" s="310"/>
+      <c r="D5" s="310"/>
+      <c r="E5" s="307"/>
+      <c r="F5" s="307"/>
+      <c r="G5" s="307"/>
+      <c r="H5" s="307"/>
+      <c r="I5" s="307"/>
+      <c r="J5" s="354"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="285"/>
-      <c r="M5" s="249"/>
-      <c r="N5" s="249"/>
-      <c r="O5" s="249"/>
+      <c r="L5" s="359"/>
+      <c r="M5" s="307"/>
+      <c r="N5" s="307"/>
+      <c r="O5" s="307"/>
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="283"/>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="283"/>
-      <c r="E6" s="282"/>
-      <c r="F6" s="282"/>
-      <c r="G6" s="282"/>
-      <c r="H6" s="282"/>
-      <c r="I6" s="282"/>
-      <c r="J6" s="281"/>
+      <c r="A6" s="357"/>
+      <c r="B6" s="357"/>
+      <c r="C6" s="357"/>
+      <c r="D6" s="357"/>
+      <c r="E6" s="356"/>
+      <c r="F6" s="356"/>
+      <c r="G6" s="356"/>
+      <c r="H6" s="356"/>
+      <c r="I6" s="356"/>
+      <c r="J6" s="355"/>
       <c r="K6" s="160"/>
-      <c r="L6" s="286"/>
-      <c r="M6" s="282"/>
-      <c r="N6" s="282"/>
-      <c r="O6" s="282"/>
+      <c r="L6" s="360"/>
+      <c r="M6" s="356"/>
+      <c r="N6" s="356"/>
+      <c r="O6" s="356"/>
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13528,8 +13528,8 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="239"/>
-      <c r="S7" s="239"/>
+      <c r="R7" s="315"/>
+      <c r="S7" s="315"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="161" t="s">
@@ -13583,8 +13583,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="239"/>
-      <c r="S8" s="239"/>
+      <c r="R8" s="315"/>
+      <c r="S8" s="315"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="161" t="s">
@@ -17871,7 +17871,7 @@
       <c r="I81" s="113"/>
       <c r="J81" s="113"/>
       <c r="K81" s="113"/>
-      <c r="L81" s="371"/>
+      <c r="L81" s="277"/>
       <c r="M81" s="113"/>
       <c r="N81" s="113"/>
       <c r="O81" s="114"/>
@@ -17917,6 +17917,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
@@ -17933,7 +17934,6 @@
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17976,7 +17976,7 @@
         <v>353</v>
       </c>
       <c r="H3" s="197" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I3" s="198"/>
       <c r="J3" s="199"/>
@@ -18020,42 +18020,42 @@
       <c r="M5" s="227"/>
     </row>
     <row r="6" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C6" s="294" t="s">
-        <v>372</v>
-      </c>
-      <c r="D6" s="295"/>
-      <c r="E6" s="295"/>
-      <c r="F6" s="295"/>
-      <c r="G6" s="295"/>
-      <c r="H6" s="295"/>
-      <c r="I6" s="295"/>
-      <c r="J6" s="296"/>
+      <c r="C6" s="361" t="s">
+        <v>371</v>
+      </c>
+      <c r="D6" s="362"/>
+      <c r="E6" s="362"/>
+      <c r="F6" s="362"/>
+      <c r="G6" s="362"/>
+      <c r="H6" s="362"/>
+      <c r="I6" s="362"/>
+      <c r="J6" s="363"/>
       <c r="K6" s="227"/>
       <c r="L6" s="227"/>
       <c r="M6" s="227"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="297"/>
-      <c r="D7" s="298"/>
-      <c r="E7" s="298"/>
-      <c r="F7" s="298"/>
-      <c r="G7" s="298"/>
-      <c r="H7" s="298"/>
-      <c r="I7" s="298"/>
-      <c r="J7" s="299"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="365"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
+      <c r="G7" s="365"/>
+      <c r="H7" s="365"/>
+      <c r="I7" s="365"/>
+      <c r="J7" s="366"/>
       <c r="K7" s="53"/>
       <c r="L7" s="53"/>
       <c r="M7" s="53"/>
     </row>
     <row r="8" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="300"/>
-      <c r="D8" s="301"/>
-      <c r="E8" s="301"/>
-      <c r="F8" s="301"/>
-      <c r="G8" s="301"/>
-      <c r="H8" s="301"/>
-      <c r="I8" s="301"/>
-      <c r="J8" s="302"/>
+      <c r="C8" s="367"/>
+      <c r="D8" s="368"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
+      <c r="G8" s="368"/>
+      <c r="H8" s="368"/>
+      <c r="I8" s="368"/>
+      <c r="J8" s="369"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
@@ -18095,7 +18095,7 @@
         <v>353</v>
       </c>
       <c r="H12" s="197" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I12" s="198"/>
       <c r="J12" s="199"/>
@@ -18142,44 +18142,44 @@
       <c r="N14" s="227"/>
     </row>
     <row r="15" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C15" s="294" t="s">
-        <v>373</v>
-      </c>
-      <c r="D15" s="295"/>
-      <c r="E15" s="295"/>
-      <c r="F15" s="295"/>
-      <c r="G15" s="295"/>
-      <c r="H15" s="295"/>
-      <c r="I15" s="295"/>
-      <c r="J15" s="296"/>
+      <c r="C15" s="361" t="s">
+        <v>372</v>
+      </c>
+      <c r="D15" s="362"/>
+      <c r="E15" s="362"/>
+      <c r="F15" s="362"/>
+      <c r="G15" s="362"/>
+      <c r="H15" s="362"/>
+      <c r="I15" s="362"/>
+      <c r="J15" s="363"/>
       <c r="K15" s="227"/>
       <c r="L15" s="227"/>
       <c r="M15" s="227"/>
       <c r="N15" s="227"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="297"/>
-      <c r="D16" s="298"/>
-      <c r="E16" s="298"/>
-      <c r="F16" s="298"/>
-      <c r="G16" s="298"/>
-      <c r="H16" s="298"/>
-      <c r="I16" s="298"/>
-      <c r="J16" s="299"/>
+      <c r="C16" s="364"/>
+      <c r="D16" s="365"/>
+      <c r="E16" s="365"/>
+      <c r="F16" s="365"/>
+      <c r="G16" s="365"/>
+      <c r="H16" s="365"/>
+      <c r="I16" s="365"/>
+      <c r="J16" s="366"/>
       <c r="K16" s="227"/>
       <c r="L16" s="227"/>
       <c r="M16" s="227"/>
       <c r="N16" s="227"/>
     </row>
     <row r="17" spans="3:14" ht="144.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="300"/>
-      <c r="D17" s="301"/>
-      <c r="E17" s="301"/>
-      <c r="F17" s="301"/>
-      <c r="G17" s="301"/>
-      <c r="H17" s="301"/>
-      <c r="I17" s="301"/>
-      <c r="J17" s="302"/>
+      <c r="C17" s="367"/>
+      <c r="D17" s="368"/>
+      <c r="E17" s="368"/>
+      <c r="F17" s="368"/>
+      <c r="G17" s="368"/>
+      <c r="H17" s="368"/>
+      <c r="I17" s="368"/>
+      <c r="J17" s="369"/>
       <c r="K17" s="227"/>
       <c r="L17" s="227"/>
       <c r="M17" s="227"/>
@@ -18237,7 +18237,7 @@
         <v>357</v>
       </c>
       <c r="H22" s="215" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I22" s="198"/>
       <c r="J22" s="199"/>
@@ -18261,42 +18261,42 @@
       <c r="M23" s="227"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="294" t="s">
-        <v>374</v>
-      </c>
-      <c r="D24" s="295"/>
-      <c r="E24" s="295"/>
-      <c r="F24" s="295"/>
-      <c r="G24" s="295"/>
-      <c r="H24" s="295"/>
-      <c r="I24" s="295"/>
-      <c r="J24" s="296"/>
+      <c r="C24" s="361" t="s">
+        <v>373</v>
+      </c>
+      <c r="D24" s="362"/>
+      <c r="E24" s="362"/>
+      <c r="F24" s="362"/>
+      <c r="G24" s="362"/>
+      <c r="H24" s="362"/>
+      <c r="I24" s="362"/>
+      <c r="J24" s="363"/>
       <c r="K24" s="227"/>
       <c r="L24" s="227"/>
       <c r="M24" s="227"/>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="297"/>
-      <c r="D25" s="298"/>
-      <c r="E25" s="298"/>
-      <c r="F25" s="298"/>
-      <c r="G25" s="298"/>
-      <c r="H25" s="298"/>
-      <c r="I25" s="298"/>
-      <c r="J25" s="299"/>
+      <c r="C25" s="364"/>
+      <c r="D25" s="365"/>
+      <c r="E25" s="365"/>
+      <c r="F25" s="365"/>
+      <c r="G25" s="365"/>
+      <c r="H25" s="365"/>
+      <c r="I25" s="365"/>
+      <c r="J25" s="366"/>
       <c r="K25" s="227"/>
       <c r="L25" s="227"/>
       <c r="M25" s="227"/>
     </row>
     <row r="26" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="300"/>
-      <c r="D26" s="301"/>
-      <c r="E26" s="301"/>
-      <c r="F26" s="301"/>
-      <c r="G26" s="301"/>
-      <c r="H26" s="301"/>
-      <c r="I26" s="301"/>
-      <c r="J26" s="302"/>
+      <c r="C26" s="367"/>
+      <c r="D26" s="368"/>
+      <c r="E26" s="368"/>
+      <c r="F26" s="368"/>
+      <c r="G26" s="368"/>
+      <c r="H26" s="368"/>
+      <c r="I26" s="368"/>
+      <c r="J26" s="369"/>
       <c r="K26" s="227"/>
       <c r="L26" s="227"/>
       <c r="M26" s="227"/>
@@ -18330,7 +18330,7 @@
         <v>353</v>
       </c>
       <c r="H30" s="197" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I30" s="198"/>
       <c r="J30" s="199"/>
@@ -18352,7 +18352,7 @@
         <v>357</v>
       </c>
       <c r="H31" s="53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I31" s="198"/>
       <c r="J31" s="199"/>
@@ -18374,40 +18374,40 @@
       <c r="L32" s="227"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="294" t="s">
-        <v>377</v>
-      </c>
-      <c r="D33" s="295"/>
-      <c r="E33" s="295"/>
-      <c r="F33" s="295"/>
-      <c r="G33" s="295"/>
-      <c r="H33" s="295"/>
-      <c r="I33" s="295"/>
-      <c r="J33" s="296"/>
+      <c r="C33" s="361" t="s">
+        <v>376</v>
+      </c>
+      <c r="D33" s="362"/>
+      <c r="E33" s="362"/>
+      <c r="F33" s="362"/>
+      <c r="G33" s="362"/>
+      <c r="H33" s="362"/>
+      <c r="I33" s="362"/>
+      <c r="J33" s="363"/>
       <c r="K33" s="227"/>
       <c r="L33" s="227"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="297"/>
-      <c r="D34" s="298"/>
-      <c r="E34" s="298"/>
-      <c r="F34" s="298"/>
-      <c r="G34" s="298"/>
-      <c r="H34" s="298"/>
-      <c r="I34" s="298"/>
-      <c r="J34" s="299"/>
+      <c r="C34" s="364"/>
+      <c r="D34" s="365"/>
+      <c r="E34" s="365"/>
+      <c r="F34" s="365"/>
+      <c r="G34" s="365"/>
+      <c r="H34" s="365"/>
+      <c r="I34" s="365"/>
+      <c r="J34" s="366"/>
       <c r="K34" s="227"/>
       <c r="L34" s="227"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="300"/>
-      <c r="D35" s="301"/>
-      <c r="E35" s="301"/>
-      <c r="F35" s="301"/>
-      <c r="G35" s="301"/>
-      <c r="H35" s="301"/>
-      <c r="I35" s="301"/>
-      <c r="J35" s="302"/>
+      <c r="C35" s="367"/>
+      <c r="D35" s="368"/>
+      <c r="E35" s="368"/>
+      <c r="F35" s="368"/>
+      <c r="G35" s="368"/>
+      <c r="H35" s="368"/>
+      <c r="I35" s="368"/>
+      <c r="J35" s="369"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
@@ -18438,7 +18438,7 @@
         <v>353</v>
       </c>
       <c r="H39" s="197" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I39" s="198"/>
       <c r="J39" s="199"/>
@@ -18458,12 +18458,12 @@
         <v>357</v>
       </c>
       <c r="H40" s="53" t="s">
+        <v>377</v>
+      </c>
+      <c r="I40" s="370" t="s">
         <v>378</v>
       </c>
-      <c r="I40" s="303" t="s">
-        <v>379</v>
-      </c>
-      <c r="J40" s="304"/>
+      <c r="J40" s="371"/>
     </row>
     <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C41" s="192" t="s">
@@ -18478,36 +18478,36 @@
       <c r="J41" s="200"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="294" t="s">
-        <v>380</v>
-      </c>
-      <c r="D42" s="295"/>
-      <c r="E42" s="295"/>
-      <c r="F42" s="295"/>
-      <c r="G42" s="295"/>
-      <c r="H42" s="295"/>
-      <c r="I42" s="295"/>
-      <c r="J42" s="296"/>
+      <c r="C42" s="361" t="s">
+        <v>379</v>
+      </c>
+      <c r="D42" s="362"/>
+      <c r="E42" s="362"/>
+      <c r="F42" s="362"/>
+      <c r="G42" s="362"/>
+      <c r="H42" s="362"/>
+      <c r="I42" s="362"/>
+      <c r="J42" s="363"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="297"/>
-      <c r="D43" s="298"/>
-      <c r="E43" s="298"/>
-      <c r="F43" s="298"/>
-      <c r="G43" s="298"/>
-      <c r="H43" s="298"/>
-      <c r="I43" s="298"/>
-      <c r="J43" s="299"/>
+      <c r="C43" s="364"/>
+      <c r="D43" s="365"/>
+      <c r="E43" s="365"/>
+      <c r="F43" s="365"/>
+      <c r="G43" s="365"/>
+      <c r="H43" s="365"/>
+      <c r="I43" s="365"/>
+      <c r="J43" s="366"/>
     </row>
     <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="300"/>
-      <c r="D44" s="301"/>
-      <c r="E44" s="301"/>
-      <c r="F44" s="301"/>
-      <c r="G44" s="301"/>
-      <c r="H44" s="301"/>
-      <c r="I44" s="301"/>
-      <c r="J44" s="302"/>
+      <c r="C44" s="367"/>
+      <c r="D44" s="368"/>
+      <c r="E44" s="368"/>
+      <c r="F44" s="368"/>
+      <c r="G44" s="368"/>
+      <c r="H44" s="368"/>
+      <c r="I44" s="368"/>
+      <c r="J44" s="369"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/2026/EL MIRADOR/Mayo/Mayo - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Mayo/Mayo - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D7F07E-BAD5-4C78-96DA-2D34F32C80B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F99BFF5-F540-448A-9D46-37EDAC854DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$143</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="425">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1154,46 +1149,6 @@
     <t>Quienes adeudan ARBA deben abonar el monto coloreado en ROSADO si es que en el trancurso del mes 3 y 4 del 2026 no abonaron ninguna cuota.</t>
   </si>
   <si>
-    <t>Ferraro jose</t>
-  </si>
-  <si>
-    <t>Adjunto el comprobante de pago de las expensas netas de la cochera 30 , $58.102,08 07/05</t>
-  </si>
-  <si>
-    <t>Deposito $382.000 el 08/05:                                                                                                                                                                                                                                                                                                                                               Dto 2D.       53.453
-Dto 2F.        54.022
-Dto3A.        93.827
-Dto3C.       101.220
-               ———————-
-                    302.522.-
-Más              78.474.-
-                 ——————-
-                    382.000.-
-Las cocheras son 29/30/34/37/38/39
-6 X 13.079=78.474</t>
-  </si>
-  <si>
-    <t>El ultimo dia de abril el abono 102.165,29 para el 6E y 27.009,81 para la cochera 12 corregir</t>
-  </si>
-  <si>
-    <t>6E y Cochera 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local 2 </t>
-  </si>
-  <si>
-    <t>Pago $244.445 el 19/05</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>IMPORTANTE!</t>
-  </si>
-  <si>
-    <t>10B en marzo pago $81.371,5 y se lo pusimos en ARBA cuando le tenia que quedar a favor en las expensas</t>
-  </si>
-  <si>
     <t>Transf 22/05</t>
   </si>
   <si>
@@ -1330,6 +1285,33 @@
   </si>
   <si>
     <t>Cuota ARBA</t>
+  </si>
+  <si>
+    <t>8D</t>
+  </si>
+  <si>
+    <t>Habia abonado bien el mes pasado, $206.121,4 y lo pusimos impago</t>
+  </si>
+  <si>
+    <t>UF 51</t>
+  </si>
+  <si>
+    <t>Abono de mas este mes, abono $377.877,51 - Le debe quedar dinero a favor</t>
+  </si>
+  <si>
+    <t>COCHERA 37</t>
+  </si>
+  <si>
+    <t>La cochera 37 habia pagado $33.586,06 el 10/05 y se lo pusimos al 2F</t>
+  </si>
+  <si>
+    <t>COCHERA 39</t>
+  </si>
+  <si>
+    <t>Jose ferraro</t>
+  </si>
+  <si>
+    <t>Anbono $58.102,08 el 07/05 de la cochera 39 por ende dice que no debe tener deuda alguna - Esa plata se la imputamos a la COCH 30</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1537,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,31 +1630,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2043,7 +2019,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="372">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2310,36 +2286,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2414,6 +2366,83 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2434,60 +2463,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2618,27 +2593,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2662,6 +2616,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2690,12 +2665,13 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2777,9 +2753,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2817,9 +2793,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2852,26 +2828,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2904,26 +2863,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3098,24 +3040,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N143"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="82"/>
       <c r="B1" s="91"/>
       <c r="C1" s="98" t="s">
@@ -3129,7 +3071,7 @@
       <c r="I1" s="80"/>
       <c r="J1" s="81"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="83"/>
       <c r="B2" s="92"/>
       <c r="C2" s="92" t="s">
@@ -3143,7 +3085,7 @@
       <c r="I2" s="93"/>
       <c r="J2" s="79"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="83"/>
       <c r="B3" s="92"/>
       <c r="C3" s="92" t="s">
@@ -3159,7 +3101,7 @@
       <c r="I3" s="93"/>
       <c r="J3" s="79"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="83"/>
       <c r="B4" s="92"/>
       <c r="C4" s="92" t="s">
@@ -3173,11 +3115,11 @@
       <c r="I4" s="93"/>
       <c r="J4" s="79"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="87"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="92" t="s">
@@ -3189,7 +3131,7 @@
       <c r="I5" s="92"/>
       <c r="J5" s="88"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="87"/>
       <c r="B6" s="92"/>
       <c r="C6" s="92" t="s">
@@ -3203,7 +3145,7 @@
       <c r="I6" s="92"/>
       <c r="J6" s="88"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="89"/>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -3215,128 +3157,128 @@
       <c r="I7" s="90"/>
       <c r="J7" s="94"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="303" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="304" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="303"/>
-      <c r="C14" s="303"/>
-      <c r="D14" s="303"/>
-      <c r="E14" s="303"/>
-      <c r="F14" s="303"/>
-      <c r="G14" s="303"/>
-      <c r="H14" s="303"/>
-      <c r="I14" s="303"/>
-      <c r="J14" s="303"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="303"/>
-      <c r="B15" s="303"/>
-      <c r="C15" s="303"/>
-      <c r="D15" s="303"/>
-      <c r="E15" s="303"/>
-      <c r="F15" s="303"/>
-      <c r="G15" s="303"/>
-      <c r="H15" s="303"/>
-      <c r="I15" s="303"/>
-      <c r="J15" s="303"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="303"/>
-      <c r="B16" s="303"/>
-      <c r="C16" s="303"/>
-      <c r="D16" s="303"/>
-      <c r="E16" s="303"/>
-      <c r="F16" s="303"/>
-      <c r="G16" s="303"/>
-      <c r="H16" s="303"/>
-      <c r="I16" s="303"/>
-      <c r="J16" s="303"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="303"/>
-      <c r="B17" s="303"/>
-      <c r="C17" s="303"/>
-      <c r="D17" s="303"/>
-      <c r="E17" s="303"/>
-      <c r="F17" s="303"/>
-      <c r="G17" s="303"/>
-      <c r="H17" s="303"/>
-      <c r="I17" s="303"/>
-      <c r="J17" s="303"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="303"/>
-      <c r="B18" s="303"/>
-      <c r="C18" s="303"/>
-      <c r="D18" s="303"/>
-      <c r="E18" s="303"/>
-      <c r="F18" s="303"/>
-      <c r="G18" s="303"/>
-      <c r="H18" s="303"/>
-      <c r="I18" s="303"/>
-      <c r="J18" s="303"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="304"/>
+      <c r="C14" s="304"/>
+      <c r="D14" s="304"/>
+      <c r="E14" s="304"/>
+      <c r="F14" s="304"/>
+      <c r="G14" s="304"/>
+      <c r="H14" s="304"/>
+      <c r="I14" s="304"/>
+      <c r="J14" s="304"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="304"/>
+      <c r="B15" s="304"/>
+      <c r="C15" s="304"/>
+      <c r="D15" s="304"/>
+      <c r="E15" s="304"/>
+      <c r="F15" s="304"/>
+      <c r="G15" s="304"/>
+      <c r="H15" s="304"/>
+      <c r="I15" s="304"/>
+      <c r="J15" s="304"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="304"/>
+      <c r="B16" s="304"/>
+      <c r="C16" s="304"/>
+      <c r="D16" s="304"/>
+      <c r="E16" s="304"/>
+      <c r="F16" s="304"/>
+      <c r="G16" s="304"/>
+      <c r="H16" s="304"/>
+      <c r="I16" s="304"/>
+      <c r="J16" s="304"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="304"/>
+      <c r="B17" s="304"/>
+      <c r="C17" s="304"/>
+      <c r="D17" s="304"/>
+      <c r="E17" s="304"/>
+      <c r="F17" s="304"/>
+      <c r="G17" s="304"/>
+      <c r="H17" s="304"/>
+      <c r="I17" s="304"/>
+      <c r="J17" s="304"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="304"/>
+      <c r="B18" s="304"/>
+      <c r="C18" s="304"/>
+      <c r="D18" s="304"/>
+      <c r="E18" s="304"/>
+      <c r="F18" s="304"/>
+      <c r="G18" s="304"/>
+      <c r="H18" s="304"/>
+      <c r="I18" s="304"/>
+      <c r="J18" s="304"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="304" t="s">
-        <v>418</v>
-      </c>
-      <c r="B20" s="304"/>
-      <c r="C20" s="304"/>
-      <c r="D20" s="304"/>
-      <c r="E20" s="304"/>
-      <c r="F20" s="304"/>
-      <c r="G20" s="304"/>
-      <c r="H20" s="304"/>
-      <c r="I20" s="304"/>
-      <c r="J20" s="304"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="304"/>
-      <c r="B21" s="304"/>
-      <c r="C21" s="304"/>
-      <c r="D21" s="304"/>
-      <c r="E21" s="304"/>
-      <c r="F21" s="304"/>
-      <c r="G21" s="304"/>
-      <c r="H21" s="304"/>
-      <c r="I21" s="304"/>
-      <c r="J21" s="304"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="304"/>
-      <c r="B22" s="304"/>
-      <c r="C22" s="304"/>
-      <c r="D22" s="304"/>
-      <c r="E22" s="304"/>
-      <c r="F22" s="304"/>
-      <c r="G22" s="304"/>
-      <c r="H22" s="304"/>
-      <c r="I22" s="304"/>
-      <c r="J22" s="304"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="305" t="s">
+        <v>408</v>
+      </c>
+      <c r="B20" s="305"/>
+      <c r="C20" s="305"/>
+      <c r="D20" s="305"/>
+      <c r="E20" s="305"/>
+      <c r="F20" s="305"/>
+      <c r="G20" s="305"/>
+      <c r="H20" s="305"/>
+      <c r="I20" s="305"/>
+      <c r="J20" s="305"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="305"/>
+      <c r="B21" s="305"/>
+      <c r="C21" s="305"/>
+      <c r="D21" s="305"/>
+      <c r="E21" s="305"/>
+      <c r="F21" s="305"/>
+      <c r="G21" s="305"/>
+      <c r="H21" s="305"/>
+      <c r="I21" s="305"/>
+      <c r="J21" s="305"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="305"/>
+      <c r="B22" s="305"/>
+      <c r="C22" s="305"/>
+      <c r="D22" s="305"/>
+      <c r="E22" s="305"/>
+      <c r="F22" s="305"/>
+      <c r="G22" s="305"/>
+      <c r="H22" s="305"/>
+      <c r="I22" s="305"/>
+      <c r="J22" s="305"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="69"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="230" t="s">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="231"/>
-      <c r="C24" s="232"/>
-      <c r="D24" s="233"/>
-      <c r="E24" s="234" t="s">
+      <c r="B24" s="209"/>
+      <c r="C24" s="210"/>
+      <c r="D24" s="211"/>
+      <c r="E24" s="212" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="234" t="s">
+      <c r="F24" s="212" t="s">
         <v>165</v>
       </c>
       <c r="G24" s="70" t="s">
@@ -3352,28 +3294,28 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="235" t="s">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="213" t="s">
         <v>341</v>
       </c>
       <c r="B25" s="181"/>
       <c r="C25" s="181"/>
       <c r="D25" s="179"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="236"/>
+      <c r="E25" s="214"/>
+      <c r="F25" s="214"/>
       <c r="G25" s="44"/>
       <c r="H25" s="44"/>
       <c r="I25" s="44"/>
       <c r="J25" s="44"/>
       <c r="L25" s="50"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="237" t="s">
-        <v>394</v>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="215" t="s">
+        <v>384</v>
       </c>
       <c r="B26" s="181"/>
       <c r="C26" s="181" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D26" s="179">
         <v>3000000</v>
@@ -3386,12 +3328,12 @@
       <c r="J26" s="3"/>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="238" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="238"/>
-      <c r="C27" s="238"/>
+      <c r="B27" s="216"/>
+      <c r="C27" s="216"/>
       <c r="D27" s="31">
         <f>SUM(D25:D26)</f>
         <v>3000000</v>
@@ -3400,7 +3342,7 @@
         <f>D27*93.2%</f>
         <v>2796000</v>
       </c>
-      <c r="F27" s="239">
+      <c r="F27" s="217">
         <f>$D27*1.08%</f>
         <v>32400</v>
       </c>
@@ -3429,154 +3371,154 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="237" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="215" t="s">
         <v>234</v>
       </c>
       <c r="B28" s="181"/>
       <c r="C28" s="181"/>
       <c r="D28" s="179"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="236"/>
+      <c r="E28" s="214"/>
+      <c r="F28" s="214"/>
       <c r="G28" s="44"/>
       <c r="H28" s="44"/>
       <c r="I28" s="44"/>
       <c r="J28" s="44"/>
       <c r="L28" s="50"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="237" t="s">
-        <v>383</v>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B29" s="181" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C29" s="181"/>
       <c r="D29" s="179">
         <v>63630</v>
       </c>
-      <c r="E29" s="236"/>
-      <c r="F29" s="236"/>
+      <c r="E29" s="214"/>
+      <c r="F29" s="214"/>
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
       <c r="I29" s="44"/>
       <c r="J29" s="44"/>
       <c r="L29" s="50"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="237" t="s">
-        <v>383</v>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B30" s="181" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C30" s="181"/>
       <c r="D30" s="179">
         <v>60000</v>
       </c>
-      <c r="E30" s="236"/>
-      <c r="F30" s="236"/>
+      <c r="E30" s="214"/>
+      <c r="F30" s="214"/>
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
       <c r="I30" s="44"/>
       <c r="J30" s="44"/>
       <c r="L30" s="50"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="237" t="s">
-        <v>383</v>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B31" s="181" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C31" s="181"/>
       <c r="D31" s="179">
         <v>99726.06</v>
       </c>
-      <c r="E31" s="236"/>
-      <c r="F31" s="236"/>
+      <c r="E31" s="214"/>
+      <c r="F31" s="214"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
       <c r="I31" s="44"/>
       <c r="J31" s="44"/>
       <c r="L31" s="50"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="237" t="s">
-        <v>383</v>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B32" s="181" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C32" s="181"/>
       <c r="D32" s="179">
         <v>44990.07</v>
       </c>
-      <c r="E32" s="236"/>
-      <c r="F32" s="236"/>
+      <c r="E32" s="214"/>
+      <c r="F32" s="214"/>
       <c r="G32" s="44"/>
       <c r="H32" s="44"/>
       <c r="I32" s="44"/>
       <c r="J32" s="44"/>
       <c r="L32" s="50"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="237" t="s">
-        <v>383</v>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B33" s="181" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C33" s="181"/>
       <c r="D33" s="179">
         <v>70000.03</v>
       </c>
-      <c r="E33" s="236"/>
-      <c r="F33" s="236"/>
+      <c r="E33" s="214"/>
+      <c r="F33" s="214"/>
       <c r="G33" s="44"/>
       <c r="H33" s="44"/>
       <c r="I33" s="44"/>
       <c r="J33" s="44"/>
       <c r="L33" s="50"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="237" t="s">
-        <v>383</v>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="215" t="s">
+        <v>373</v>
       </c>
       <c r="B34" s="181" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C34" s="181"/>
       <c r="D34" s="179">
         <v>60015.95</v>
       </c>
-      <c r="E34" s="236"/>
-      <c r="F34" s="236"/>
+      <c r="E34" s="214"/>
+      <c r="F34" s="214"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44"/>
       <c r="I34" s="44"/>
       <c r="J34" s="44"/>
       <c r="L34" s="50"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="237"/>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="215"/>
       <c r="B35" s="181"/>
       <c r="C35" s="181"/>
       <c r="D35" s="179"/>
-      <c r="E35" s="236"/>
-      <c r="F35" s="236"/>
+      <c r="E35" s="214"/>
+      <c r="F35" s="214"/>
       <c r="G35" s="44"/>
       <c r="H35" s="44"/>
       <c r="I35" s="44"/>
       <c r="J35" s="44"/>
       <c r="L35" s="50"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="238" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="216" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="238"/>
-      <c r="C36" s="238"/>
+      <c r="B36" s="216"/>
+      <c r="C36" s="216"/>
       <c r="D36" s="31">
         <f>SUM(D29:D35)</f>
         <v>398362.11000000004</v>
@@ -3599,99 +3541,99 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="237" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="215" t="s">
         <v>230</v>
       </c>
       <c r="B37" s="141"/>
       <c r="C37" s="141"/>
       <c r="D37" s="179"/>
-      <c r="E37" s="240"/>
-      <c r="F37" s="240"/>
+      <c r="E37" s="218"/>
+      <c r="F37" s="218"/>
       <c r="G37" s="38"/>
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
       <c r="J37" s="38"/>
       <c r="L37" s="50"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="141" t="s">
         <v>342</v>
       </c>
       <c r="B38" s="141"/>
-      <c r="C38" s="241"/>
+      <c r="C38" s="219"/>
       <c r="D38" s="179">
         <v>0</v>
       </c>
-      <c r="E38" s="240"/>
-      <c r="F38" s="240"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
       <c r="G38" s="38"/>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
       <c r="J38" s="38"/>
       <c r="L38" s="50"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="141" t="s">
         <v>362</v>
       </c>
       <c r="B39" s="141" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C39" s="141" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D39" s="179">
         <v>1742902</v>
       </c>
-      <c r="E39" s="240"/>
-      <c r="F39" s="240"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
       <c r="G39" s="38"/>
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
       <c r="J39" s="38"/>
       <c r="L39" s="50"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="141" t="s">
         <v>233</v>
       </c>
       <c r="B40" s="141" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C40" s="141" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D40" s="179">
         <v>1742902</v>
       </c>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
+      <c r="E40" s="218"/>
+      <c r="F40" s="218"/>
       <c r="G40" s="38"/>
       <c r="H40" s="38"/>
       <c r="I40" s="38"/>
       <c r="J40" s="38"/>
       <c r="L40" s="50"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="141"/>
       <c r="B41" s="141"/>
       <c r="C41" s="141"/>
       <c r="D41" s="179"/>
-      <c r="E41" s="240"/>
-      <c r="F41" s="240"/>
+      <c r="E41" s="218"/>
+      <c r="F41" s="218"/>
       <c r="G41" s="38"/>
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
       <c r="J41" s="38"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="238" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="216" t="s">
         <v>232</v>
       </c>
-      <c r="B42" s="238"/>
-      <c r="C42" s="238"/>
+      <c r="B42" s="216"/>
+      <c r="C42" s="216"/>
       <c r="D42" s="180">
         <f>SUM(D38:D41)</f>
         <v>3485804</v>
@@ -3700,7 +3642,7 @@
         <f>D42*93.2%</f>
         <v>3248769.3280000002</v>
       </c>
-      <c r="F42" s="239">
+      <c r="F42" s="217">
         <f>$D42*1.08%</f>
         <v>37646.683199999999</v>
       </c>
@@ -3729,66 +3671,66 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="237" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="215" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="181"/>
       <c r="C43" s="181"/>
       <c r="D43" s="33"/>
-      <c r="E43" s="242"/>
-      <c r="F43" s="242"/>
+      <c r="E43" s="220"/>
+      <c r="F43" s="220"/>
       <c r="G43" s="34"/>
       <c r="H43" s="34"/>
       <c r="I43" s="34"/>
       <c r="J43" s="3"/>
       <c r="L43" s="50"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="181"/>
       <c r="B44" s="181"/>
       <c r="C44" s="181"/>
       <c r="D44" s="33"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
+      <c r="E44" s="221"/>
+      <c r="F44" s="221"/>
       <c r="G44" s="84"/>
       <c r="H44" s="84"/>
       <c r="I44" s="84"/>
       <c r="J44" s="3"/>
       <c r="L44" s="50"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="181"/>
       <c r="B45" s="181"/>
       <c r="C45" s="181"/>
       <c r="D45" s="33"/>
-      <c r="E45" s="243"/>
-      <c r="F45" s="243"/>
+      <c r="E45" s="221"/>
+      <c r="F45" s="221"/>
       <c r="G45" s="84"/>
       <c r="H45" s="84"/>
       <c r="I45" s="84"/>
       <c r="J45" s="3"/>
       <c r="L45" s="50"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="181"/>
       <c r="B46" s="181"/>
-      <c r="C46" s="244"/>
+      <c r="C46" s="222"/>
       <c r="D46" s="33"/>
-      <c r="E46" s="245"/>
-      <c r="F46" s="245"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
       <c r="G46" s="55"/>
       <c r="H46" s="55"/>
       <c r="I46" s="55"/>
       <c r="J46" s="3"/>
       <c r="L46" s="50"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="238" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="216" t="s">
         <v>231</v>
       </c>
-      <c r="B47" s="238"/>
-      <c r="C47" s="238"/>
+      <c r="B47" s="216"/>
+      <c r="C47" s="216"/>
       <c r="D47" s="31">
         <f>SUM(D43:D46)</f>
         <v>0</v>
@@ -3797,7 +3739,7 @@
         <f>D47*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F47" s="239">
+      <c r="F47" s="217">
         <f>$D47*1.08%</f>
         <v>0</v>
       </c>
@@ -3826,22 +3768,22 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="237" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="215" t="s">
         <v>222</v>
       </c>
       <c r="B48" s="181"/>
       <c r="C48" s="181"/>
       <c r="D48" s="181"/>
-      <c r="E48" s="246"/>
-      <c r="F48" s="246"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
       <c r="G48" s="35"/>
       <c r="H48" s="35"/>
       <c r="I48" s="35"/>
       <c r="J48" s="25"/>
       <c r="L48" s="50"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="181" t="s">
         <v>226</v>
       </c>
@@ -3852,11 +3794,11 @@
       <c r="D49" s="33">
         <v>214371</v>
       </c>
-      <c r="E49" s="236">
+      <c r="E49" s="214">
         <f>D49*93.2%</f>
         <v>199793.772</v>
       </c>
-      <c r="F49" s="236">
+      <c r="F49" s="214">
         <f>$D49*1.08%</f>
         <v>2315.2067999999999</v>
       </c>
@@ -3882,13 +3824,13 @@
       </c>
       <c r="L49" s="50"/>
     </row>
-    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="297"/>
-      <c r="B50" s="298"/>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="291"/>
+      <c r="B50" s="292"/>
       <c r="C50" s="181"/>
       <c r="D50" s="33"/>
-      <c r="E50" s="236"/>
-      <c r="F50" s="236"/>
+      <c r="E50" s="214"/>
+      <c r="F50" s="214"/>
       <c r="G50" s="44"/>
       <c r="H50" s="44"/>
       <c r="I50" s="44"/>
@@ -3896,12 +3838,12 @@
       <c r="K50" s="32"/>
       <c r="L50" s="50"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="238" t="s">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="247"/>
-      <c r="C51" s="247"/>
+      <c r="B51" s="225"/>
+      <c r="C51" s="225"/>
       <c r="D51" s="31">
         <f t="shared" ref="D51:J51" si="0">SUM(D49:D50)</f>
         <v>214371</v>
@@ -3939,37 +3881,37 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="237" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="215" t="s">
         <v>3</v>
       </c>
       <c r="B52" s="181"/>
       <c r="C52" s="181"/>
       <c r="D52" s="182"/>
-      <c r="E52" s="246"/>
-      <c r="F52" s="246"/>
+      <c r="E52" s="224"/>
+      <c r="F52" s="224"/>
       <c r="G52" s="35"/>
       <c r="H52" s="35"/>
       <c r="I52" s="35"/>
       <c r="J52" s="3"/>
       <c r="L52" s="50"/>
     </row>
-    <row r="53" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="248" t="s">
+    <row r="53" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="226" t="s">
         <v>227</v>
       </c>
       <c r="B53" s="181"/>
-      <c r="C53" s="244" t="s">
-        <v>403</v>
-      </c>
-      <c r="D53" s="249">
+      <c r="C53" s="222" t="s">
+        <v>393</v>
+      </c>
+      <c r="D53" s="227">
         <v>36079.1</v>
       </c>
-      <c r="E53" s="250">
+      <c r="E53" s="228">
         <f>D53*93.2%</f>
         <v>33625.7212</v>
       </c>
-      <c r="F53" s="236">
+      <c r="F53" s="214">
         <f>$D53*1.08%</f>
         <v>389.65428000000003</v>
       </c>
@@ -4000,22 +3942,22 @@
       <c r="M53" s="64"/>
       <c r="N53" s="64"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="181" t="s">
         <v>228</v>
       </c>
       <c r="B54" s="181"/>
-      <c r="C54" s="244" t="s">
-        <v>390</v>
-      </c>
-      <c r="D54" s="249">
+      <c r="C54" s="222" t="s">
+        <v>380</v>
+      </c>
+      <c r="D54" s="227">
         <v>3898893.1</v>
       </c>
-      <c r="E54" s="250">
+      <c r="E54" s="228">
         <f t="shared" ref="E54" si="1">D54*93.2%</f>
         <v>3633768.3692000001</v>
       </c>
-      <c r="F54" s="236">
+      <c r="F54" s="214">
         <f t="shared" ref="F54" si="2">$D54*1.08%</f>
         <v>42108.045480000001</v>
       </c>
@@ -4046,22 +3988,22 @@
       <c r="M54" s="64"/>
       <c r="N54" s="64"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="181" t="s">
         <v>229</v>
       </c>
       <c r="B55" s="181"/>
       <c r="C55" s="181" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D55" s="33">
         <v>151564.79999999999</v>
       </c>
-      <c r="E55" s="250">
+      <c r="E55" s="228">
         <f>D55</f>
         <v>151564.79999999999</v>
       </c>
-      <c r="F55" s="236"/>
+      <c r="F55" s="214"/>
       <c r="G55" s="44"/>
       <c r="H55" s="44"/>
       <c r="I55" s="44"/>
@@ -4083,22 +4025,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="181" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B56" s="181"/>
-      <c r="C56" s="244" t="s">
+      <c r="C56" s="222" t="s">
         <v>360</v>
       </c>
       <c r="D56" s="33">
         <v>359504.14</v>
       </c>
-      <c r="E56" s="250">
+      <c r="E56" s="228">
         <f>D56</f>
         <v>359504.14</v>
       </c>
-      <c r="F56" s="236"/>
+      <c r="F56" s="214"/>
       <c r="G56" s="44"/>
       <c r="H56" s="44"/>
       <c r="I56" s="44"/>
@@ -4114,22 +4056,22 @@
       <c r="M56" s="64"/>
       <c r="N56" s="64"/>
     </row>
-    <row r="57" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="285" t="s">
+    <row r="57" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="279" t="s">
         <v>361</v>
       </c>
-      <c r="B57" s="305"/>
+      <c r="B57" s="306"/>
       <c r="C57" s="141" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D57" s="33">
         <v>50000</v>
       </c>
-      <c r="E57" s="250">
+      <c r="E57" s="228">
         <f>D57</f>
         <v>50000</v>
       </c>
-      <c r="F57" s="236"/>
+      <c r="F57" s="214"/>
       <c r="G57" s="44"/>
       <c r="H57" s="44"/>
       <c r="I57" s="44"/>
@@ -4151,22 +4093,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="141" t="s">
         <v>259</v>
       </c>
       <c r="B58" s="141"/>
-      <c r="C58" s="244" t="s">
-        <v>391</v>
+      <c r="C58" s="222" t="s">
+        <v>381</v>
       </c>
       <c r="D58" s="33">
         <v>5760.01</v>
       </c>
-      <c r="E58" s="250">
+      <c r="E58" s="228">
         <f>D58*93.2%</f>
         <v>5368.3293200000007</v>
       </c>
-      <c r="F58" s="236">
+      <c r="F58" s="214">
         <f>$D58*1.08%</f>
         <v>62.208108000000003</v>
       </c>
@@ -4203,22 +4145,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="141" t="s">
         <v>260</v>
       </c>
       <c r="B59" s="141"/>
-      <c r="C59" s="244" t="s">
-        <v>391</v>
+      <c r="C59" s="222" t="s">
+        <v>381</v>
       </c>
       <c r="D59" s="33">
         <v>907421.13</v>
       </c>
-      <c r="E59" s="250">
+      <c r="E59" s="228">
         <f>D59</f>
         <v>907421.13</v>
       </c>
-      <c r="F59" s="236"/>
+      <c r="F59" s="214"/>
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
       <c r="I59" s="44"/>
@@ -4240,22 +4182,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="251" t="s">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="229" t="s">
         <v>258</v>
       </c>
-      <c r="B60" s="252"/>
+      <c r="B60" s="230"/>
       <c r="C60" s="181" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D60" s="33">
         <v>120000</v>
       </c>
-      <c r="E60" s="250">
+      <c r="E60" s="228">
         <f>D60</f>
         <v>120000</v>
       </c>
-      <c r="F60" s="250"/>
+      <c r="F60" s="228"/>
       <c r="G60" s="49"/>
       <c r="H60" s="49"/>
       <c r="I60" s="49"/>
@@ -4277,12 +4219,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="238" t="s">
+    <row r="61" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="216" t="s">
         <v>4</v>
       </c>
-      <c r="B61" s="247"/>
-      <c r="C61" s="247"/>
+      <c r="B61" s="225"/>
+      <c r="C61" s="225"/>
       <c r="D61" s="31">
         <f>SUM(D53:D60)</f>
         <v>5529222.2799999993</v>
@@ -4324,63 +4266,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="181"/>
       <c r="B62" s="181"/>
       <c r="C62" s="181"/>
       <c r="D62" s="182"/>
-      <c r="E62" s="246"/>
-      <c r="F62" s="246"/>
+      <c r="E62" s="224"/>
+      <c r="F62" s="224"/>
       <c r="G62" s="35"/>
       <c r="H62" s="35"/>
       <c r="I62" s="35"/>
       <c r="J62" s="3"/>
       <c r="L62" s="50"/>
     </row>
-    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="181"/>
       <c r="B63" s="181"/>
       <c r="C63" s="181"/>
       <c r="D63" s="182"/>
-      <c r="E63" s="242"/>
-      <c r="F63" s="242"/>
+      <c r="E63" s="220"/>
+      <c r="F63" s="220"/>
       <c r="G63" s="34"/>
       <c r="H63" s="34"/>
       <c r="I63" s="34"/>
       <c r="J63" s="3"/>
       <c r="L63" s="50"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="237" t="s">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="215" t="s">
         <v>223</v>
       </c>
       <c r="B64" s="181"/>
       <c r="C64" s="181"/>
       <c r="D64" s="182"/>
-      <c r="E64" s="242"/>
-      <c r="F64" s="242"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
       <c r="G64" s="34"/>
       <c r="H64" s="34"/>
       <c r="I64" s="34"/>
       <c r="J64" s="3"/>
       <c r="L64" s="50"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="242" t="s">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="220" t="s">
         <v>340</v>
       </c>
-      <c r="B65" s="253"/>
+      <c r="B65" s="231"/>
       <c r="C65" s="141" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D65" s="33">
         <v>200000</v>
       </c>
-      <c r="E65" s="250">
+      <c r="E65" s="228">
         <f t="shared" ref="E65:E67" si="12">D65</f>
         <v>200000</v>
       </c>
-      <c r="F65" s="245"/>
+      <c r="F65" s="223"/>
       <c r="G65" s="55"/>
       <c r="H65" s="55"/>
       <c r="I65" s="55"/>
@@ -4394,22 +4336,22 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="297" t="s">
+    <row r="66" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="291" t="s">
         <v>339</v>
       </c>
-      <c r="B66" s="298"/>
+      <c r="B66" s="292"/>
       <c r="C66" s="33" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="D66" s="33">
         <v>314672.59999999998</v>
       </c>
-      <c r="E66" s="250">
+      <c r="E66" s="228">
         <f>D66*93.2%</f>
         <v>293274.86320000002</v>
       </c>
-      <c r="F66" s="236">
+      <c r="F66" s="214">
         <f>$D66*1.08%</f>
         <v>3398.4640799999997</v>
       </c>
@@ -4438,22 +4380,22 @@
         <v>314672.59999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="297" t="s">
+    <row r="67" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="291" t="s">
         <v>339</v>
       </c>
-      <c r="B67" s="298"/>
+      <c r="B67" s="292"/>
       <c r="C67" s="33" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D67" s="33">
         <v>313198</v>
       </c>
-      <c r="E67" s="250">
+      <c r="E67" s="228">
         <f t="shared" si="12"/>
         <v>313198</v>
       </c>
-      <c r="F67" s="236"/>
+      <c r="F67" s="214"/>
       <c r="G67" s="44"/>
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
@@ -4461,22 +4403,22 @@
       <c r="K67" s="32"/>
       <c r="L67" s="54"/>
     </row>
-    <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="297" t="s">
-        <v>399</v>
-      </c>
-      <c r="B68" s="298"/>
+    <row r="68" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="291" t="s">
+        <v>389</v>
+      </c>
+      <c r="B68" s="292"/>
       <c r="C68" s="33" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D68" s="33">
         <v>597500</v>
       </c>
-      <c r="E68" s="250">
+      <c r="E68" s="228">
         <f>D68*93.2%</f>
         <v>556870</v>
       </c>
-      <c r="F68" s="236">
+      <c r="F68" s="214">
         <f>$D68*1.08%</f>
         <v>6453</v>
       </c>
@@ -4502,22 +4444,22 @@
       </c>
       <c r="L68" s="54"/>
     </row>
-    <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="297" t="s">
-        <v>388</v>
-      </c>
-      <c r="B69" s="298"/>
+    <row r="69" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="291" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="292"/>
       <c r="C69" s="33" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D69" s="33">
         <v>21000</v>
       </c>
-      <c r="E69" s="250">
+      <c r="E69" s="228">
         <f>D69</f>
         <v>21000</v>
       </c>
-      <c r="F69" s="236"/>
+      <c r="F69" s="214"/>
       <c r="G69" s="44"/>
       <c r="H69" s="44"/>
       <c r="I69" s="44"/>
@@ -4531,22 +4473,22 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="254" t="s">
-        <v>401</v>
-      </c>
-      <c r="B70" s="255"/>
+    <row r="70" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="232" t="s">
+        <v>391</v>
+      </c>
+      <c r="B70" s="233"/>
       <c r="C70" s="33" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="D70" s="33">
         <v>200000</v>
       </c>
-      <c r="E70" s="250">
+      <c r="E70" s="228">
         <f>D70</f>
         <v>200000</v>
       </c>
-      <c r="F70" s="236"/>
+      <c r="F70" s="214"/>
       <c r="G70" s="44"/>
       <c r="H70" s="44"/>
       <c r="I70" s="44"/>
@@ -4557,22 +4499,22 @@
       </c>
       <c r="L70" s="54"/>
     </row>
-    <row r="71" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="254" t="s">
-        <v>385</v>
-      </c>
-      <c r="B71" s="255"/>
+    <row r="71" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="232" t="s">
+        <v>375</v>
+      </c>
+      <c r="B71" s="233"/>
       <c r="C71" s="33" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D71" s="33">
         <v>125000</v>
       </c>
-      <c r="E71" s="250">
+      <c r="E71" s="228">
         <f>D71</f>
         <v>125000</v>
       </c>
-      <c r="F71" s="236"/>
+      <c r="F71" s="214"/>
       <c r="G71" s="44"/>
       <c r="H71" s="44"/>
       <c r="I71" s="44"/>
@@ -4583,22 +4525,22 @@
       </c>
       <c r="L71" s="54"/>
     </row>
-    <row r="72" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="254" t="s">
-        <v>389</v>
-      </c>
-      <c r="B72" s="255"/>
+    <row r="72" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="232" t="s">
+        <v>379</v>
+      </c>
+      <c r="B72" s="233"/>
       <c r="C72" s="33" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D72" s="33">
         <v>25000</v>
       </c>
-      <c r="E72" s="250">
+      <c r="E72" s="228">
         <f>D72</f>
         <v>25000</v>
       </c>
-      <c r="F72" s="236"/>
+      <c r="F72" s="214"/>
       <c r="G72" s="44"/>
       <c r="H72" s="44"/>
       <c r="I72" s="44"/>
@@ -4609,22 +4551,22 @@
       </c>
       <c r="L72" s="54"/>
     </row>
-    <row r="73" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="297" t="s">
+    <row r="73" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="291" t="s">
         <v>359</v>
       </c>
-      <c r="B73" s="298"/>
+      <c r="B73" s="292"/>
       <c r="C73" s="33" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D73" s="33">
         <v>46200</v>
       </c>
-      <c r="E73" s="250">
+      <c r="E73" s="228">
         <f>D73</f>
         <v>46200</v>
       </c>
-      <c r="F73" s="236"/>
+      <c r="F73" s="214"/>
       <c r="G73" s="44"/>
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
@@ -4635,22 +4577,22 @@
       </c>
       <c r="L73" s="54"/>
     </row>
-    <row r="74" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="297" t="s">
-        <v>406</v>
-      </c>
-      <c r="B74" s="298"/>
+    <row r="74" spans="1:14" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="291" t="s">
+        <v>396</v>
+      </c>
+      <c r="B74" s="292"/>
       <c r="C74" s="33" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D74" s="33">
         <v>191400</v>
       </c>
-      <c r="E74" s="250">
+      <c r="E74" s="228">
         <f>D74*93.2%</f>
         <v>178384.80000000002</v>
       </c>
-      <c r="F74" s="236">
+      <c r="F74" s="214">
         <f>$D74*1.08%</f>
         <v>2067.12</v>
       </c>
@@ -4673,12 +4615,12 @@
       <c r="L74" s="50"/>
       <c r="M74" s="32"/>
     </row>
-    <row r="75" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="238" t="s">
+    <row r="75" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="216" t="s">
         <v>224</v>
       </c>
-      <c r="B75" s="238"/>
-      <c r="C75" s="238"/>
+      <c r="B75" s="216"/>
+      <c r="C75" s="216"/>
       <c r="D75" s="31">
         <f t="shared" ref="D75:J75" si="15">SUM(D65:D74)</f>
         <v>2033970.6</v>
@@ -4717,65 +4659,65 @@
       </c>
       <c r="N75" s="32"/>
     </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="181"/>
       <c r="B76" s="181"/>
       <c r="C76" s="181"/>
       <c r="D76" s="182"/>
-      <c r="E76" s="246"/>
-      <c r="F76" s="246"/>
+      <c r="E76" s="224"/>
+      <c r="F76" s="224"/>
       <c r="G76" s="35"/>
       <c r="H76" s="35"/>
       <c r="I76" s="35"/>
       <c r="J76" s="3"/>
       <c r="L76" s="50"/>
     </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="181"/>
       <c r="B77" s="181"/>
       <c r="C77" s="181"/>
       <c r="D77" s="182"/>
-      <c r="E77" s="242"/>
-      <c r="F77" s="242"/>
+      <c r="E77" s="220"/>
+      <c r="F77" s="220"/>
       <c r="G77" s="34"/>
       <c r="H77" s="34"/>
       <c r="I77" s="34"/>
       <c r="J77" s="3"/>
       <c r="L77" s="50"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="237" t="s">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="215" t="s">
         <v>5</v>
       </c>
       <c r="B78" s="181"/>
       <c r="C78" s="181"/>
       <c r="D78" s="182"/>
-      <c r="E78" s="242"/>
-      <c r="F78" s="242"/>
+      <c r="E78" s="220"/>
+      <c r="F78" s="220"/>
       <c r="G78" s="34"/>
       <c r="H78" s="34"/>
       <c r="I78" s="34"/>
       <c r="J78" s="3"/>
       <c r="L78" s="50"/>
     </row>
-    <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="256" t="s">
+    <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="234" t="s">
         <v>6</v>
       </c>
       <c r="B79" s="181" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C79" s="181" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D79" s="33">
         <v>860560</v>
       </c>
-      <c r="E79" s="250">
+      <c r="E79" s="228">
         <f>D79*93.2%</f>
         <v>802041.92</v>
       </c>
-      <c r="F79" s="236">
+      <c r="F79" s="214">
         <f>$D79*1.08%</f>
         <v>9294.0480000000007</v>
       </c>
@@ -4799,16 +4741,16 @@
         <v>343</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="237"/>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="215"/>
       <c r="B80" s="181"/>
       <c r="C80" s="181"/>
       <c r="D80" s="33"/>
-      <c r="E80" s="250">
+      <c r="E80" s="228">
         <f>D80*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F80" s="236">
+      <c r="F80" s="214">
         <f>$D80*1.08%</f>
         <v>0</v>
       </c>
@@ -4831,13 +4773,13 @@
       <c r="L80" s="50"/>
       <c r="N80" s="33"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="181"/>
       <c r="B81" s="181"/>
       <c r="C81" s="181"/>
       <c r="D81" s="182"/>
-      <c r="E81" s="257"/>
-      <c r="F81" s="257"/>
+      <c r="E81" s="235"/>
+      <c r="F81" s="235"/>
       <c r="G81" s="36"/>
       <c r="H81" s="36"/>
       <c r="I81" s="36"/>
@@ -4845,12 +4787,12 @@
       <c r="L81" s="50"/>
       <c r="N81" s="32"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="238" t="s">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A82" s="216" t="s">
         <v>7</v>
       </c>
-      <c r="B82" s="238"/>
-      <c r="C82" s="238"/>
+      <c r="B82" s="216"/>
+      <c r="C82" s="216"/>
       <c r="D82" s="31">
         <f>SUM(D79:D81)</f>
         <v>860560</v>
@@ -4889,7 +4831,7 @@
       </c>
       <c r="N82" s="32"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="181" t="s">
         <v>26</v>
       </c>
@@ -4899,11 +4841,11 @@
         <f>256650.95-853</f>
         <v>255797.95</v>
       </c>
-      <c r="E83" s="250">
+      <c r="E83" s="228">
         <f>D83*93.2%</f>
         <v>238403.68940000003</v>
       </c>
-      <c r="F83" s="236">
+      <c r="F83" s="214">
         <f>$D83*1.08%</f>
         <v>2762.6178600000003</v>
       </c>
@@ -4925,20 +4867,20 @@
       </c>
       <c r="L83" s="50"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="181" t="s">
         <v>27</v>
       </c>
       <c r="B84" s="181"/>
-      <c r="C84" s="258"/>
+      <c r="C84" s="236"/>
       <c r="D84" s="33">
         <v>69000</v>
       </c>
-      <c r="E84" s="250">
+      <c r="E84" s="228">
         <f>D84*93.2%</f>
         <v>64308</v>
       </c>
-      <c r="F84" s="236">
+      <c r="F84" s="214">
         <f>$D84*1.08%</f>
         <v>745.2</v>
       </c>
@@ -4960,12 +4902,12 @@
       </c>
       <c r="L84" s="50"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="238" t="s">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="216" t="s">
         <v>225</v>
       </c>
-      <c r="B85" s="238"/>
-      <c r="C85" s="238"/>
+      <c r="B85" s="216"/>
+      <c r="C85" s="216"/>
       <c r="D85" s="52">
         <f>SUM(D83:D84)</f>
         <v>324797.95</v>
@@ -5003,31 +4945,31 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="73"/>
       <c r="B86" s="73"/>
       <c r="C86" s="73"/>
       <c r="D86" s="73"/>
-      <c r="E86" s="259"/>
-      <c r="F86" s="259"/>
+      <c r="E86" s="237"/>
+      <c r="F86" s="237"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="72"/>
       <c r="L86" s="50"/>
     </row>
-    <row r="87" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="260" t="s">
+    <row r="87" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="238" t="s">
         <v>293</v>
       </c>
-      <c r="B87" s="261"/>
-      <c r="C87" s="261"/>
+      <c r="B87" s="239"/>
+      <c r="C87" s="239"/>
       <c r="D87" s="74"/>
-      <c r="E87" s="262">
+      <c r="E87" s="240">
         <f>D87*93.2%</f>
         <v>0</v>
       </c>
-      <c r="F87" s="262">
+      <c r="F87" s="240">
         <f>$D87*1.08%</f>
         <v>0</v>
       </c>
@@ -5056,10 +4998,10 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="263"/>
-      <c r="B88" s="264"/>
-      <c r="C88" s="264"/>
+    <row r="88" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="241"/>
+      <c r="B88" s="242"/>
+      <c r="C88" s="242"/>
       <c r="D88" s="75"/>
       <c r="E88" s="75"/>
       <c r="F88" s="75"/>
@@ -5070,12 +5012,12 @@
       <c r="K88" s="32"/>
       <c r="L88" s="50"/>
     </row>
-    <row r="89" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="265" t="s">
+    <row r="89" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="243" t="s">
         <v>28</v>
       </c>
-      <c r="B89" s="266"/>
-      <c r="C89" s="267"/>
+      <c r="B89" s="244"/>
+      <c r="C89" s="245"/>
       <c r="D89" s="66">
         <f t="shared" ref="D89:J89" si="18">SUM(D87+D42+D36+D85+D82+D75+D61+D51+D27++D47)</f>
         <v>15847087.939999999</v>
@@ -5117,108 +5059,108 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="65"/>
       <c r="B90" s="65"/>
       <c r="C90" s="65"/>
       <c r="D90" s="65"/>
-      <c r="E90" s="268"/>
-      <c r="F90" s="268"/>
+      <c r="E90" s="246"/>
+      <c r="F90" s="246"/>
       <c r="G90" s="32"/>
       <c r="H90" s="32"/>
       <c r="I90" s="32"/>
     </row>
-    <row r="91" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="269" t="s">
+    <row r="91" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="247" t="s">
         <v>36</v>
       </c>
-      <c r="B91" s="270"/>
-      <c r="C91" s="270"/>
+      <c r="B91" s="248"/>
+      <c r="C91" s="248"/>
       <c r="D91" s="65"/>
-      <c r="E91" s="268"/>
-      <c r="F91" s="268"/>
+      <c r="E91" s="246"/>
+      <c r="F91" s="246"/>
       <c r="G91" s="32"/>
       <c r="H91" s="32"/>
       <c r="I91" s="32"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="271"/>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A92" s="249"/>
       <c r="B92" s="65"/>
-      <c r="C92" s="210"/>
+      <c r="C92" s="205"/>
       <c r="D92" s="65"/>
-      <c r="E92" s="268"/>
-      <c r="F92" s="268"/>
+      <c r="E92" s="246"/>
+      <c r="F92" s="246"/>
       <c r="G92" s="32"/>
       <c r="H92" s="32"/>
       <c r="I92" s="32"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="271"/>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="249"/>
       <c r="B93" s="65"/>
-      <c r="C93" s="210"/>
+      <c r="C93" s="205"/>
       <c r="D93" s="65"/>
-      <c r="E93" s="268"/>
-      <c r="F93" s="268"/>
+      <c r="E93" s="246"/>
+      <c r="F93" s="246"/>
       <c r="G93" s="32"/>
       <c r="H93" s="32"/>
       <c r="I93" s="32"/>
     </row>
-    <row r="94" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="271"/>
+    <row r="94" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="249"/>
       <c r="B94" s="65"/>
-      <c r="C94" s="210"/>
+      <c r="C94" s="205"/>
       <c r="D94" s="65"/>
-      <c r="E94" s="268"/>
-      <c r="F94" s="268"/>
+      <c r="E94" s="246"/>
+      <c r="F94" s="246"/>
       <c r="G94" s="32"/>
       <c r="H94" s="32"/>
       <c r="I94" s="32"/>
     </row>
-    <row r="95" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="272" t="s">
+    <row r="95" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="B95" s="273"/>
-      <c r="C95" s="274">
+      <c r="B95" s="251"/>
+      <c r="C95" s="252">
         <f>SUM(C92:C94)</f>
         <v>0</v>
       </c>
       <c r="D95" s="65"/>
-      <c r="E95" s="268"/>
-      <c r="F95" s="268"/>
+      <c r="E95" s="246"/>
+      <c r="F95" s="246"/>
       <c r="G95" s="32"/>
       <c r="H95" s="32"/>
       <c r="I95" s="32"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="65"/>
       <c r="B96" s="65"/>
       <c r="C96" s="65"/>
       <c r="D96" s="65"/>
-      <c r="E96" s="268"/>
-      <c r="F96" s="268"/>
+      <c r="E96" s="246"/>
+      <c r="F96" s="246"/>
       <c r="G96" s="32"/>
       <c r="H96" s="32"/>
       <c r="I96" s="32"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="65"/>
       <c r="B97" s="65"/>
       <c r="C97" s="65"/>
       <c r="D97" s="65"/>
-      <c r="E97" s="275"/>
-      <c r="F97" s="275"/>
+      <c r="E97" s="253"/>
+      <c r="F97" s="253"/>
       <c r="G97" s="46"/>
       <c r="H97" s="46"/>
       <c r="I97" s="46"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="281" t="s">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="300" t="s">
         <v>32</v>
       </c>
-      <c r="B98" s="282"/>
-      <c r="C98" s="282"/>
-      <c r="D98" s="282"/>
+      <c r="B98" s="301"/>
+      <c r="C98" s="301"/>
+      <c r="D98" s="301"/>
       <c r="E98" s="60" t="s">
         <v>10</v>
       </c>
@@ -5238,24 +5180,24 @@
         <v>169</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="285"/>
-      <c r="B99" s="286"/>
-      <c r="C99" s="276"/>
+    <row r="99" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="279"/>
+      <c r="B99" s="280"/>
+      <c r="C99" s="254"/>
       <c r="D99" s="33"/>
-      <c r="E99" s="250">
+      <c r="E99" s="228">
         <f>D99</f>
         <v>0</v>
       </c>
-      <c r="F99" s="250"/>
+      <c r="F99" s="228"/>
       <c r="G99" s="49"/>
       <c r="H99" s="49"/>
       <c r="I99" s="49"/>
       <c r="J99" s="44"/>
     </row>
-    <row r="100" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="283"/>
-      <c r="B100" s="284"/>
+    <row r="100" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="302"/>
+      <c r="B100" s="303"/>
       <c r="C100" s="62"/>
       <c r="D100" s="33"/>
       <c r="E100" s="49"/>
@@ -5265,12 +5207,12 @@
       <c r="I100" s="49"/>
       <c r="J100" s="44"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="278" t="s">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="297" t="s">
         <v>16</v>
       </c>
-      <c r="B101" s="279"/>
-      <c r="C101" s="280"/>
+      <c r="B101" s="298"/>
+      <c r="C101" s="299"/>
       <c r="D101" s="59">
         <f>SUM(D99:D100)</f>
         <v>0</v>
@@ -5296,14 +5238,14 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E103" s="32"/>
       <c r="F103" s="32"/>
       <c r="G103" s="32"/>
       <c r="H103" s="32"/>
       <c r="I103" s="32"/>
     </row>
-    <row r="104" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="27" t="s">
         <v>29</v>
       </c>
@@ -5312,7 +5254,7 @@
         <v>15847087.939999999</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="29" t="s">
         <v>31</v>
       </c>
@@ -5320,45 +5262,45 @@
         <f>D89-D87</f>
         <v>15847087.939999999</v>
       </c>
-      <c r="D105" s="287" t="s">
+      <c r="D105" s="281" t="s">
         <v>284</v>
       </c>
-      <c r="E105" s="287"/>
-      <c r="F105" s="287"/>
-      <c r="G105" s="287"/>
-      <c r="H105" s="287"/>
-      <c r="I105" s="287"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D106" s="287"/>
-      <c r="E106" s="287"/>
-      <c r="F106" s="287"/>
-      <c r="G106" s="287"/>
-      <c r="H106" s="287"/>
-      <c r="I106" s="287"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D107" s="287"/>
-      <c r="E107" s="287"/>
-      <c r="F107" s="287"/>
-      <c r="G107" s="287"/>
-      <c r="H107" s="287"/>
-      <c r="I107" s="287"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E105" s="281"/>
+      <c r="F105" s="281"/>
+      <c r="G105" s="281"/>
+      <c r="H105" s="281"/>
+      <c r="I105" s="281"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D106" s="281"/>
+      <c r="E106" s="281"/>
+      <c r="F106" s="281"/>
+      <c r="G106" s="281"/>
+      <c r="H106" s="281"/>
+      <c r="I106" s="281"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D107" s="281"/>
+      <c r="E107" s="281"/>
+      <c r="F107" s="281"/>
+      <c r="G107" s="281"/>
+      <c r="H107" s="281"/>
+      <c r="I107" s="281"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B108" s="9"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="287"/>
-      <c r="E108" s="287"/>
-      <c r="F108" s="287"/>
-      <c r="G108" s="287"/>
-      <c r="H108" s="287"/>
-      <c r="I108" s="287"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D108" s="281"/>
+      <c r="E108" s="281"/>
+      <c r="F108" s="281"/>
+      <c r="G108" s="281"/>
+      <c r="H108" s="281"/>
+      <c r="I108" s="281"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
         <v>20</v>
       </c>
@@ -5366,14 +5308,14 @@
         <v>4948144.8095401041</v>
       </c>
       <c r="C109" s="12"/>
-      <c r="D109" s="287"/>
-      <c r="E109" s="287"/>
-      <c r="F109" s="287"/>
-      <c r="G109" s="287"/>
-      <c r="H109" s="287"/>
-      <c r="I109" s="287"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D109" s="281"/>
+      <c r="E109" s="281"/>
+      <c r="F109" s="281"/>
+      <c r="G109" s="281"/>
+      <c r="H109" s="281"/>
+      <c r="I109" s="281"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
         <v>21</v>
       </c>
@@ -5384,14 +5326,14 @@
       <c r="C110" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D110" s="287"/>
-      <c r="E110" s="287"/>
-      <c r="F110" s="287"/>
-      <c r="G110" s="287"/>
-      <c r="H110" s="287"/>
-      <c r="I110" s="287"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D110" s="281"/>
+      <c r="E110" s="281"/>
+      <c r="F110" s="281"/>
+      <c r="G110" s="281"/>
+      <c r="H110" s="281"/>
+      <c r="I110" s="281"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>346</v>
       </c>
@@ -5400,14 +5342,14 @@
         <v>1031545.1199999999</v>
       </c>
       <c r="C111" s="12"/>
-      <c r="D111" s="287"/>
-      <c r="E111" s="287"/>
-      <c r="F111" s="287"/>
-      <c r="G111" s="287"/>
-      <c r="H111" s="287"/>
-      <c r="I111" s="287"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D111" s="281"/>
+      <c r="E111" s="281"/>
+      <c r="F111" s="281"/>
+      <c r="G111" s="281"/>
+      <c r="H111" s="281"/>
+      <c r="I111" s="281"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>34</v>
       </c>
@@ -5416,15 +5358,15 @@
         <v>-15847087.939999999</v>
       </c>
       <c r="C112" s="10"/>
-      <c r="D112" s="287"/>
-      <c r="E112" s="287"/>
-      <c r="F112" s="287"/>
-      <c r="G112" s="287"/>
-      <c r="H112" s="287"/>
-      <c r="I112" s="287"/>
+      <c r="D112" s="281"/>
+      <c r="E112" s="281"/>
+      <c r="F112" s="281"/>
+      <c r="G112" s="281"/>
+      <c r="H112" s="281"/>
+      <c r="I112" s="281"/>
       <c r="K112" s="33"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>33</v>
       </c>
@@ -5433,49 +5375,49 @@
         <v>0</v>
       </c>
       <c r="C113" s="10"/>
-      <c r="D113" s="287"/>
-      <c r="E113" s="287"/>
-      <c r="F113" s="287"/>
-      <c r="G113" s="287"/>
-      <c r="H113" s="287"/>
-      <c r="I113" s="287"/>
+      <c r="D113" s="281"/>
+      <c r="E113" s="281"/>
+      <c r="F113" s="281"/>
+      <c r="G113" s="281"/>
+      <c r="H113" s="281"/>
+      <c r="I113" s="281"/>
       <c r="K113" s="39"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B114" s="63">
         <f>-PRORRATEO!H57</f>
         <v>-640914.39</v>
       </c>
       <c r="C114" s="10"/>
-      <c r="D114" s="287"/>
-      <c r="E114" s="287"/>
-      <c r="F114" s="287"/>
-      <c r="G114" s="287"/>
-      <c r="H114" s="287"/>
-      <c r="I114" s="287"/>
+      <c r="D114" s="281"/>
+      <c r="E114" s="281"/>
+      <c r="F114" s="281"/>
+      <c r="G114" s="281"/>
+      <c r="H114" s="281"/>
+      <c r="I114" s="281"/>
       <c r="K114" s="39"/>
     </row>
-    <row r="115" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="194" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B115" s="63">
         <f>-B131</f>
         <v>534732.1100000001</v>
       </c>
       <c r="C115" s="10"/>
-      <c r="D115" s="287"/>
-      <c r="E115" s="287"/>
-      <c r="F115" s="287"/>
-      <c r="G115" s="287"/>
-      <c r="H115" s="287"/>
-      <c r="I115" s="287"/>
+      <c r="D115" s="281"/>
+      <c r="E115" s="281"/>
+      <c r="F115" s="281"/>
+      <c r="G115" s="281"/>
+      <c r="H115" s="281"/>
+      <c r="I115" s="281"/>
       <c r="K115" s="39"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>274</v>
       </c>
@@ -5484,15 +5426,15 @@
         <v>0</v>
       </c>
       <c r="C116" s="10"/>
-      <c r="D116" s="287"/>
-      <c r="E116" s="287"/>
-      <c r="F116" s="287"/>
-      <c r="G116" s="287"/>
-      <c r="H116" s="287"/>
-      <c r="I116" s="287"/>
+      <c r="D116" s="281"/>
+      <c r="E116" s="281"/>
+      <c r="F116" s="281"/>
+      <c r="G116" s="281"/>
+      <c r="H116" s="281"/>
+      <c r="I116" s="281"/>
       <c r="K116" s="39"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>30</v>
       </c>
@@ -5501,29 +5443,29 @@
         <v>-60000</v>
       </c>
       <c r="C117" s="14"/>
-      <c r="D117" s="287"/>
-      <c r="E117" s="287"/>
-      <c r="F117" s="287"/>
-      <c r="G117" s="287"/>
-      <c r="H117" s="287"/>
-      <c r="I117" s="287"/>
-    </row>
-    <row r="118" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D117" s="281"/>
+      <c r="E117" s="281"/>
+      <c r="F117" s="281"/>
+      <c r="G117" s="281"/>
+      <c r="H117" s="281"/>
+      <c r="I117" s="281"/>
+    </row>
+    <row r="118" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="194" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B118" s="63">
         <v>-39639</v>
       </c>
       <c r="C118" s="14"/>
-      <c r="D118" s="287"/>
-      <c r="E118" s="287"/>
-      <c r="F118" s="287"/>
-      <c r="G118" s="287"/>
-      <c r="H118" s="287"/>
-      <c r="I118" s="287"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D118" s="281"/>
+      <c r="E118" s="281"/>
+      <c r="F118" s="281"/>
+      <c r="G118" s="281"/>
+      <c r="H118" s="281"/>
+      <c r="I118" s="281"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
         <v>36</v>
       </c>
@@ -5532,44 +5474,44 @@
         <v>0</v>
       </c>
       <c r="C119" s="14"/>
-      <c r="D119" s="287"/>
-      <c r="E119" s="287"/>
-      <c r="F119" s="287"/>
-      <c r="G119" s="287"/>
-      <c r="H119" s="287"/>
-      <c r="I119" s="287"/>
-    </row>
-    <row r="120" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="228" t="s">
-        <v>415</v>
+      <c r="D119" s="281"/>
+      <c r="E119" s="281"/>
+      <c r="F119" s="281"/>
+      <c r="G119" s="281"/>
+      <c r="H119" s="281"/>
+      <c r="I119" s="281"/>
+    </row>
+    <row r="120" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="206" t="s">
+        <v>405</v>
       </c>
       <c r="B120" s="63">
         <v>-81371</v>
       </c>
       <c r="C120" s="14"/>
-      <c r="D120" s="287"/>
-      <c r="E120" s="287"/>
-      <c r="F120" s="287"/>
-      <c r="G120" s="287"/>
-      <c r="H120" s="287"/>
-      <c r="I120" s="287"/>
-    </row>
-    <row r="121" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D120" s="281"/>
+      <c r="E120" s="281"/>
+      <c r="F120" s="281"/>
+      <c r="G120" s="281"/>
+      <c r="H120" s="281"/>
+      <c r="I120" s="281"/>
+    </row>
+    <row r="121" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="194" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="B121" s="63">
         <v>-10013539</v>
       </c>
       <c r="C121" s="14"/>
-      <c r="D121" s="287"/>
-      <c r="E121" s="287"/>
-      <c r="F121" s="287"/>
-      <c r="G121" s="287"/>
-      <c r="H121" s="287"/>
-      <c r="I121" s="287"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D121" s="281"/>
+      <c r="E121" s="281"/>
+      <c r="F121" s="281"/>
+      <c r="G121" s="281"/>
+      <c r="H121" s="281"/>
+      <c r="I121" s="281"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>23</v>
       </c>
@@ -5578,44 +5520,44 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C122" s="51"/>
-      <c r="D122" s="287"/>
-      <c r="E122" s="287"/>
-      <c r="F122" s="287"/>
-      <c r="G122" s="287"/>
-      <c r="H122" s="287"/>
-      <c r="I122" s="287"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D122" s="281"/>
+      <c r="E122" s="281"/>
+      <c r="F122" s="281"/>
+      <c r="G122" s="281"/>
+      <c r="H122" s="281"/>
+      <c r="I122" s="281"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="14"/>
       <c r="C123" s="10"/>
-      <c r="D123" s="287"/>
-      <c r="E123" s="287"/>
-      <c r="F123" s="287"/>
-      <c r="G123" s="287"/>
-      <c r="H123" s="287"/>
-      <c r="I123" s="287"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D123" s="281"/>
+      <c r="E123" s="281"/>
+      <c r="F123" s="281"/>
+      <c r="G123" s="281"/>
+      <c r="H123" s="281"/>
+      <c r="I123" s="281"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>273</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="10"/>
-      <c r="D124" s="287"/>
-      <c r="E124" s="287"/>
-      <c r="F124" s="287"/>
-      <c r="G124" s="287"/>
-      <c r="H124" s="287"/>
-      <c r="I124" s="287"/>
-    </row>
-    <row r="125" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="207"/>
+      <c r="D124" s="281"/>
+      <c r="E124" s="281"/>
+      <c r="F124" s="281"/>
+      <c r="G124" s="281"/>
+      <c r="H124" s="281"/>
+      <c r="I124" s="281"/>
+    </row>
+    <row r="125" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="202"/>
       <c r="B125" s="22"/>
       <c r="C125" s="10"/>
       <c r="D125" s="17"/>
       <c r="E125" s="17"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="25" t="s">
         <v>16</v>
       </c>
@@ -5626,17 +5568,17 @@
       <c r="C126" s="10"/>
       <c r="E126" s="17"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="14"/>
       <c r="C127" s="10"/>
       <c r="D127" s="17"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="14"/>
       <c r="C128" s="10"/>
       <c r="D128" s="17"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>19</v>
       </c>
@@ -5646,9 +5588,9 @@
       <c r="C129" s="10"/>
       <c r="D129" s="17"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B130" s="23">
         <f>-B114</f>
@@ -5657,9 +5599,9 @@
       <c r="C130" s="10"/>
       <c r="D130" s="17"/>
     </row>
-    <row r="131" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="229" t="s">
-        <v>422</v>
+    <row r="131" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="207" t="s">
+        <v>412</v>
       </c>
       <c r="B131" s="63">
         <f>-(D30+D31+D32+D33+D34+D70)</f>
@@ -5668,7 +5610,7 @@
       <c r="C131" s="10"/>
       <c r="D131" s="17"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="25" t="s">
         <v>16</v>
       </c>
@@ -5679,22 +5621,22 @@
       <c r="C132" s="10"/>
       <c r="D132" s="17"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="14"/>
       <c r="C133" s="10"/>
       <c r="D133" s="17"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="14"/>
       <c r="C134" s="10"/>
       <c r="D134" s="17"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="14"/>
       <c r="C135" s="10"/>
       <c r="D135" s="17"/>
     </row>
-    <row r="136" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C136" s="10"/>
       <c r="D136" s="32"/>
       <c r="E136" s="64"/>
@@ -5703,7 +5645,7 @@
       <c r="H136" s="64"/>
       <c r="I136" s="64"/>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>366</v>
       </c>
@@ -5711,17 +5653,17 @@
         <v>438840</v>
       </c>
       <c r="C137" s="16"/>
-      <c r="D137" s="288" t="s">
-        <v>424</v>
-      </c>
-      <c r="E137" s="289"/>
-      <c r="F137" s="289"/>
-      <c r="G137" s="289"/>
-      <c r="H137" s="289"/>
-      <c r="I137" s="289"/>
-      <c r="J137" s="290"/>
-    </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D137" s="282" t="s">
+        <v>414</v>
+      </c>
+      <c r="E137" s="283"/>
+      <c r="F137" s="283"/>
+      <c r="G137" s="283"/>
+      <c r="H137" s="283"/>
+      <c r="I137" s="283"/>
+      <c r="J137" s="284"/>
+    </row>
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="11" t="s">
         <v>240</v>
       </c>
@@ -5729,27 +5671,27 @@
         <v>60000</v>
       </c>
       <c r="C138" s="16"/>
-      <c r="D138" s="291"/>
-      <c r="E138" s="292"/>
-      <c r="F138" s="292"/>
-      <c r="G138" s="292"/>
-      <c r="H138" s="292"/>
-      <c r="I138" s="292"/>
-      <c r="J138" s="293"/>
-    </row>
-    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="285"/>
+      <c r="E138" s="286"/>
+      <c r="F138" s="286"/>
+      <c r="G138" s="286"/>
+      <c r="H138" s="286"/>
+      <c r="I138" s="286"/>
+      <c r="J138" s="287"/>
+    </row>
+    <row r="139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11"/>
       <c r="B139" s="63"/>
       <c r="C139" s="16"/>
-      <c r="D139" s="291"/>
-      <c r="E139" s="292"/>
-      <c r="F139" s="292"/>
-      <c r="G139" s="292"/>
-      <c r="H139" s="292"/>
-      <c r="I139" s="292"/>
-      <c r="J139" s="293"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D139" s="285"/>
+      <c r="E139" s="286"/>
+      <c r="F139" s="286"/>
+      <c r="G139" s="286"/>
+      <c r="H139" s="286"/>
+      <c r="I139" s="286"/>
+      <c r="J139" s="287"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="25" t="s">
         <v>16</v>
       </c>
@@ -5758,58 +5700,54 @@
         <v>498840</v>
       </c>
       <c r="C140" s="16"/>
-      <c r="D140" s="291"/>
-      <c r="E140" s="292"/>
-      <c r="F140" s="292"/>
-      <c r="G140" s="292"/>
-      <c r="H140" s="292"/>
-      <c r="I140" s="292"/>
-      <c r="J140" s="293"/>
-    </row>
-    <row r="141" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D140" s="285"/>
+      <c r="E140" s="286"/>
+      <c r="F140" s="286"/>
+      <c r="G140" s="286"/>
+      <c r="H140" s="286"/>
+      <c r="I140" s="286"/>
+      <c r="J140" s="287"/>
+    </row>
+    <row r="141" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C141" s="17"/>
-      <c r="D141" s="291"/>
-      <c r="E141" s="292"/>
-      <c r="F141" s="292"/>
-      <c r="G141" s="292"/>
-      <c r="H141" s="292"/>
-      <c r="I141" s="292"/>
-      <c r="J141" s="293"/>
-    </row>
-    <row r="142" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="299" t="s">
+      <c r="D141" s="285"/>
+      <c r="E141" s="286"/>
+      <c r="F141" s="286"/>
+      <c r="G141" s="286"/>
+      <c r="H141" s="286"/>
+      <c r="I141" s="286"/>
+      <c r="J141" s="287"/>
+    </row>
+    <row r="142" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="293" t="s">
         <v>367</v>
       </c>
-      <c r="B142" s="301">
+      <c r="B142" s="295">
         <f>B140+B122+B132</f>
         <v>1292035.369540107</v>
       </c>
       <c r="C142" s="10"/>
-      <c r="D142" s="291"/>
-      <c r="E142" s="292"/>
-      <c r="F142" s="292"/>
-      <c r="G142" s="292"/>
-      <c r="H142" s="292"/>
-      <c r="I142" s="292"/>
-      <c r="J142" s="293"/>
-    </row>
-    <row r="143" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="300"/>
-      <c r="B143" s="302"/>
-      <c r="D143" s="294"/>
-      <c r="E143" s="295"/>
-      <c r="F143" s="295"/>
-      <c r="G143" s="295"/>
-      <c r="H143" s="295"/>
-      <c r="I143" s="295"/>
-      <c r="J143" s="296"/>
+      <c r="D142" s="285"/>
+      <c r="E142" s="286"/>
+      <c r="F142" s="286"/>
+      <c r="G142" s="286"/>
+      <c r="H142" s="286"/>
+      <c r="I142" s="286"/>
+      <c r="J142" s="287"/>
+    </row>
+    <row r="143" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="294"/>
+      <c r="B143" s="296"/>
+      <c r="D143" s="288"/>
+      <c r="E143" s="289"/>
+      <c r="F143" s="289"/>
+      <c r="G143" s="289"/>
+      <c r="H143" s="289"/>
+      <c r="I143" s="289"/>
+      <c r="J143" s="290"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D137:J143"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
     <mergeCell ref="A14:J18"/>
     <mergeCell ref="A20:J22"/>
     <mergeCell ref="A50:B50"/>
@@ -5819,11 +5757,15 @@
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="D105:I124"/>
+    <mergeCell ref="D137:J143"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
     <mergeCell ref="A101:C101"/>
     <mergeCell ref="A98:D98"/>
     <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="D105:I124"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5834,37 +5776,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="340" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="341" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="341"/>
-      <c r="C1" s="341"/>
-      <c r="D1" s="341"/>
-      <c r="E1" s="341"/>
+      <c r="B1" s="342"/>
+      <c r="C1" s="342"/>
+      <c r="D1" s="342"/>
+      <c r="E1" s="342"/>
       <c r="F1" s="125" t="s">
         <v>276</v>
       </c>
@@ -5876,20 +5818,20 @@
       <c r="L1" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="318">
+      <c r="M1" s="319">
         <f>RESUMEN!D89-N3</f>
         <v>15847087.939999999</v>
       </c>
-      <c r="N1" s="319"/>
+      <c r="N1" s="320"/>
       <c r="O1" s="126"/>
       <c r="P1" s="45"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="342"/>
-      <c r="B2" s="343"/>
-      <c r="C2" s="343"/>
-      <c r="D2" s="343"/>
-      <c r="E2" s="343"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="343"/>
+      <c r="B2" s="344"/>
+      <c r="C2" s="344"/>
+      <c r="D2" s="344"/>
+      <c r="E2" s="344"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5908,12 +5850,12 @@
       <c r="O2" s="127"/>
       <c r="P2" s="45"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="342"/>
-      <c r="B3" s="343"/>
-      <c r="C3" s="343"/>
-      <c r="D3" s="343"/>
-      <c r="E3" s="343"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="343"/>
+      <c r="B3" s="344"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="344"/>
+      <c r="E3" s="344"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5932,12 +5874,12 @@
       <c r="O3" s="129"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="344"/>
-      <c r="B4" s="345"/>
-      <c r="C4" s="345"/>
-      <c r="D4" s="345"/>
-      <c r="E4" s="345"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="345"/>
+      <c r="B4" s="346"/>
+      <c r="C4" s="346"/>
+      <c r="D4" s="346"/>
+      <c r="E4" s="346"/>
       <c r="F4" s="130"/>
       <c r="G4" s="130"/>
       <c r="H4" s="130"/>
@@ -5950,98 +5892,98 @@
       <c r="O4" s="133"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="325" t="s">
+      <c r="C5" s="326" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="326"/>
-      <c r="E5" s="326"/>
-      <c r="F5" s="326"/>
-      <c r="G5" s="326"/>
-      <c r="H5" s="326"/>
-      <c r="I5" s="326"/>
-      <c r="J5" s="326"/>
-      <c r="K5" s="326"/>
-      <c r="L5" s="326"/>
-      <c r="M5" s="326"/>
-      <c r="N5" s="326"/>
-      <c r="O5" s="327"/>
+      <c r="D5" s="327"/>
+      <c r="E5" s="327"/>
+      <c r="F5" s="327"/>
+      <c r="G5" s="327"/>
+      <c r="H5" s="327"/>
+      <c r="I5" s="327"/>
+      <c r="J5" s="327"/>
+      <c r="K5" s="327"/>
+      <c r="L5" s="327"/>
+      <c r="M5" s="327"/>
+      <c r="N5" s="327"/>
+      <c r="O5" s="328"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="328"/>
-      <c r="D6" s="329"/>
-      <c r="E6" s="329"/>
-      <c r="F6" s="329"/>
-      <c r="G6" s="329"/>
-      <c r="H6" s="329"/>
-      <c r="I6" s="329"/>
-      <c r="J6" s="329"/>
-      <c r="K6" s="329"/>
-      <c r="L6" s="329"/>
-      <c r="M6" s="329"/>
-      <c r="N6" s="329"/>
-      <c r="O6" s="330"/>
+      <c r="C6" s="329"/>
+      <c r="D6" s="330"/>
+      <c r="E6" s="330"/>
+      <c r="F6" s="330"/>
+      <c r="G6" s="330"/>
+      <c r="H6" s="330"/>
+      <c r="I6" s="330"/>
+      <c r="J6" s="330"/>
+      <c r="K6" s="330"/>
+      <c r="L6" s="330"/>
+      <c r="M6" s="330"/>
+      <c r="N6" s="330"/>
+      <c r="O6" s="331"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="328"/>
-      <c r="D7" s="329"/>
-      <c r="E7" s="329"/>
-      <c r="F7" s="329"/>
-      <c r="G7" s="329"/>
-      <c r="H7" s="329"/>
-      <c r="I7" s="329"/>
-      <c r="J7" s="329"/>
-      <c r="K7" s="329"/>
-      <c r="L7" s="329"/>
-      <c r="M7" s="329"/>
-      <c r="N7" s="329"/>
-      <c r="O7" s="330"/>
+      <c r="C7" s="329"/>
+      <c r="D7" s="330"/>
+      <c r="E7" s="330"/>
+      <c r="F7" s="330"/>
+      <c r="G7" s="330"/>
+      <c r="H7" s="330"/>
+      <c r="I7" s="330"/>
+      <c r="J7" s="330"/>
+      <c r="K7" s="330"/>
+      <c r="L7" s="330"/>
+      <c r="M7" s="330"/>
+      <c r="N7" s="330"/>
+      <c r="O7" s="331"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="331"/>
-      <c r="D8" s="332"/>
-      <c r="E8" s="332"/>
-      <c r="F8" s="332"/>
-      <c r="G8" s="332"/>
-      <c r="H8" s="332"/>
-      <c r="I8" s="332"/>
-      <c r="J8" s="332"/>
-      <c r="K8" s="332"/>
-      <c r="L8" s="332"/>
-      <c r="M8" s="332"/>
-      <c r="N8" s="332"/>
-      <c r="O8" s="333"/>
+      <c r="C8" s="332"/>
+      <c r="D8" s="333"/>
+      <c r="E8" s="333"/>
+      <c r="F8" s="333"/>
+      <c r="G8" s="333"/>
+      <c r="H8" s="333"/>
+      <c r="I8" s="333"/>
+      <c r="J8" s="333"/>
+      <c r="K8" s="333"/>
+      <c r="L8" s="333"/>
+      <c r="M8" s="333"/>
+      <c r="N8" s="333"/>
+      <c r="O8" s="334"/>
       <c r="Q8" s="64"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="334" t="s">
+      <c r="C9" s="335" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="335"/>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
-      <c r="G9" s="335"/>
-      <c r="H9" s="335"/>
-      <c r="I9" s="335"/>
-      <c r="J9" s="335"/>
-      <c r="K9" s="335"/>
-      <c r="L9" s="335"/>
-      <c r="M9" s="335"/>
-      <c r="N9" s="335"/>
-      <c r="O9" s="336"/>
+      <c r="D9" s="336"/>
+      <c r="E9" s="336"/>
+      <c r="F9" s="336"/>
+      <c r="G9" s="336"/>
+      <c r="H9" s="336"/>
+      <c r="I9" s="336"/>
+      <c r="J9" s="336"/>
+      <c r="K9" s="336"/>
+      <c r="L9" s="336"/>
+      <c r="M9" s="336"/>
+      <c r="N9" s="336"/>
+      <c r="O9" s="337"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -6050,22 +5992,22 @@
         <v>139642.24780800001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="337"/>
-      <c r="D10" s="338"/>
-      <c r="E10" s="338"/>
-      <c r="F10" s="338"/>
-      <c r="G10" s="338"/>
-      <c r="H10" s="338"/>
-      <c r="I10" s="338"/>
-      <c r="J10" s="338"/>
-      <c r="K10" s="338"/>
-      <c r="L10" s="338"/>
-      <c r="M10" s="338"/>
-      <c r="N10" s="338"/>
-      <c r="O10" s="339"/>
+      <c r="C10" s="338"/>
+      <c r="D10" s="339"/>
+      <c r="E10" s="339"/>
+      <c r="F10" s="339"/>
+      <c r="G10" s="339"/>
+      <c r="H10" s="339"/>
+      <c r="I10" s="339"/>
+      <c r="J10" s="339"/>
+      <c r="K10" s="339"/>
+      <c r="L10" s="339"/>
+      <c r="M10" s="339"/>
+      <c r="N10" s="339"/>
+      <c r="O10" s="340"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -6074,50 +6016,50 @@
         <v>165501.923328</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="309" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="310" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="311" t="s">
+      <c r="B11" s="312" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="309" t="s">
+      <c r="C11" s="310" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="313" t="s">
+      <c r="D11" s="314" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="313" t="s">
+      <c r="E11" s="314" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="309" t="s">
+      <c r="F11" s="310" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="309" t="s">
+      <c r="G11" s="310" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="309" t="s">
+      <c r="H11" s="310" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="320" t="s">
+      <c r="I11" s="321" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="306" t="s">
+      <c r="J11" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="306" t="s">
-        <v>425</v>
-      </c>
-      <c r="L11" s="306" t="s">
+      <c r="K11" s="307" t="s">
+        <v>415</v>
+      </c>
+      <c r="L11" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="322" t="s">
+      <c r="M11" s="323" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="306" t="s">
+      <c r="N11" s="307" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="306" t="s">
+      <c r="O11" s="307" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -6128,22 +6070,22 @@
         <v>156451.03689600001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="310"/>
-      <c r="B12" s="312"/>
-      <c r="C12" s="310"/>
-      <c r="D12" s="314"/>
-      <c r="E12" s="314"/>
-      <c r="F12" s="310"/>
-      <c r="G12" s="310"/>
-      <c r="H12" s="310"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="307"/>
-      <c r="K12" s="307"/>
-      <c r="L12" s="307"/>
-      <c r="M12" s="323"/>
-      <c r="N12" s="307"/>
-      <c r="O12" s="307"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="311"/>
+      <c r="B12" s="313"/>
+      <c r="C12" s="311"/>
+      <c r="D12" s="315"/>
+      <c r="E12" s="315"/>
+      <c r="F12" s="311"/>
+      <c r="G12" s="311"/>
+      <c r="H12" s="311"/>
+      <c r="I12" s="322"/>
+      <c r="J12" s="308"/>
+      <c r="K12" s="308"/>
+      <c r="L12" s="308"/>
+      <c r="M12" s="324"/>
+      <c r="N12" s="308"/>
+      <c r="O12" s="308"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -6152,20 +6094,20 @@
         <v>192654.582624</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="310"/>
-      <c r="B13" s="312"/>
-      <c r="C13" s="310"/>
-      <c r="D13" s="314"/>
-      <c r="E13" s="314"/>
-      <c r="F13" s="310"/>
-      <c r="G13" s="310"/>
-      <c r="H13" s="310"/>
-      <c r="I13" s="321"/>
-      <c r="J13" s="307"/>
-      <c r="K13" s="308"/>
-      <c r="L13" s="308"/>
-      <c r="M13" s="323"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="311"/>
+      <c r="B13" s="313"/>
+      <c r="C13" s="311"/>
+      <c r="D13" s="315"/>
+      <c r="E13" s="315"/>
+      <c r="F13" s="311"/>
+      <c r="G13" s="311"/>
+      <c r="H13" s="311"/>
+      <c r="I13" s="322"/>
+      <c r="J13" s="308"/>
+      <c r="K13" s="309"/>
+      <c r="L13" s="309"/>
+      <c r="M13" s="324"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 18/06</v>
@@ -6182,7 +6124,7 @@
         <v>224979.17702399998</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="201" t="s">
         <v>114</v>
       </c>
@@ -6233,10 +6175,10 @@
       <c r="P14" s="85" t="s">
         <v>350</v>
       </c>
-      <c r="R14" s="315"/>
-      <c r="S14" s="315"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R14" s="316"/>
+      <c r="S14" s="316"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="24" t="s">
@@ -6284,10 +6226,10 @@
       <c r="P15" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="R15" s="315"/>
-      <c r="S15" s="315"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="316"/>
+      <c r="S15" s="316"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -6339,7 +6281,7 @@
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6389,7 +6331,7 @@
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
@@ -6407,7 +6349,7 @@
       <c r="G18" s="118">
         <v>391506.5096339999</v>
       </c>
-      <c r="H18" s="208">
+      <c r="H18" s="203">
         <v>98945</v>
       </c>
       <c r="I18" s="119">
@@ -6438,7 +6380,7 @@
       <c r="P18" s="85"/>
       <c r="S18" s="32"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="43" t="s">
         <v>116</v>
       </c>
@@ -6456,7 +6398,7 @@
       <c r="G19" s="149">
         <v>388906.01</v>
       </c>
-      <c r="H19" s="209">
+      <c r="H19" s="204">
         <f>G19</f>
         <v>388906.01</v>
       </c>
@@ -6492,7 +6434,7 @@
       </c>
       <c r="S19" s="32"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
         <v>117</v>
       </c>
@@ -6547,7 +6489,7 @@
       </c>
       <c r="S20" s="32"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
         <v>116</v>
       </c>
@@ -6601,7 +6543,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
         <v>118</v>
       </c>
@@ -6660,7 +6602,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
         <v>118</v>
       </c>
@@ -6716,7 +6658,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
         <v>118</v>
       </c>
@@ -6772,7 +6714,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="43" t="s">
         <v>116</v>
       </c>
@@ -6828,7 +6770,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
         <v>117</v>
       </c>
@@ -6882,7 +6824,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
         <v>116</v>
       </c>
@@ -6938,7 +6880,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="78" t="s">
         <v>118</v>
       </c>
@@ -6992,7 +6934,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="78" t="s">
         <v>118</v>
       </c>
@@ -7046,7 +6988,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="78" t="s">
         <v>118</v>
       </c>
@@ -7097,7 +7039,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="78" t="s">
         <v>116</v>
       </c>
@@ -7151,7 +7093,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
         <v>117</v>
       </c>
@@ -7207,7 +7149,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
         <v>116</v>
       </c>
@@ -7261,7 +7203,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="108" t="s">
         <v>118</v>
       </c>
@@ -7318,7 +7260,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
         <v>118</v>
       </c>
@@ -7327,7 +7269,7 @@
         <v>56</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E35" s="104" t="s">
         <v>272</v>
@@ -7374,7 +7316,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="43" t="s">
         <v>118</v>
       </c>
@@ -7425,7 +7367,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>116</v>
       </c>
@@ -7484,7 +7426,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
         <v>117</v>
       </c>
@@ -7538,7 +7480,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78" t="s">
         <v>116</v>
       </c>
@@ -7690,7 +7632,7 @@
       <c r="DI39" s="53"/>
       <c r="DJ39" s="53"/>
     </row>
-    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="78" t="s">
         <v>118</v>
       </c>
@@ -7841,7 +7783,7 @@
       <c r="DI40" s="53"/>
       <c r="DJ40" s="53"/>
     </row>
-    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="78" t="s">
         <v>118</v>
       </c>
@@ -7850,7 +7792,7 @@
         <v>62</v>
       </c>
       <c r="D41" s="78" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="E41" s="104"/>
       <c r="F41" s="105">
@@ -7995,7 +7937,7 @@
       <c r="DI41" s="53"/>
       <c r="DJ41" s="53"/>
     </row>
-    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="78" t="s">
         <v>118</v>
       </c>
@@ -8146,7 +8088,7 @@
       <c r="DI42" s="53"/>
       <c r="DJ42" s="53"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="43" t="s">
         <v>116</v>
       </c>
@@ -8200,7 +8142,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="43" t="s">
         <v>117</v>
       </c>
@@ -8256,7 +8198,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="43" t="s">
         <v>116</v>
       </c>
@@ -8316,7 +8258,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="137" t="s">
         <v>118</v>
       </c>
@@ -8370,7 +8312,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="43" t="s">
         <v>118</v>
       </c>
@@ -8426,7 +8368,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="43" t="s">
         <v>118</v>
       </c>
@@ -8480,7 +8422,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="43" t="s">
         <v>116</v>
       </c>
@@ -8534,7 +8476,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="43" t="s">
         <v>117</v>
       </c>
@@ -8589,7 +8531,7 @@
       </c>
       <c r="Q50" s="32"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="43" t="s">
         <v>116</v>
       </c>
@@ -8644,7 +8586,7 @@
       </c>
       <c r="Q51" s="32"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="43" t="s">
         <v>118</v>
       </c>
@@ -8656,7 +8598,7 @@
         <v>267</v>
       </c>
       <c r="E52" s="104" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F52" s="105">
         <v>9.4000000000000004E-3</v>
@@ -8700,10 +8642,10 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="Q52" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="43" t="s">
         <v>118</v>
       </c>
@@ -8757,7 +8699,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="43" t="s">
         <v>118</v>
       </c>
@@ -8808,7 +8750,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
         <v>116</v>
       </c>
@@ -8863,7 +8805,7 @@
       </c>
       <c r="R55" s="45"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
         <v>117</v>
       </c>
@@ -8919,7 +8861,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="43" t="s">
         <v>116</v>
       </c>
@@ -8972,18 +8914,18 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="43" t="s">
         <v>118</v>
       </c>
       <c r="B58" s="3"/>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="256" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="78" t="s">
+      <c r="D58" s="257" t="s">
         <v>193</v>
       </c>
-      <c r="E58" s="104" t="s">
+      <c r="E58" s="258" t="s">
         <v>299</v>
       </c>
       <c r="F58" s="105">
@@ -9025,7 +8967,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="78" t="s">
         <v>118</v>
       </c>
@@ -9082,7 +9024,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="78" t="s">
         <v>118</v>
       </c>
@@ -9139,7 +9081,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="78" t="s">
         <v>116</v>
       </c>
@@ -9193,7 +9135,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="78" t="s">
         <v>117</v>
       </c>
@@ -9247,7 +9189,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="43" t="s">
         <v>116</v>
       </c>
@@ -9300,7 +9242,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="43" t="s">
         <v>118</v>
       </c>
@@ -9312,7 +9254,7 @@
         <v>197</v>
       </c>
       <c r="E64" s="104" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="F64" s="105">
         <v>9.4000000000000004E-3</v>
@@ -9355,7 +9297,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="43" t="s">
         <v>118</v>
       </c>
@@ -9409,7 +9351,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="43" t="s">
         <v>118</v>
       </c>
@@ -9464,7 +9406,7 @@
       </c>
       <c r="S66" s="147"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="43" t="s">
         <v>116</v>
       </c>
@@ -9519,7 +9461,7 @@
       </c>
       <c r="S67" s="32"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="108" t="s">
         <v>117</v>
       </c>
@@ -9528,7 +9470,7 @@
         <v>89</v>
       </c>
       <c r="D68" s="78" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="E68" s="104"/>
       <c r="F68" s="105">
@@ -9573,15 +9515,15 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
         <v>116</v>
       </c>
       <c r="B69" s="3"/>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="265" t="s">
         <v>90</v>
       </c>
-      <c r="D69" s="78" t="s">
+      <c r="D69" s="266" t="s">
         <v>201</v>
       </c>
       <c r="E69" s="104"/>
@@ -9627,7 +9569,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
         <v>118</v>
       </c>
@@ -9681,7 +9623,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="43" t="s">
         <v>118</v>
       </c>
@@ -9738,7 +9680,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="43" t="s">
         <v>118</v>
       </c>
@@ -9789,7 +9731,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="43" t="s">
         <v>119</v>
       </c>
@@ -9844,7 +9786,7 @@
       </c>
       <c r="Q73" s="53"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="43" t="s">
         <v>116</v>
       </c>
@@ -9897,7 +9839,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="43" t="s">
         <v>118</v>
       </c>
@@ -9951,7 +9893,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="43" t="s">
         <v>118</v>
       </c>
@@ -10004,7 +9946,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="78" t="s">
         <v>118</v>
       </c>
@@ -10057,7 +9999,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="78" t="s">
         <v>119</v>
       </c>
@@ -10111,7 +10053,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="43" t="s">
         <v>116</v>
       </c>
@@ -10165,7 +10107,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="43" t="s">
         <v>118</v>
       </c>
@@ -10216,7 +10158,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
         <v>118</v>
       </c>
@@ -10272,7 +10214,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
         <v>118</v>
       </c>
@@ -10329,7 +10271,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="43" t="s">
         <v>119</v>
       </c>
@@ -10383,7 +10325,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="43" t="s">
         <v>116</v>
       </c>
@@ -10437,7 +10379,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="43" t="s">
         <v>118</v>
       </c>
@@ -10491,7 +10433,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="43" t="s">
         <v>118</v>
       </c>
@@ -10545,7 +10487,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="78" t="s">
         <v>118</v>
       </c>
@@ -10599,7 +10541,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="78"/>
       <c r="B88" s="24"/>
       <c r="C88" s="24" t="s">
@@ -10651,7 +10593,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="78"/>
       <c r="B89" s="24"/>
       <c r="C89" s="24" t="s">
@@ -10703,7 +10645,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="78"/>
       <c r="B90" s="24"/>
       <c r="C90" s="24" t="s">
@@ -10755,7 +10697,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="78"/>
       <c r="B91" s="24"/>
       <c r="C91" s="24" t="s">
@@ -10807,7 +10749,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="78"/>
       <c r="B92" s="24"/>
       <c r="C92" s="141" t="s">
@@ -10862,7 +10804,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="78"/>
       <c r="B93" s="24"/>
       <c r="C93" s="24" t="s">
@@ -10911,7 +10853,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="78"/>
       <c r="B94" s="24"/>
       <c r="C94" s="24" t="s">
@@ -10963,7 +10905,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="78"/>
       <c r="B95" s="24"/>
       <c r="C95" s="24" t="s">
@@ -11015,7 +10957,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="78"/>
       <c r="B96" s="24"/>
       <c r="C96" s="24" t="s">
@@ -11067,7 +11009,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="78"/>
       <c r="B97" s="24"/>
       <c r="C97" s="24" t="s">
@@ -11116,7 +11058,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="78"/>
       <c r="B98" s="24"/>
       <c r="C98" s="24" t="s">
@@ -11168,7 +11110,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="78"/>
       <c r="B99" s="24"/>
       <c r="C99" s="24" t="s">
@@ -11220,7 +11162,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="78"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24" t="s">
@@ -11272,7 +11214,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="78"/>
       <c r="B101" s="24"/>
       <c r="C101" s="24" t="s">
@@ -11321,7 +11263,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="78"/>
       <c r="B102" s="24"/>
       <c r="C102" s="24" t="s">
@@ -11373,7 +11315,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="78"/>
       <c r="B103" s="24"/>
       <c r="C103" s="24" t="s">
@@ -11425,7 +11367,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="78"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24" t="s">
@@ -11474,7 +11416,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="78"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24" t="s">
@@ -11526,7 +11468,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="78"/>
       <c r="B106" s="24"/>
       <c r="C106" s="24" t="s">
@@ -11577,7 +11519,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="78"/>
       <c r="B107" s="24"/>
       <c r="C107" s="24" t="s">
@@ -11629,7 +11571,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="78"/>
       <c r="B108" s="24"/>
       <c r="C108" s="24" t="s">
@@ -11681,7 +11623,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="78"/>
       <c r="B109" s="24"/>
       <c r="C109" s="24" t="s">
@@ -11733,7 +11675,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="78"/>
       <c r="B110" s="24"/>
       <c r="C110" s="24" t="s">
@@ -11784,7 +11726,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="78"/>
       <c r="B111" s="24"/>
       <c r="C111" s="24" t="s">
@@ -11836,7 +11778,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="78"/>
       <c r="B112" s="24"/>
       <c r="C112" s="24" t="s">
@@ -11888,7 +11830,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="78"/>
       <c r="B113" s="24"/>
       <c r="C113" s="24" t="s">
@@ -11940,7 +11882,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="78"/>
       <c r="B114" s="24"/>
       <c r="C114" s="24" t="s">
@@ -11992,7 +11934,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="78"/>
       <c r="B115" s="24"/>
       <c r="C115" s="24" t="s">
@@ -12044,7 +11986,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="78"/>
       <c r="B116" s="24"/>
       <c r="C116" s="24" t="s">
@@ -12098,7 +12040,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="78"/>
       <c r="B117" s="24"/>
       <c r="C117" s="24" t="s">
@@ -12152,7 +12094,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="78"/>
       <c r="B118" s="24"/>
       <c r="C118" s="24" t="s">
@@ -12209,7 +12151,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="97"/>
       <c r="B119" s="24"/>
       <c r="C119" s="24" t="s">
@@ -12261,7 +12203,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="97"/>
       <c r="B120" s="24"/>
       <c r="C120" s="24" t="s">
@@ -12313,7 +12255,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="97"/>
       <c r="B121" s="24"/>
       <c r="C121" s="24" t="s">
@@ -12367,7 +12309,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="97"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
@@ -12419,7 +12361,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="97"/>
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
@@ -12470,13 +12412,13 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="97"/>
       <c r="B124" s="24"/>
-      <c r="C124" s="24" t="s">
+      <c r="C124" s="277" t="s">
         <v>156</v>
       </c>
-      <c r="D124" s="78" t="s">
+      <c r="D124" s="278" t="s">
         <v>177</v>
       </c>
       <c r="E124" s="78"/>
@@ -12525,7 +12467,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="140"/>
       <c r="B125" s="135"/>
       <c r="C125" s="24" t="s">
@@ -12579,13 +12521,13 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="140"/>
       <c r="B126" s="135"/>
-      <c r="C126" s="24" t="s">
+      <c r="C126" s="371" t="s">
         <v>158</v>
       </c>
-      <c r="D126" s="78" t="s">
+      <c r="D126" s="372" t="s">
         <v>177</v>
       </c>
       <c r="E126" s="78"/>
@@ -12631,7 +12573,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="97"/>
       <c r="B127" s="24"/>
       <c r="C127" s="24" t="s">
@@ -12683,7 +12625,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="97"/>
       <c r="B128" s="24"/>
       <c r="C128" s="24" t="s">
@@ -12734,7 +12676,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="97"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24" t="s">
@@ -12786,7 +12728,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="97" t="s">
         <v>24</v>
       </c>
@@ -12839,7 +12781,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="97" t="s">
         <v>24</v>
       </c>
@@ -12893,7 +12835,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="40" t="s">
         <v>24</v>
       </c>
@@ -12912,7 +12854,7 @@
       <c r="N132" s="2"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -12954,43 +12896,43 @@
       </c>
       <c r="Q133" s="45"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L134" s="47">
         <f>L133-M1</f>
         <v>-598476.0837599989</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="317"/>
-      <c r="D135" s="317"/>
-      <c r="E135" s="317"/>
-      <c r="F135" s="317"/>
-      <c r="G135" s="317"/>
-      <c r="H135" s="317"/>
-      <c r="I135" s="317"/>
-      <c r="J135" s="317"/>
-      <c r="K135" s="317"/>
-      <c r="L135" s="317"/>
-      <c r="M135" s="317"/>
-      <c r="N135" s="317"/>
-      <c r="O135" s="317"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="317"/>
-      <c r="D136" s="317"/>
-      <c r="E136" s="317"/>
-      <c r="F136" s="317"/>
-      <c r="G136" s="317"/>
-      <c r="H136" s="317"/>
-      <c r="I136" s="317"/>
-      <c r="J136" s="317"/>
-      <c r="K136" s="317"/>
-      <c r="L136" s="317"/>
-      <c r="M136" s="317"/>
-      <c r="N136" s="317"/>
-      <c r="O136" s="317"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="318"/>
+      <c r="D135" s="318"/>
+      <c r="E135" s="318"/>
+      <c r="F135" s="318"/>
+      <c r="G135" s="318"/>
+      <c r="H135" s="318"/>
+      <c r="I135" s="318"/>
+      <c r="J135" s="318"/>
+      <c r="K135" s="318"/>
+      <c r="L135" s="318"/>
+      <c r="M135" s="318"/>
+      <c r="N135" s="318"/>
+      <c r="O135" s="318"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="318"/>
+      <c r="D136" s="318"/>
+      <c r="E136" s="318"/>
+      <c r="F136" s="318"/>
+      <c r="G136" s="318"/>
+      <c r="H136" s="318"/>
+      <c r="I136" s="318"/>
+      <c r="J136" s="318"/>
+      <c r="K136" s="318"/>
+      <c r="L136" s="318"/>
+      <c r="M136" s="318"/>
+      <c r="N136" s="318"/>
+      <c r="O136" s="318"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="57"/>
       <c r="D137" s="57"/>
       <c r="E137" s="57"/>
@@ -13005,129 +12947,129 @@
       <c r="N137" s="57"/>
       <c r="O137" s="57"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="324" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C138" s="325" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="324"/>
-      <c r="E138" s="324"/>
-      <c r="F138" s="324"/>
-      <c r="G138" s="324"/>
-      <c r="H138" s="324"/>
-      <c r="I138" s="324"/>
-      <c r="J138" s="324"/>
-      <c r="K138" s="324"/>
-      <c r="L138" s="324"/>
-      <c r="M138" s="324"/>
-      <c r="N138" s="324"/>
-      <c r="O138" s="324"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="324"/>
-      <c r="D139" s="324"/>
-      <c r="E139" s="324"/>
-      <c r="F139" s="324"/>
-      <c r="G139" s="324"/>
-      <c r="H139" s="324"/>
-      <c r="I139" s="324"/>
-      <c r="J139" s="324"/>
-      <c r="K139" s="324"/>
-      <c r="L139" s="324"/>
-      <c r="M139" s="324"/>
-      <c r="N139" s="324"/>
-      <c r="O139" s="324"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="324"/>
-      <c r="D140" s="324"/>
-      <c r="E140" s="324"/>
-      <c r="F140" s="324"/>
-      <c r="G140" s="324"/>
-      <c r="H140" s="324"/>
-      <c r="I140" s="324"/>
-      <c r="J140" s="324"/>
-      <c r="K140" s="324"/>
-      <c r="L140" s="324"/>
-      <c r="M140" s="324"/>
-      <c r="N140" s="324"/>
-      <c r="O140" s="324"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="324"/>
-      <c r="D141" s="324"/>
-      <c r="E141" s="324"/>
-      <c r="F141" s="324"/>
-      <c r="G141" s="324"/>
-      <c r="H141" s="324"/>
-      <c r="I141" s="324"/>
-      <c r="J141" s="324"/>
-      <c r="K141" s="324"/>
-      <c r="L141" s="324"/>
-      <c r="M141" s="324"/>
-      <c r="N141" s="324"/>
-      <c r="O141" s="324"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="324"/>
-      <c r="D142" s="324"/>
-      <c r="E142" s="324"/>
-      <c r="F142" s="324"/>
-      <c r="G142" s="324"/>
-      <c r="H142" s="324"/>
-      <c r="I142" s="324"/>
-      <c r="J142" s="324"/>
-      <c r="K142" s="324"/>
-      <c r="L142" s="324"/>
-      <c r="M142" s="324"/>
-      <c r="N142" s="324"/>
-      <c r="O142" s="324"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="324"/>
-      <c r="D143" s="324"/>
-      <c r="E143" s="324"/>
-      <c r="F143" s="324"/>
-      <c r="G143" s="324"/>
-      <c r="H143" s="324"/>
-      <c r="I143" s="324"/>
-      <c r="J143" s="324"/>
-      <c r="K143" s="324"/>
-      <c r="L143" s="324"/>
-      <c r="M143" s="324"/>
-      <c r="N143" s="324"/>
-      <c r="O143" s="324"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="324"/>
-      <c r="D144" s="324"/>
-      <c r="E144" s="324"/>
-      <c r="F144" s="324"/>
-      <c r="G144" s="324"/>
-      <c r="H144" s="324"/>
-      <c r="I144" s="324"/>
-      <c r="J144" s="324"/>
-      <c r="K144" s="324"/>
-      <c r="L144" s="324"/>
-      <c r="M144" s="324"/>
-      <c r="N144" s="324"/>
-      <c r="O144" s="324"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="324"/>
-      <c r="D145" s="324"/>
-      <c r="E145" s="324"/>
-      <c r="F145" s="324"/>
-      <c r="G145" s="324"/>
-      <c r="H145" s="324"/>
-      <c r="I145" s="324"/>
-      <c r="J145" s="324"/>
-      <c r="K145" s="324"/>
-      <c r="L145" s="324"/>
-      <c r="M145" s="324"/>
-      <c r="N145" s="324"/>
-      <c r="O145" s="324"/>
-    </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="325"/>
+      <c r="E138" s="325"/>
+      <c r="F138" s="325"/>
+      <c r="G138" s="325"/>
+      <c r="H138" s="325"/>
+      <c r="I138" s="325"/>
+      <c r="J138" s="325"/>
+      <c r="K138" s="325"/>
+      <c r="L138" s="325"/>
+      <c r="M138" s="325"/>
+      <c r="N138" s="325"/>
+      <c r="O138" s="325"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C139" s="325"/>
+      <c r="D139" s="325"/>
+      <c r="E139" s="325"/>
+      <c r="F139" s="325"/>
+      <c r="G139" s="325"/>
+      <c r="H139" s="325"/>
+      <c r="I139" s="325"/>
+      <c r="J139" s="325"/>
+      <c r="K139" s="325"/>
+      <c r="L139" s="325"/>
+      <c r="M139" s="325"/>
+      <c r="N139" s="325"/>
+      <c r="O139" s="325"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="325"/>
+      <c r="D140" s="325"/>
+      <c r="E140" s="325"/>
+      <c r="F140" s="325"/>
+      <c r="G140" s="325"/>
+      <c r="H140" s="325"/>
+      <c r="I140" s="325"/>
+      <c r="J140" s="325"/>
+      <c r="K140" s="325"/>
+      <c r="L140" s="325"/>
+      <c r="M140" s="325"/>
+      <c r="N140" s="325"/>
+      <c r="O140" s="325"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C141" s="325"/>
+      <c r="D141" s="325"/>
+      <c r="E141" s="325"/>
+      <c r="F141" s="325"/>
+      <c r="G141" s="325"/>
+      <c r="H141" s="325"/>
+      <c r="I141" s="325"/>
+      <c r="J141" s="325"/>
+      <c r="K141" s="325"/>
+      <c r="L141" s="325"/>
+      <c r="M141" s="325"/>
+      <c r="N141" s="325"/>
+      <c r="O141" s="325"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C142" s="325"/>
+      <c r="D142" s="325"/>
+      <c r="E142" s="325"/>
+      <c r="F142" s="325"/>
+      <c r="G142" s="325"/>
+      <c r="H142" s="325"/>
+      <c r="I142" s="325"/>
+      <c r="J142" s="325"/>
+      <c r="K142" s="325"/>
+      <c r="L142" s="325"/>
+      <c r="M142" s="325"/>
+      <c r="N142" s="325"/>
+      <c r="O142" s="325"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="325"/>
+      <c r="D143" s="325"/>
+      <c r="E143" s="325"/>
+      <c r="F143" s="325"/>
+      <c r="G143" s="325"/>
+      <c r="H143" s="325"/>
+      <c r="I143" s="325"/>
+      <c r="J143" s="325"/>
+      <c r="K143" s="325"/>
+      <c r="L143" s="325"/>
+      <c r="M143" s="325"/>
+      <c r="N143" s="325"/>
+      <c r="O143" s="325"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C144" s="325"/>
+      <c r="D144" s="325"/>
+      <c r="E144" s="325"/>
+      <c r="F144" s="325"/>
+      <c r="G144" s="325"/>
+      <c r="H144" s="325"/>
+      <c r="I144" s="325"/>
+      <c r="J144" s="325"/>
+      <c r="K144" s="325"/>
+      <c r="L144" s="325"/>
+      <c r="M144" s="325"/>
+      <c r="N144" s="325"/>
+      <c r="O144" s="325"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C145" s="325"/>
+      <c r="D145" s="325"/>
+      <c r="E145" s="325"/>
+      <c r="F145" s="325"/>
+      <c r="G145" s="325"/>
+      <c r="H145" s="325"/>
+      <c r="I145" s="325"/>
+      <c r="J145" s="325"/>
+      <c r="K145" s="325"/>
+      <c r="L145" s="325"/>
+      <c r="M145" s="325"/>
+      <c r="N145" s="325"/>
+      <c r="O145" s="325"/>
+    </row>
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="E146" s="57"/>
@@ -13142,7 +13084,7 @@
       <c r="N146" s="57"/>
       <c r="O146" s="57"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="57"/>
       <c r="D147" s="57"/>
       <c r="E147" s="57"/>
@@ -13157,116 +13099,116 @@
       <c r="N147" s="57"/>
       <c r="O147" s="57"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="316" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C148" s="317" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="316"/>
-      <c r="E148" s="316"/>
-      <c r="F148" s="316"/>
-      <c r="G148" s="316"/>
-      <c r="H148" s="316"/>
-      <c r="I148" s="316"/>
-      <c r="J148" s="316"/>
-      <c r="K148" s="316"/>
-      <c r="L148" s="316"/>
-      <c r="M148" s="316"/>
-      <c r="N148" s="316"/>
-      <c r="O148" s="316"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="316"/>
-      <c r="D149" s="316"/>
-      <c r="E149" s="316"/>
-      <c r="F149" s="316"/>
-      <c r="G149" s="316"/>
-      <c r="H149" s="316"/>
-      <c r="I149" s="316"/>
-      <c r="J149" s="316"/>
-      <c r="K149" s="316"/>
-      <c r="L149" s="316"/>
-      <c r="M149" s="316"/>
-      <c r="N149" s="316"/>
-      <c r="O149" s="316"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="316"/>
-      <c r="D150" s="316"/>
-      <c r="E150" s="316"/>
-      <c r="F150" s="316"/>
-      <c r="G150" s="316"/>
-      <c r="H150" s="316"/>
-      <c r="I150" s="316"/>
-      <c r="J150" s="316"/>
-      <c r="K150" s="316"/>
-      <c r="L150" s="316"/>
-      <c r="M150" s="316"/>
-      <c r="N150" s="316"/>
-      <c r="O150" s="316"/>
+      <c r="D148" s="317"/>
+      <c r="E148" s="317"/>
+      <c r="F148" s="317"/>
+      <c r="G148" s="317"/>
+      <c r="H148" s="317"/>
+      <c r="I148" s="317"/>
+      <c r="J148" s="317"/>
+      <c r="K148" s="317"/>
+      <c r="L148" s="317"/>
+      <c r="M148" s="317"/>
+      <c r="N148" s="317"/>
+      <c r="O148" s="317"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="317"/>
+      <c r="D149" s="317"/>
+      <c r="E149" s="317"/>
+      <c r="F149" s="317"/>
+      <c r="G149" s="317"/>
+      <c r="H149" s="317"/>
+      <c r="I149" s="317"/>
+      <c r="J149" s="317"/>
+      <c r="K149" s="317"/>
+      <c r="L149" s="317"/>
+      <c r="M149" s="317"/>
+      <c r="N149" s="317"/>
+      <c r="O149" s="317"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="317"/>
+      <c r="D150" s="317"/>
+      <c r="E150" s="317"/>
+      <c r="F150" s="317"/>
+      <c r="G150" s="317"/>
+      <c r="H150" s="317"/>
+      <c r="I150" s="317"/>
+      <c r="J150" s="317"/>
+      <c r="K150" s="317"/>
+      <c r="L150" s="317"/>
+      <c r="M150" s="317"/>
+      <c r="N150" s="317"/>
+      <c r="O150" s="317"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>598476.0837599989</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="316"/>
-      <c r="D151" s="316"/>
-      <c r="E151" s="316"/>
-      <c r="F151" s="316"/>
-      <c r="G151" s="316"/>
-      <c r="H151" s="316"/>
-      <c r="I151" s="316"/>
-      <c r="J151" s="316"/>
-      <c r="K151" s="316"/>
-      <c r="L151" s="316"/>
-      <c r="M151" s="316"/>
-      <c r="N151" s="316"/>
-      <c r="O151" s="316"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="316"/>
-      <c r="D152" s="316"/>
-      <c r="E152" s="316"/>
-      <c r="F152" s="316"/>
-      <c r="G152" s="316"/>
-      <c r="H152" s="316"/>
-      <c r="I152" s="316"/>
-      <c r="J152" s="316"/>
-      <c r="K152" s="316"/>
-      <c r="L152" s="316"/>
-      <c r="M152" s="316"/>
-      <c r="N152" s="316"/>
-      <c r="O152" s="316"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="316"/>
-      <c r="D153" s="316"/>
-      <c r="E153" s="316"/>
-      <c r="F153" s="316"/>
-      <c r="G153" s="316"/>
-      <c r="H153" s="316"/>
-      <c r="I153" s="316"/>
-      <c r="J153" s="316"/>
-      <c r="K153" s="316"/>
-      <c r="L153" s="316"/>
-      <c r="M153" s="316"/>
-      <c r="N153" s="316"/>
-      <c r="O153" s="316"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="316"/>
-      <c r="D154" s="316"/>
-      <c r="E154" s="316"/>
-      <c r="F154" s="316"/>
-      <c r="G154" s="316"/>
-      <c r="H154" s="316"/>
-      <c r="I154" s="316"/>
-      <c r="J154" s="316"/>
-      <c r="K154" s="316"/>
-      <c r="L154" s="316"/>
-      <c r="M154" s="316"/>
-      <c r="N154" s="316"/>
-      <c r="O154" s="316"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="317"/>
+      <c r="D151" s="317"/>
+      <c r="E151" s="317"/>
+      <c r="F151" s="317"/>
+      <c r="G151" s="317"/>
+      <c r="H151" s="317"/>
+      <c r="I151" s="317"/>
+      <c r="J151" s="317"/>
+      <c r="K151" s="317"/>
+      <c r="L151" s="317"/>
+      <c r="M151" s="317"/>
+      <c r="N151" s="317"/>
+      <c r="O151" s="317"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="317"/>
+      <c r="D152" s="317"/>
+      <c r="E152" s="317"/>
+      <c r="F152" s="317"/>
+      <c r="G152" s="317"/>
+      <c r="H152" s="317"/>
+      <c r="I152" s="317"/>
+      <c r="J152" s="317"/>
+      <c r="K152" s="317"/>
+      <c r="L152" s="317"/>
+      <c r="M152" s="317"/>
+      <c r="N152" s="317"/>
+      <c r="O152" s="317"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="317"/>
+      <c r="D153" s="317"/>
+      <c r="E153" s="317"/>
+      <c r="F153" s="317"/>
+      <c r="G153" s="317"/>
+      <c r="H153" s="317"/>
+      <c r="I153" s="317"/>
+      <c r="J153" s="317"/>
+      <c r="K153" s="317"/>
+      <c r="L153" s="317"/>
+      <c r="M153" s="317"/>
+      <c r="N153" s="317"/>
+      <c r="O153" s="317"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="317"/>
+      <c r="D154" s="317"/>
+      <c r="E154" s="317"/>
+      <c r="F154" s="317"/>
+      <c r="G154" s="317"/>
+      <c r="H154" s="317"/>
+      <c r="I154" s="317"/>
+      <c r="J154" s="317"/>
+      <c r="K154" s="317"/>
+      <c r="L154" s="317"/>
+      <c r="M154" s="317"/>
+      <c r="N154" s="317"/>
+      <c r="O154" s="317"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -13303,84 +13245,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="349" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="358" t="s">
         <v>305</v>
       </c>
-      <c r="B1" s="349"/>
-      <c r="C1" s="349"/>
-      <c r="D1" s="349"/>
-      <c r="E1" s="349"/>
-      <c r="F1" s="349"/>
-      <c r="G1" s="349"/>
-      <c r="H1" s="349"/>
-      <c r="I1" s="349"/>
-      <c r="J1" s="349"/>
-      <c r="K1" s="349"/>
-      <c r="L1" s="349"/>
-      <c r="M1" s="349"/>
-      <c r="N1" s="349"/>
-      <c r="O1" s="350"/>
+      <c r="B1" s="358"/>
+      <c r="C1" s="358"/>
+      <c r="D1" s="358"/>
+      <c r="E1" s="358"/>
+      <c r="F1" s="358"/>
+      <c r="G1" s="358"/>
+      <c r="H1" s="358"/>
+      <c r="I1" s="358"/>
+      <c r="J1" s="358"/>
+      <c r="K1" s="358"/>
+      <c r="L1" s="358"/>
+      <c r="M1" s="358"/>
+      <c r="N1" s="358"/>
+      <c r="O1" s="359"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="351"/>
-      <c r="B2" s="351"/>
-      <c r="C2" s="351"/>
-      <c r="D2" s="351"/>
-      <c r="E2" s="351"/>
-      <c r="F2" s="351"/>
-      <c r="G2" s="351"/>
-      <c r="H2" s="351"/>
-      <c r="I2" s="351"/>
-      <c r="J2" s="351"/>
-      <c r="K2" s="351"/>
-      <c r="L2" s="351"/>
-      <c r="M2" s="351"/>
-      <c r="N2" s="351"/>
-      <c r="O2" s="352"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="360"/>
+      <c r="B2" s="360"/>
+      <c r="C2" s="360"/>
+      <c r="D2" s="360"/>
+      <c r="E2" s="360"/>
+      <c r="F2" s="360"/>
+      <c r="G2" s="360"/>
+      <c r="H2" s="360"/>
+      <c r="I2" s="360"/>
+      <c r="J2" s="360"/>
+      <c r="K2" s="360"/>
+      <c r="L2" s="360"/>
+      <c r="M2" s="360"/>
+      <c r="N2" s="360"/>
+      <c r="O2" s="361"/>
       <c r="R2" s="32"/>
     </row>
-    <row r="3" spans="1:27" s="190" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="346" t="s">
+    <row r="3" spans="1:27" s="190" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="355" t="s">
         <v>369</v>
       </c>
-      <c r="B3" s="347"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="347"/>
-      <c r="E3" s="347"/>
-      <c r="F3" s="347"/>
-      <c r="G3" s="347"/>
-      <c r="H3" s="347"/>
-      <c r="I3" s="347"/>
-      <c r="J3" s="347"/>
-      <c r="K3" s="347"/>
-      <c r="L3" s="347"/>
-      <c r="M3" s="347"/>
-      <c r="N3" s="347"/>
-      <c r="O3" s="348"/>
+      <c r="B3" s="356"/>
+      <c r="C3" s="356"/>
+      <c r="D3" s="356"/>
+      <c r="E3" s="356"/>
+      <c r="F3" s="356"/>
+      <c r="G3" s="356"/>
+      <c r="H3" s="356"/>
+      <c r="I3" s="356"/>
+      <c r="J3" s="356"/>
+      <c r="K3" s="356"/>
+      <c r="L3" s="356"/>
+      <c r="M3" s="356"/>
+      <c r="N3" s="356"/>
+      <c r="O3" s="357"/>
       <c r="P3" s="191"/>
       <c r="Q3" s="191"/>
       <c r="R3" s="191"/>
@@ -13394,89 +13336,89 @@
       <c r="Z3" s="191"/>
       <c r="AA3" s="191"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="309" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="310" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="309" t="s">
+      <c r="B4" s="310" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="309" t="s">
+      <c r="C4" s="310" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="309" t="s">
+      <c r="D4" s="310" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="306" t="s">
+      <c r="E4" s="307" t="s">
         <v>331</v>
       </c>
-      <c r="F4" s="306" t="s">
+      <c r="F4" s="307" t="s">
         <v>332</v>
       </c>
-      <c r="G4" s="306" t="s">
+      <c r="G4" s="307" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="306" t="s">
+      <c r="H4" s="307" t="s">
         <v>337</v>
       </c>
-      <c r="I4" s="306" t="s">
+      <c r="I4" s="307" t="s">
         <v>347</v>
       </c>
-      <c r="J4" s="353" t="s">
+      <c r="J4" s="347" t="s">
         <v>333</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="358" t="s">
+      <c r="L4" s="352" t="s">
         <v>344</v>
       </c>
-      <c r="M4" s="306" t="s">
+      <c r="M4" s="307" t="s">
         <v>345</v>
       </c>
-      <c r="N4" s="306" t="s">
+      <c r="N4" s="307" t="s">
         <v>334</v>
       </c>
-      <c r="O4" s="306" t="s">
+      <c r="O4" s="307" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="310"/>
-      <c r="B5" s="310"/>
-      <c r="C5" s="310"/>
-      <c r="D5" s="310"/>
-      <c r="E5" s="307"/>
-      <c r="F5" s="307"/>
-      <c r="G5" s="307"/>
-      <c r="H5" s="307"/>
-      <c r="I5" s="307"/>
-      <c r="J5" s="354"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="311"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="311"/>
+      <c r="D5" s="311"/>
+      <c r="E5" s="308"/>
+      <c r="F5" s="308"/>
+      <c r="G5" s="308"/>
+      <c r="H5" s="308"/>
+      <c r="I5" s="308"/>
+      <c r="J5" s="348"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="359"/>
-      <c r="M5" s="307"/>
-      <c r="N5" s="307"/>
-      <c r="O5" s="307"/>
+      <c r="L5" s="353"/>
+      <c r="M5" s="308"/>
+      <c r="N5" s="308"/>
+      <c r="O5" s="308"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="357"/>
-      <c r="B6" s="357"/>
-      <c r="C6" s="357"/>
-      <c r="D6" s="357"/>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
-      <c r="G6" s="356"/>
-      <c r="H6" s="356"/>
-      <c r="I6" s="356"/>
-      <c r="J6" s="355"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="351"/>
+      <c r="B6" s="351"/>
+      <c r="C6" s="351"/>
+      <c r="D6" s="351"/>
+      <c r="E6" s="350"/>
+      <c r="F6" s="350"/>
+      <c r="G6" s="350"/>
+      <c r="H6" s="350"/>
+      <c r="I6" s="350"/>
+      <c r="J6" s="349"/>
       <c r="K6" s="160"/>
-      <c r="L6" s="360"/>
-      <c r="M6" s="356"/>
-      <c r="N6" s="356"/>
-      <c r="O6" s="356"/>
+      <c r="L6" s="354"/>
+      <c r="M6" s="350"/>
+      <c r="N6" s="350"/>
+      <c r="O6" s="350"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="161" t="s">
         <v>109</v>
       </c>
@@ -13511,7 +13453,7 @@
       <c r="K7" s="176">
         <v>-85849.897062580741</v>
       </c>
-      <c r="L7" s="209">
+      <c r="L7" s="204">
         <v>0</v>
       </c>
       <c r="M7" s="151">
@@ -13528,10 +13470,10 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="315"/>
-      <c r="S7" s="315"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R7" s="316"/>
+      <c r="S7" s="316"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="161" t="s">
         <v>313</v>
       </c>
@@ -13566,7 +13508,7 @@
       <c r="K8" s="113">
         <v>-300554.55212712329</v>
       </c>
-      <c r="L8" s="209"/>
+      <c r="L8" s="204"/>
       <c r="M8" s="151">
         <f t="shared" ref="M8:M69" si="3">IF(L8=H8,I8,J8)</f>
         <v>34751.71</v>
@@ -13583,10 +13525,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="315"/>
-      <c r="S8" s="315"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R8" s="316"/>
+      <c r="S8" s="316"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="161" t="s">
         <v>110</v>
       </c>
@@ -13621,7 +13563,7 @@
       <c r="K9" s="113">
         <v>-96183.680968261731</v>
       </c>
-      <c r="L9" s="209"/>
+      <c r="L9" s="204"/>
       <c r="M9" s="151">
         <f t="shared" si="3"/>
         <v>220785.72</v>
@@ -13640,7 +13582,7 @@
       </c>
       <c r="S9" s="32"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="161" t="s">
         <v>111</v>
       </c>
@@ -13675,7 +13617,7 @@
       <c r="K10" s="113">
         <v>-118441.06168819009</v>
       </c>
-      <c r="L10" s="209">
+      <c r="L10" s="204">
         <f>J10</f>
         <v>271876.73</v>
       </c>
@@ -13696,7 +13638,7 @@
       </c>
       <c r="S10" s="32"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="165" t="s">
         <v>112</v>
       </c>
@@ -13731,7 +13673,7 @@
       <c r="K11" s="121">
         <v>-139108.62949955213</v>
       </c>
-      <c r="L11" s="208">
+      <c r="L11" s="203">
         <v>0</v>
       </c>
       <c r="M11" s="120">
@@ -13751,7 +13693,7 @@
       </c>
       <c r="S11" s="32"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="168" t="s">
         <v>40</v>
       </c>
@@ -13788,7 +13730,7 @@
       <c r="K12" s="152">
         <v>-35723.479268552619</v>
       </c>
-      <c r="L12" s="209">
+      <c r="L12" s="204">
         <v>0</v>
       </c>
       <c r="M12" s="149">
@@ -13807,7 +13749,7 @@
       </c>
       <c r="S12" s="32"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="161" t="s">
         <v>41</v>
       </c>
@@ -13842,7 +13784,7 @@
       <c r="K13" s="114">
         <v>-13552.263311434101</v>
       </c>
-      <c r="L13" s="209"/>
+      <c r="L13" s="204"/>
       <c r="M13" s="149">
         <v>0</v>
       </c>
@@ -13860,7 +13802,7 @@
       </c>
       <c r="S13" s="32"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="161" t="s">
         <v>42</v>
       </c>
@@ -13897,7 +13839,7 @@
       <c r="K14" s="114">
         <v>-32267.293598652584</v>
       </c>
-      <c r="L14" s="209"/>
+      <c r="L14" s="204"/>
       <c r="M14" s="149">
         <v>0</v>
       </c>
@@ -13914,7 +13856,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="161" t="s">
         <v>43</v>
       </c>
@@ -13951,7 +13893,7 @@
       <c r="K15" s="114">
         <v>-39458.119568728027</v>
       </c>
-      <c r="L15" s="209"/>
+      <c r="L15" s="204"/>
       <c r="M15" s="149">
         <v>0</v>
       </c>
@@ -13968,7 +13910,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="161" t="s">
         <v>44</v>
       </c>
@@ -14003,7 +13945,7 @@
       <c r="K16" s="114">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L16" s="209"/>
+      <c r="L16" s="204"/>
       <c r="M16" s="149">
         <v>0</v>
       </c>
@@ -14020,7 +13962,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="161" t="s">
         <v>45</v>
       </c>
@@ -14057,7 +13999,7 @@
       <c r="K17" s="114">
         <v>-39739.963279933261</v>
       </c>
-      <c r="L17" s="209"/>
+      <c r="L17" s="204"/>
       <c r="M17" s="149">
         <v>0</v>
       </c>
@@ -14074,7 +14016,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="161" t="s">
         <v>46</v>
       </c>
@@ -14111,7 +14053,7 @@
       <c r="K18" s="114">
         <v>-59469.023064297158</v>
       </c>
-      <c r="L18" s="209"/>
+      <c r="L18" s="204"/>
       <c r="M18" s="149">
         <v>0</v>
       </c>
@@ -14128,7 +14070,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="161" t="s">
         <v>47</v>
       </c>
@@ -14163,7 +14105,7 @@
       <c r="K19" s="114">
         <v>-46167.529954363912</v>
       </c>
-      <c r="L19" s="209"/>
+      <c r="L19" s="204"/>
       <c r="M19" s="149">
         <v>0</v>
       </c>
@@ -14180,7 +14122,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="161" t="s">
         <v>48</v>
       </c>
@@ -14215,7 +14157,7 @@
       <c r="K20" s="114">
         <v>-50450.024305730825</v>
       </c>
-      <c r="L20" s="209"/>
+      <c r="L20" s="204"/>
       <c r="M20" s="149">
         <v>0</v>
       </c>
@@ -14232,7 +14174,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="161" t="s">
         <v>49</v>
       </c>
@@ -14267,7 +14209,7 @@
       <c r="K21" s="114">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L21" s="209"/>
+      <c r="L21" s="204"/>
       <c r="M21" s="149">
         <v>0</v>
       </c>
@@ -14284,7 +14226,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="161" t="s">
         <v>50</v>
       </c>
@@ -14319,7 +14261,7 @@
       <c r="K22" s="114">
         <v>-54278.041973373794</v>
       </c>
-      <c r="L22" s="209"/>
+      <c r="L22" s="204"/>
       <c r="M22" s="149">
         <v>0</v>
       </c>
@@ -14336,7 +14278,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="161" t="s">
         <v>51</v>
       </c>
@@ -14371,7 +14313,7 @@
       <c r="K23" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L23" s="209"/>
+      <c r="L23" s="204"/>
       <c r="M23" s="149">
         <f t="shared" si="3"/>
         <v>189591.12</v>
@@ -14389,7 +14331,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="161" t="s">
         <v>52</v>
       </c>
@@ -14424,7 +14366,7 @@
       <c r="K24" s="114">
         <v>-26459.180750895117</v>
       </c>
-      <c r="L24" s="209"/>
+      <c r="L24" s="204"/>
       <c r="M24" s="149">
         <v>0</v>
       </c>
@@ -14441,7 +14383,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="161" t="s">
         <v>53</v>
       </c>
@@ -14476,7 +14418,7 @@
       <c r="K25" s="114">
         <v>-18320.652254346118</v>
       </c>
-      <c r="L25" s="209">
+      <c r="L25" s="204">
         <f>H25</f>
         <v>86455.14</v>
       </c>
@@ -14496,7 +14438,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="161" t="s">
         <v>54</v>
       </c>
@@ -14533,7 +14475,7 @@
       <c r="K26" s="114">
         <v>-35494.022958517773</v>
       </c>
-      <c r="L26" s="209"/>
+      <c r="L26" s="204"/>
       <c r="M26" s="149">
         <v>0</v>
       </c>
@@ -14550,7 +14492,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="161" t="s">
         <v>55</v>
       </c>
@@ -14585,7 +14527,7 @@
       <c r="K27" s="114">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L27" s="209"/>
+      <c r="L27" s="204"/>
       <c r="M27" s="149">
         <f t="shared" si="3"/>
         <v>187595.16</v>
@@ -14606,7 +14548,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="161" t="s">
         <v>56</v>
       </c>
@@ -14641,7 +14583,7 @@
       <c r="K28" s="114">
         <v>-54278.041973373794</v>
       </c>
-      <c r="L28" s="209"/>
+      <c r="L28" s="204"/>
       <c r="M28" s="149">
         <v>0</v>
       </c>
@@ -14658,7 +14600,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="161" t="s">
         <v>57</v>
       </c>
@@ -14693,7 +14635,7 @@
       <c r="K29" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L29" s="209"/>
+      <c r="L29" s="204"/>
       <c r="M29" s="149">
         <f t="shared" si="3"/>
         <v>189591.18</v>
@@ -14711,7 +14653,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="161" t="s">
         <v>58</v>
       </c>
@@ -14746,7 +14688,7 @@
       <c r="K30" s="114">
         <v>-41158.725612503535</v>
       </c>
-      <c r="L30" s="209"/>
+      <c r="L30" s="204"/>
       <c r="M30" s="149">
         <v>0</v>
       </c>
@@ -14766,7 +14708,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="161" t="s">
         <v>59</v>
       </c>
@@ -14803,7 +14745,7 @@
       <c r="K31" s="114">
         <v>-27056.996275699232</v>
       </c>
-      <c r="L31" s="209"/>
+      <c r="L31" s="204"/>
       <c r="M31" s="149">
         <v>0</v>
       </c>
@@ -14820,7 +14762,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="161" t="s">
         <v>60</v>
       </c>
@@ -14857,7 +14799,7 @@
       <c r="K32" s="114">
         <v>-55523.211107424344</v>
       </c>
-      <c r="L32" s="209"/>
+      <c r="L32" s="204"/>
       <c r="M32" s="149">
         <f t="shared" si="3"/>
         <v>460534.21</v>
@@ -14973,7 +14915,7 @@
       <c r="DI32" s="53"/>
       <c r="DJ32" s="53"/>
     </row>
-    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="161" t="s">
         <v>61</v>
       </c>
@@ -15008,7 +14950,7 @@
       <c r="K33" s="114">
         <v>-58645.240752840618</v>
       </c>
-      <c r="L33" s="209">
+      <c r="L33" s="204">
         <f>J33</f>
         <v>187595.22</v>
       </c>
@@ -15128,7 +15070,7 @@
       <c r="DI33" s="53"/>
       <c r="DJ33" s="53"/>
     </row>
-    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="161" t="s">
         <v>62</v>
       </c>
@@ -15165,7 +15107,7 @@
       <c r="K34" s="114">
         <v>-68627.40939162203</v>
       </c>
-      <c r="L34" s="209"/>
+      <c r="L34" s="204"/>
       <c r="M34" s="149">
         <v>0</v>
       </c>
@@ -15282,7 +15224,7 @@
       <c r="DI34" s="53"/>
       <c r="DJ34" s="53"/>
     </row>
-    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="161" t="s">
         <v>63</v>
       </c>
@@ -15317,7 +15259,7 @@
       <c r="K35" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L35" s="209"/>
+      <c r="L35" s="204"/>
       <c r="M35" s="149">
         <f t="shared" si="3"/>
         <v>189591.24</v>
@@ -15433,7 +15375,7 @@
       <c r="DI35" s="53"/>
       <c r="DJ35" s="53"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="161" t="s">
         <v>64</v>
       </c>
@@ -15470,7 +15412,7 @@
       <c r="K36" s="114">
         <v>-37544.788729454507</v>
       </c>
-      <c r="L36" s="209"/>
+      <c r="L36" s="204"/>
       <c r="M36" s="149">
         <v>0</v>
       </c>
@@ -15487,7 +15429,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="161" t="s">
         <v>65</v>
       </c>
@@ -15522,7 +15464,7 @@
       <c r="K37" s="114">
         <v>-15441.692614377418</v>
       </c>
-      <c r="L37" s="209">
+      <c r="L37" s="204">
         <v>0</v>
       </c>
       <c r="M37" s="149">
@@ -15541,7 +15483,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="161" t="s">
         <v>66</v>
       </c>
@@ -15578,7 +15520,7 @@
       <c r="K38" s="114">
         <v>-44496.597872541868</v>
       </c>
-      <c r="L38" s="209"/>
+      <c r="L38" s="204"/>
       <c r="M38" s="149">
         <v>0</v>
       </c>
@@ -15601,7 +15543,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="161" t="s">
         <v>67</v>
       </c>
@@ -15638,7 +15580,7 @@
       <c r="K39" s="114">
         <v>-29363.23717477388</v>
       </c>
-      <c r="L39" s="209"/>
+      <c r="L39" s="204"/>
       <c r="M39" s="149">
         <v>238127.28000000003</v>
       </c>
@@ -15655,7 +15597,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="161" t="s">
         <v>68</v>
       </c>
@@ -15690,7 +15632,7 @@
       <c r="K40" s="114">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L40" s="209"/>
+      <c r="L40" s="204"/>
       <c r="M40" s="149">
         <v>0</v>
       </c>
@@ -15707,7 +15649,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="161" t="s">
         <v>69</v>
       </c>
@@ -15742,7 +15684,7 @@
       <c r="K41" s="114">
         <v>-23841.94471455997</v>
       </c>
-      <c r="L41" s="209"/>
+      <c r="L41" s="204"/>
       <c r="M41" s="149">
         <v>0</v>
       </c>
@@ -15759,7 +15701,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="161" t="s">
         <v>70</v>
       </c>
@@ -15796,7 +15738,7 @@
       <c r="K42" s="114">
         <v>-54586.004053324927</v>
       </c>
-      <c r="L42" s="209"/>
+      <c r="L42" s="204"/>
       <c r="M42" s="149">
         <v>0</v>
       </c>
@@ -15813,7 +15755,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="161" t="s">
         <v>71</v>
       </c>
@@ -15850,7 +15792,7 @@
       <c r="K43" s="114">
         <v>-15488.300927353266</v>
       </c>
-      <c r="L43" s="209"/>
+      <c r="L43" s="204"/>
       <c r="M43" s="149">
         <v>0</v>
       </c>
@@ -15868,7 +15810,7 @@
       </c>
       <c r="Q43" s="32"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="161" t="s">
         <v>72</v>
       </c>
@@ -15905,7 +15847,7 @@
       <c r="K44" s="114">
         <v>-44496.597872541868</v>
       </c>
-      <c r="L44" s="209"/>
+      <c r="L44" s="204"/>
       <c r="M44" s="149">
         <v>0</v>
       </c>
@@ -15923,7 +15865,7 @@
       </c>
       <c r="Q44" s="32"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="161" t="s">
         <v>73</v>
       </c>
@@ -15958,7 +15900,7 @@
       <c r="K45" s="114">
         <v>-18872.781500367477</v>
       </c>
-      <c r="L45" s="209">
+      <c r="L45" s="204">
         <v>206121.34</v>
       </c>
       <c r="M45" s="149">
@@ -15980,7 +15922,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="161" t="s">
         <v>74</v>
       </c>
@@ -16015,7 +15957,7 @@
       <c r="K46" s="114">
         <v>-26270.852233588957</v>
       </c>
-      <c r="L46" s="209"/>
+      <c r="L46" s="204"/>
       <c r="M46" s="149">
         <v>0</v>
       </c>
@@ -16032,7 +15974,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="161" t="s">
         <v>75</v>
       </c>
@@ -16067,7 +16009,7 @@
       <c r="K47" s="114">
         <v>-19073.555771647982</v>
       </c>
-      <c r="L47" s="209"/>
+      <c r="L47" s="204"/>
       <c r="M47" s="149">
         <v>0</v>
       </c>
@@ -16084,7 +16026,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="161" t="s">
         <v>76</v>
       </c>
@@ -16121,7 +16063,7 @@
       <c r="K48" s="114">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L48" s="209"/>
+      <c r="L48" s="204"/>
       <c r="M48" s="149">
         <v>0</v>
       </c>
@@ -16139,7 +16081,7 @@
       </c>
       <c r="R48" s="45"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="161" t="s">
         <v>77</v>
       </c>
@@ -16174,7 +16116,7 @@
       <c r="K49" s="114">
         <v>-20574.590917979629</v>
       </c>
-      <c r="L49" s="209"/>
+      <c r="L49" s="204"/>
       <c r="M49" s="149">
         <v>0</v>
       </c>
@@ -16191,7 +16133,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="161" t="s">
         <v>78</v>
       </c>
@@ -16228,7 +16170,7 @@
       <c r="K50" s="114">
         <v>-55523.211107424344</v>
       </c>
-      <c r="L50" s="209"/>
+      <c r="L50" s="204"/>
       <c r="M50" s="149">
         <f t="shared" si="3"/>
         <v>460534.39</v>
@@ -16246,7 +16188,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="161" t="s">
         <v>79</v>
       </c>
@@ -16281,7 +16223,7 @@
       <c r="K51" s="114">
         <v>-21231.879187913408</v>
       </c>
-      <c r="L51" s="209"/>
+      <c r="L51" s="204"/>
       <c r="M51" s="149">
         <v>0</v>
       </c>
@@ -16298,7 +16240,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="161" t="s">
         <v>80</v>
       </c>
@@ -16333,7 +16275,7 @@
       <c r="K52" s="114">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L52" s="209"/>
+      <c r="L52" s="204"/>
       <c r="M52" s="149">
         <v>0</v>
       </c>
@@ -16353,7 +16295,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="161" t="s">
         <v>81</v>
       </c>
@@ -16390,7 +16332,7 @@
       <c r="K53" s="114">
         <v>-26652.784512487007</v>
       </c>
-      <c r="L53" s="209"/>
+      <c r="L53" s="204"/>
       <c r="M53" s="149">
         <v>0</v>
       </c>
@@ -16410,7 +16352,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="161" t="s">
         <v>82</v>
       </c>
@@ -16447,7 +16389,7 @@
       <c r="K54" s="114">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L54" s="209"/>
+      <c r="L54" s="204"/>
       <c r="M54" s="149">
         <v>0</v>
       </c>
@@ -16464,7 +16406,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="161" t="s">
         <v>83</v>
       </c>
@@ -16499,7 +16441,7 @@
       <c r="K55" s="114">
         <v>-16488.587028911512</v>
       </c>
-      <c r="L55" s="209"/>
+      <c r="L55" s="204"/>
       <c r="M55" s="149">
         <v>0</v>
       </c>
@@ -16516,7 +16458,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="161" t="s">
         <v>84</v>
       </c>
@@ -16553,7 +16495,7 @@
       <c r="K56" s="114">
         <v>-28251.808173042373</v>
       </c>
-      <c r="L56" s="209"/>
+      <c r="L56" s="204"/>
       <c r="M56" s="149">
         <v>0</v>
       </c>
@@ -16570,7 +16512,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="161" t="s">
         <v>85</v>
       </c>
@@ -16607,7 +16549,7 @@
       <c r="K57" s="114">
         <v>-26426.913457296439</v>
       </c>
-      <c r="L57" s="209"/>
+      <c r="L57" s="204"/>
       <c r="M57" s="149">
         <v>0</v>
       </c>
@@ -16624,7 +16566,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="161" t="s">
         <v>86</v>
       </c>
@@ -16661,7 +16603,7 @@
       <c r="K58" s="114">
         <v>-27606.462301069463</v>
       </c>
-      <c r="L58" s="209"/>
+      <c r="L58" s="204"/>
       <c r="M58" s="149">
         <v>0</v>
       </c>
@@ -16678,7 +16620,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="161" t="s">
         <v>87</v>
       </c>
@@ -16715,7 +16657,7 @@
       <c r="K59" s="114">
         <v>-33257.557922213571</v>
       </c>
-      <c r="L59" s="209"/>
+      <c r="L59" s="204"/>
       <c r="M59" s="149">
         <f>IF(L59=H59,I59,J59)</f>
         <v>275853.48</v>
@@ -16734,7 +16676,7 @@
       </c>
       <c r="S59" s="147"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="161" t="s">
         <v>88</v>
       </c>
@@ -16771,7 +16713,7 @@
       <c r="K60" s="114">
         <v>-42237.887320636306</v>
       </c>
-      <c r="L60" s="209"/>
+      <c r="L60" s="204"/>
       <c r="M60" s="149">
         <v>0</v>
       </c>
@@ -16789,7 +16731,7 @@
       </c>
       <c r="S60" s="32"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="161" t="s">
         <v>89</v>
       </c>
@@ -16824,7 +16766,7 @@
       <c r="K61" s="114">
         <v>-16488.587028911512</v>
       </c>
-      <c r="L61" s="209"/>
+      <c r="L61" s="204"/>
       <c r="M61" s="149">
         <f>IF(L61=H61,I61,J61)</f>
         <v>174741.5</v>
@@ -16842,7 +16784,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="161" t="s">
         <v>90</v>
       </c>
@@ -16879,7 +16821,7 @@
       <c r="K62" s="114">
         <v>-46615.483485520119</v>
       </c>
-      <c r="L62" s="209"/>
+      <c r="L62" s="204"/>
       <c r="M62" s="149">
         <v>0</v>
       </c>
@@ -16896,7 +16838,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="161" t="s">
         <v>91</v>
       </c>
@@ -16931,7 +16873,7 @@
       <c r="K63" s="114">
         <v>-81340.722093700751</v>
       </c>
-      <c r="L63" s="209"/>
+      <c r="L63" s="204"/>
       <c r="M63" s="149">
         <v>0</v>
       </c>
@@ -16948,7 +16890,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="161" t="s">
         <v>92</v>
       </c>
@@ -16983,7 +16925,7 @@
       <c r="K64" s="114">
         <v>-21834.202001754922</v>
       </c>
-      <c r="L64" s="209"/>
+      <c r="L64" s="204"/>
       <c r="M64" s="149">
         <v>0</v>
       </c>
@@ -17003,7 +16945,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="161" t="s">
         <v>93</v>
       </c>
@@ -17040,7 +16982,7 @@
       <c r="K65" s="114">
         <v>-23691.364011099562</v>
       </c>
-      <c r="L65" s="209"/>
+      <c r="L65" s="204"/>
       <c r="M65" s="149">
         <f t="shared" si="3"/>
         <v>285419.53999999998</v>
@@ -17058,7 +17000,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="161" t="s">
         <v>94</v>
       </c>
@@ -17095,7 +17037,7 @@
       <c r="K66" s="114">
         <v>-41624.808742261725</v>
       </c>
-      <c r="L66" s="209"/>
+      <c r="L66" s="204"/>
       <c r="M66" s="149">
         <v>0</v>
       </c>
@@ -17113,7 +17055,7 @@
       </c>
       <c r="Q66" s="53"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="161" t="s">
         <v>95</v>
       </c>
@@ -17150,7 +17092,7 @@
       <c r="K67" s="114">
         <v>-42377.712259563734</v>
       </c>
-      <c r="L67" s="209"/>
+      <c r="L67" s="204"/>
       <c r="M67" s="149">
         <v>0</v>
       </c>
@@ -17167,7 +17109,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="161" t="s">
         <v>96</v>
       </c>
@@ -17193,7 +17135,7 @@
       <c r="K68" s="114">
         <v>-306490.57802999998</v>
       </c>
-      <c r="L68" s="209"/>
+      <c r="L68" s="204"/>
       <c r="M68" s="149">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -17211,7 +17153,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="161" t="s">
         <v>97</v>
       </c>
@@ -17246,7 +17188,7 @@
       <c r="K69" s="114">
         <v>-14036.272715413914</v>
       </c>
-      <c r="L69" s="209"/>
+      <c r="L69" s="204"/>
       <c r="M69" s="149">
         <f t="shared" si="3"/>
         <v>213867.58</v>
@@ -17264,7 +17206,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="161" t="s">
         <v>98</v>
       </c>
@@ -17301,7 +17243,7 @@
       <c r="K70" s="114">
         <v>-52250.939469883771</v>
       </c>
-      <c r="L70" s="209"/>
+      <c r="L70" s="204"/>
       <c r="M70" s="149">
         <v>0</v>
       </c>
@@ -17318,7 +17260,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="161" t="s">
         <v>99</v>
       </c>
@@ -17355,7 +17297,7 @@
       <c r="K71" s="114">
         <v>-293029.21731534239</v>
       </c>
-      <c r="L71" s="209"/>
+      <c r="L71" s="204"/>
       <c r="M71" s="149">
         <v>0</v>
       </c>
@@ -17372,7 +17314,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="161" t="s">
         <v>100</v>
       </c>
@@ -17409,7 +17351,7 @@
       <c r="K72" s="114">
         <v>-49440.664302824298</v>
       </c>
-      <c r="L72" s="209"/>
+      <c r="L72" s="204"/>
       <c r="M72" s="149">
         <v>0</v>
       </c>
@@ -17426,7 +17368,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="161" t="s">
         <v>101</v>
       </c>
@@ -17461,7 +17403,7 @@
       <c r="K73" s="114">
         <v>-18198.753589640051</v>
       </c>
-      <c r="L73" s="209"/>
+      <c r="L73" s="204"/>
       <c r="M73" s="149">
         <f t="shared" ref="M73" si="13">IF(L73=H73,I73,J73)</f>
         <v>228042.62</v>
@@ -17479,7 +17421,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="161" t="s">
         <v>102</v>
       </c>
@@ -17516,7 +17458,7 @@
       <c r="K74" s="114">
         <v>-21296.413775110734</v>
       </c>
-      <c r="L74" s="209"/>
+      <c r="L74" s="204"/>
       <c r="M74" s="149">
         <v>133429.63</v>
       </c>
@@ -17533,7 +17475,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="161" t="s">
         <v>103</v>
       </c>
@@ -17568,7 +17510,7 @@
       <c r="K75" s="114">
         <v>-19073.555771647982</v>
       </c>
-      <c r="L75" s="209"/>
+      <c r="L75" s="204"/>
       <c r="M75" s="149">
         <v>0</v>
       </c>
@@ -17585,7 +17527,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="161" t="s">
         <v>104</v>
       </c>
@@ -17622,7 +17564,7 @@
       <c r="K76" s="114">
         <v>-150580.49379336066</v>
       </c>
-      <c r="L76" s="209"/>
+      <c r="L76" s="204"/>
       <c r="M76" s="149">
         <v>0</v>
       </c>
@@ -17639,7 +17581,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="161" t="s">
         <v>105</v>
       </c>
@@ -17676,7 +17618,7 @@
       <c r="K77" s="114">
         <v>-38139.941033607349</v>
       </c>
-      <c r="L77" s="209"/>
+      <c r="L77" s="204"/>
       <c r="M77" s="149">
         <f>I77-L77</f>
         <v>238959.66</v>
@@ -17694,7 +17636,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="161" t="s">
         <v>106</v>
       </c>
@@ -17731,7 +17673,7 @@
       <c r="K78" s="114">
         <v>-28108.397979270667</v>
       </c>
-      <c r="L78" s="209"/>
+      <c r="L78" s="204"/>
       <c r="M78" s="149">
         <v>0</v>
       </c>
@@ -17748,7 +17690,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="161" t="s">
         <v>107</v>
       </c>
@@ -17785,7 +17727,7 @@
       <c r="K79" s="114">
         <v>-18535.767545003793</v>
       </c>
-      <c r="L79" s="209"/>
+      <c r="L79" s="204"/>
       <c r="M79" s="149">
         <v>0</v>
       </c>
@@ -17802,7 +17744,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="161" t="s">
         <v>108</v>
       </c>
@@ -17839,7 +17781,7 @@
       <c r="K80" s="114">
         <v>-29614.205013874453</v>
       </c>
-      <c r="L80" s="209">
+      <c r="L80" s="204">
         <f>J80</f>
         <v>279496.69</v>
       </c>
@@ -17859,7 +17801,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="24"/>
       <c r="B81" s="24"/>
       <c r="C81" s="78"/>
@@ -17871,12 +17813,12 @@
       <c r="I81" s="113"/>
       <c r="J81" s="113"/>
       <c r="K81" s="113"/>
-      <c r="L81" s="277"/>
+      <c r="L81" s="255"/>
       <c r="M81" s="113"/>
       <c r="N81" s="113"/>
       <c r="O81" s="114"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -17917,7 +17859,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M4:M6"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
@@ -17934,6 +17875,7 @@
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17942,18 +17884,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C1:N44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:M35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C2" s="202" t="s">
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C2" s="259" t="s">
         <v>351</v>
       </c>
-      <c r="D2" s="203">
+      <c r="D2" s="260">
         <v>1</v>
       </c>
-      <c r="E2" s="203"/>
+      <c r="E2" s="260"/>
       <c r="F2" s="195"/>
       <c r="G2" s="195"/>
       <c r="H2" s="195"/>
@@ -17963,48 +17905,49 @@
       <c r="L2" s="53"/>
       <c r="M2" s="53"/>
     </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C3" s="204" t="s">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C3" s="261" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="205"/>
-      <c r="E3" s="206">
+      <c r="D3" s="262"/>
+      <c r="E3" s="263">
         <v>0</v>
       </c>
       <c r="F3" s="53"/>
       <c r="G3" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="H3" s="197" t="s">
-        <v>370</v>
-      </c>
+      <c r="H3" s="197"/>
       <c r="I3" s="198"/>
       <c r="J3" s="199"/>
-      <c r="K3" s="227"/>
-      <c r="L3" s="227"/>
-      <c r="M3" s="227"/>
-    </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C4" s="204" t="s">
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C4" s="261" t="s">
         <v>354</v>
       </c>
-      <c r="D4" s="205" t="s">
+      <c r="D4" s="262" t="s">
         <v>355</v>
       </c>
-      <c r="E4" s="205" t="s">
+      <c r="E4" s="262" t="s">
         <v>356</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53" t="s">
         <v>357</v>
       </c>
+      <c r="H4" s="262" t="s">
+        <v>416</v>
+      </c>
       <c r="I4" s="198"/>
       <c r="J4" s="199"/>
-      <c r="K4" s="227"/>
-      <c r="L4" s="227"/>
-      <c r="M4" s="227"/>
-    </row>
-    <row r="5" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="264"/>
+      <c r="L4" s="264"/>
+      <c r="M4" s="264"/>
+    </row>
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="192" t="s">
         <v>358</v>
       </c>
@@ -18015,117 +17958,109 @@
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
       <c r="J5" s="200"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="227"/>
-    </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C6" s="361" t="s">
-        <v>371</v>
-      </c>
-      <c r="D6" s="362"/>
-      <c r="E6" s="362"/>
-      <c r="F6" s="362"/>
-      <c r="G6" s="362"/>
-      <c r="H6" s="362"/>
-      <c r="I6" s="362"/>
-      <c r="J6" s="363"/>
-      <c r="K6" s="227"/>
-      <c r="L6" s="227"/>
-      <c r="M6" s="227"/>
-    </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="364"/>
-      <c r="D7" s="365"/>
-      <c r="E7" s="365"/>
-      <c r="F7" s="365"/>
-      <c r="G7" s="365"/>
-      <c r="H7" s="365"/>
-      <c r="I7" s="365"/>
-      <c r="J7" s="366"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="264"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="362" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" s="363"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="363"/>
+      <c r="H6" s="363"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="364"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="365"/>
+      <c r="D7" s="366"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
+      <c r="G7" s="366"/>
+      <c r="H7" s="366"/>
+      <c r="I7" s="366"/>
+      <c r="J7" s="367"/>
       <c r="K7" s="53"/>
       <c r="L7" s="53"/>
       <c r="M7" s="53"/>
     </row>
-    <row r="8" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="367"/>
-      <c r="D8" s="368"/>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
-      <c r="G8" s="368"/>
-      <c r="H8" s="368"/>
-      <c r="I8" s="368"/>
-      <c r="J8" s="369"/>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="368"/>
+      <c r="D8" s="369"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
+      <c r="G8" s="369"/>
+      <c r="H8" s="369"/>
+      <c r="I8" s="369"/>
+      <c r="J8" s="370"/>
       <c r="K8" s="53"/>
       <c r="L8" s="53"/>
       <c r="M8" s="53"/>
     </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="K9" s="53"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
     </row>
-    <row r="10" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:14" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="202" t="s">
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="267" t="s">
         <v>351</v>
       </c>
-      <c r="D11" s="203">
+      <c r="D11" s="268">
         <f>D2+1</f>
         <v>2</v>
       </c>
-      <c r="E11" s="203"/>
+      <c r="E11" s="268"/>
       <c r="F11" s="195"/>
       <c r="G11" s="195"/>
       <c r="H11" s="195"/>
       <c r="I11" s="195"/>
       <c r="J11" s="196"/>
-      <c r="K11" s="211"/>
-    </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C12" s="204" t="s">
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="269" t="s">
         <v>352</v>
       </c>
-      <c r="D12" s="205"/>
-      <c r="E12" s="206">
+      <c r="D12" s="270"/>
+      <c r="E12" s="271">
         <v>0</v>
       </c>
       <c r="F12" s="53"/>
       <c r="G12" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="H12" s="197" t="s">
-        <v>370</v>
-      </c>
+      <c r="H12" s="197"/>
       <c r="I12" s="198"/>
       <c r="J12" s="199"/>
-      <c r="K12" s="227"/>
-      <c r="L12" s="227"/>
-      <c r="M12" s="227"/>
-      <c r="N12" s="227"/>
-    </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C13" s="204" t="s">
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="269" t="s">
         <v>354</v>
       </c>
-      <c r="D13" s="205" t="s">
+      <c r="D13" s="270" t="s">
         <v>355</v>
       </c>
-      <c r="E13" s="205" t="s">
+      <c r="E13" s="270" t="s">
         <v>356</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="53" t="s">
         <v>357</v>
       </c>
+      <c r="H13" s="270" t="s">
+        <v>418</v>
+      </c>
       <c r="I13" s="198"/>
       <c r="J13" s="199"/>
-      <c r="K13" s="227"/>
-      <c r="L13" s="227"/>
-      <c r="M13" s="227"/>
-      <c r="N13" s="227"/>
-    </row>
-    <row r="14" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="192" t="s">
         <v>358</v>
       </c>
@@ -18136,116 +18071,92 @@
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="J14" s="200"/>
-      <c r="K14" s="227"/>
-      <c r="L14" s="227"/>
-      <c r="M14" s="227"/>
-      <c r="N14" s="227"/>
-    </row>
-    <row r="15" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C15" s="361" t="s">
-        <v>372</v>
-      </c>
-      <c r="D15" s="362"/>
-      <c r="E15" s="362"/>
-      <c r="F15" s="362"/>
-      <c r="G15" s="362"/>
-      <c r="H15" s="362"/>
-      <c r="I15" s="362"/>
-      <c r="J15" s="363"/>
-      <c r="K15" s="227"/>
-      <c r="L15" s="227"/>
-      <c r="M15" s="227"/>
-      <c r="N15" s="227"/>
-    </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C16" s="364"/>
-      <c r="D16" s="365"/>
-      <c r="E16" s="365"/>
-      <c r="F16" s="365"/>
-      <c r="G16" s="365"/>
-      <c r="H16" s="365"/>
-      <c r="I16" s="365"/>
-      <c r="J16" s="366"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-    </row>
-    <row r="17" spans="3:14" ht="144.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="367"/>
-      <c r="D17" s="368"/>
-      <c r="E17" s="368"/>
-      <c r="F17" s="368"/>
-      <c r="G17" s="368"/>
-      <c r="H17" s="368"/>
-      <c r="I17" s="368"/>
-      <c r="J17" s="369"/>
-      <c r="K17" s="227"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="227"/>
-      <c r="N17" s="227"/>
-    </row>
-    <row r="19" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="212" t="s">
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="362" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="363"/>
+      <c r="E15" s="363"/>
+      <c r="F15" s="363"/>
+      <c r="G15" s="363"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="363"/>
+      <c r="J15" s="364"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="365"/>
+      <c r="D16" s="366"/>
+      <c r="E16" s="366"/>
+      <c r="F16" s="366"/>
+      <c r="G16" s="366"/>
+      <c r="H16" s="366"/>
+      <c r="I16" s="366"/>
+      <c r="J16" s="367"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="368"/>
+      <c r="D17" s="369"/>
+      <c r="E17" s="369"/>
+      <c r="F17" s="369"/>
+      <c r="G17" s="369"/>
+      <c r="H17" s="369"/>
+      <c r="I17" s="369"/>
+      <c r="J17" s="370"/>
+    </row>
+    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="273" t="s">
         <v>351</v>
       </c>
-      <c r="D20" s="213">
+      <c r="D20" s="274">
         <f>D11+1</f>
         <v>3</v>
       </c>
-      <c r="E20" s="213"/>
+      <c r="E20" s="274"/>
       <c r="F20" s="195"/>
       <c r="G20" s="195"/>
       <c r="H20" s="195"/>
       <c r="I20" s="195"/>
       <c r="J20" s="196"/>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="214" t="s">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="275" t="s">
         <v>352</v>
       </c>
-      <c r="D21" s="215"/>
-      <c r="E21" s="216">
+      <c r="D21" s="272"/>
+      <c r="E21" s="276">
         <v>0</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
         <v>353</v>
       </c>
-      <c r="H21" s="197" t="s">
-        <v>286</v>
-      </c>
+      <c r="H21" s="197"/>
       <c r="I21" s="198"/>
       <c r="J21" s="199"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="227"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="214" t="s">
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="275" t="s">
         <v>354</v>
       </c>
-      <c r="D22" s="215" t="s">
+      <c r="D22" s="272" t="s">
         <v>355</v>
       </c>
-      <c r="E22" s="215" t="s">
+      <c r="E22" s="272" t="s">
         <v>356</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
         <v>357</v>
       </c>
-      <c r="H22" s="215" t="s">
-        <v>374</v>
+      <c r="H22" s="272" t="s">
+        <v>420</v>
       </c>
       <c r="I22" s="198"/>
       <c r="J22" s="199"/>
-      <c r="K22" s="227"/>
-      <c r="L22" s="227"/>
-      <c r="M22" s="227"/>
-    </row>
-    <row r="23" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="192" t="s">
         <v>358</v>
       </c>
@@ -18256,73 +18167,61 @@
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="200"/>
-      <c r="K23" s="227"/>
-      <c r="L23" s="227"/>
-      <c r="M23" s="227"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="361" t="s">
-        <v>373</v>
-      </c>
-      <c r="D24" s="362"/>
-      <c r="E24" s="362"/>
-      <c r="F24" s="362"/>
-      <c r="G24" s="362"/>
-      <c r="H24" s="362"/>
-      <c r="I24" s="362"/>
-      <c r="J24" s="363"/>
-      <c r="K24" s="227"/>
-      <c r="L24" s="227"/>
-      <c r="M24" s="227"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="364"/>
-      <c r="D25" s="365"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
-      <c r="G25" s="365"/>
-      <c r="H25" s="365"/>
-      <c r="I25" s="365"/>
-      <c r="J25" s="366"/>
-      <c r="K25" s="227"/>
-      <c r="L25" s="227"/>
-      <c r="M25" s="227"/>
-    </row>
-    <row r="26" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="367"/>
-      <c r="D26" s="368"/>
-      <c r="E26" s="368"/>
-      <c r="F26" s="368"/>
-      <c r="G26" s="368"/>
-      <c r="H26" s="368"/>
-      <c r="I26" s="368"/>
-      <c r="J26" s="369"/>
-      <c r="K26" s="227"/>
-      <c r="L26" s="227"/>
-      <c r="M26" s="227"/>
-    </row>
-    <row r="28" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C29" s="217" t="s">
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="362" t="s">
+        <v>421</v>
+      </c>
+      <c r="D24" s="363"/>
+      <c r="E24" s="363"/>
+      <c r="F24" s="363"/>
+      <c r="G24" s="363"/>
+      <c r="H24" s="363"/>
+      <c r="I24" s="363"/>
+      <c r="J24" s="364"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="365"/>
+      <c r="D25" s="366"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
+      <c r="G25" s="366"/>
+      <c r="H25" s="366"/>
+      <c r="I25" s="366"/>
+      <c r="J25" s="367"/>
+    </row>
+    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="368"/>
+      <c r="D26" s="369"/>
+      <c r="E26" s="369"/>
+      <c r="F26" s="369"/>
+      <c r="G26" s="369"/>
+      <c r="H26" s="369"/>
+      <c r="I26" s="369"/>
+      <c r="J26" s="370"/>
+    </row>
+    <row r="28" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="373" t="s">
         <v>351</v>
       </c>
-      <c r="D29" s="218">
+      <c r="D29" s="374">
         <f>D20+1</f>
         <v>4</v>
       </c>
-      <c r="E29" s="218"/>
+      <c r="E29" s="374"/>
       <c r="F29" s="195"/>
       <c r="G29" s="195"/>
       <c r="H29" s="195"/>
       <c r="I29" s="195"/>
       <c r="J29" s="196"/>
     </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C30" s="219" t="s">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="375" t="s">
         <v>352</v>
       </c>
-      <c r="D30" s="220"/>
-      <c r="E30" s="221">
+      <c r="D30" s="376"/>
+      <c r="E30" s="377">
         <v>0</v>
       </c>
       <c r="F30" s="53"/>
@@ -18330,36 +18229,32 @@
         <v>353</v>
       </c>
       <c r="H30" s="197" t="s">
-        <v>375</v>
+        <v>423</v>
       </c>
       <c r="I30" s="198"/>
       <c r="J30" s="199"/>
-      <c r="K30" s="227"/>
-      <c r="L30" s="227"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C31" s="219" t="s">
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="375" t="s">
         <v>354</v>
       </c>
-      <c r="D31" s="220" t="s">
+      <c r="D31" s="376" t="s">
         <v>355</v>
       </c>
-      <c r="E31" s="220" t="s">
+      <c r="E31" s="376" t="s">
         <v>356</v>
       </c>
       <c r="F31" s="53"/>
       <c r="G31" s="53" t="s">
         <v>357</v>
       </c>
-      <c r="H31" s="53" t="s">
-        <v>375</v>
+      <c r="H31" s="376" t="s">
+        <v>422</v>
       </c>
       <c r="I31" s="198"/>
       <c r="J31" s="199"/>
-      <c r="K31" s="227"/>
-      <c r="L31" s="227"/>
-    </row>
-    <row r="32" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="192" t="s">
         <v>358</v>
       </c>
@@ -18370,153 +18265,45 @@
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
       <c r="J32" s="200"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="361" t="s">
-        <v>376</v>
-      </c>
-      <c r="D33" s="362"/>
-      <c r="E33" s="362"/>
-      <c r="F33" s="362"/>
-      <c r="G33" s="362"/>
-      <c r="H33" s="362"/>
-      <c r="I33" s="362"/>
-      <c r="J33" s="363"/>
-      <c r="K33" s="227"/>
-      <c r="L33" s="227"/>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="364"/>
-      <c r="D34" s="365"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
-      <c r="G34" s="365"/>
-      <c r="H34" s="365"/>
-      <c r="I34" s="365"/>
-      <c r="J34" s="366"/>
-      <c r="K34" s="227"/>
-      <c r="L34" s="227"/>
-    </row>
-    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="367"/>
-      <c r="D35" s="368"/>
-      <c r="E35" s="368"/>
-      <c r="F35" s="368"/>
-      <c r="G35" s="368"/>
-      <c r="H35" s="368"/>
-      <c r="I35" s="368"/>
-      <c r="J35" s="369"/>
-    </row>
-    <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C38" s="222" t="s">
-        <v>351</v>
-      </c>
-      <c r="D38" s="223">
-        <f>D29+1</f>
-        <v>5</v>
-      </c>
-      <c r="E38" s="223"/>
-      <c r="F38" s="195"/>
-      <c r="G38" s="195"/>
-      <c r="H38" s="195"/>
-      <c r="I38" s="195"/>
-      <c r="J38" s="196"/>
-    </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C39" s="224" t="s">
-        <v>352</v>
-      </c>
-      <c r="D39" s="225"/>
-      <c r="E39" s="226">
-        <v>0</v>
-      </c>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53" t="s">
-        <v>353</v>
-      </c>
-      <c r="H39" s="197" t="s">
-        <v>377</v>
-      </c>
-      <c r="I39" s="198"/>
-      <c r="J39" s="199"/>
-    </row>
-    <row r="40" spans="3:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C40" s="224" t="s">
-        <v>354</v>
-      </c>
-      <c r="D40" s="225" t="s">
-        <v>355</v>
-      </c>
-      <c r="E40" s="225" t="s">
-        <v>356</v>
-      </c>
-      <c r="F40" s="53"/>
-      <c r="G40" s="53" t="s">
-        <v>357</v>
-      </c>
-      <c r="H40" s="53" t="s">
-        <v>377</v>
-      </c>
-      <c r="I40" s="370" t="s">
-        <v>378</v>
-      </c>
-      <c r="J40" s="371"/>
-    </row>
-    <row r="41" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="192" t="s">
-        <v>358</v>
-      </c>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="200"/>
-    </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="361" t="s">
-        <v>379</v>
-      </c>
-      <c r="D42" s="362"/>
-      <c r="E42" s="362"/>
-      <c r="F42" s="362"/>
-      <c r="G42" s="362"/>
-      <c r="H42" s="362"/>
-      <c r="I42" s="362"/>
-      <c r="J42" s="363"/>
-    </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="364"/>
-      <c r="D43" s="365"/>
-      <c r="E43" s="365"/>
-      <c r="F43" s="365"/>
-      <c r="G43" s="365"/>
-      <c r="H43" s="365"/>
-      <c r="I43" s="365"/>
-      <c r="J43" s="366"/>
-    </row>
-    <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="367"/>
-      <c r="D44" s="368"/>
-      <c r="E44" s="368"/>
-      <c r="F44" s="368"/>
-      <c r="G44" s="368"/>
-      <c r="H44" s="368"/>
-      <c r="I44" s="368"/>
-      <c r="J44" s="369"/>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C33" s="362" t="s">
+        <v>424</v>
+      </c>
+      <c r="D33" s="363"/>
+      <c r="E33" s="363"/>
+      <c r="F33" s="363"/>
+      <c r="G33" s="363"/>
+      <c r="H33" s="363"/>
+      <c r="I33" s="363"/>
+      <c r="J33" s="364"/>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C34" s="365"/>
+      <c r="D34" s="366"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
+      <c r="G34" s="366"/>
+      <c r="H34" s="366"/>
+      <c r="I34" s="366"/>
+      <c r="J34" s="367"/>
+    </row>
+    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="368"/>
+      <c r="D35" s="369"/>
+      <c r="E35" s="369"/>
+      <c r="F35" s="369"/>
+      <c r="G35" s="369"/>
+      <c r="H35" s="369"/>
+      <c r="I35" s="369"/>
+      <c r="J35" s="370"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="C6:J8"/>
     <mergeCell ref="C15:J17"/>
-    <mergeCell ref="C6:J8"/>
     <mergeCell ref="C24:J26"/>
     <mergeCell ref="C33:J35"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="I40:J40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
